--- a/catalogo_tesis_MAN.xlsx
+++ b/catalogo_tesis_MAN.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -473,6 +473,7 @@
     <col width="45" customWidth="1" min="37" max="37"/>
     <col width="40" customWidth="1" min="38" max="38"/>
     <col width="40" customWidth="1" min="39" max="39"/>
+    <col width="40" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -668,6 +669,11 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>PDF en el sitio</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>Notas</t>
         </is>
       </c>
@@ -848,6 +854,11 @@
       </c>
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-quintanilla.pdf</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>El texto incluye resumen ejecutivo y abstract. Las tablas aparecen al final del archivo, separadas de sus títulos en el cuerpo. No se nombra una contraparte institucional formal: se usan fuentes públicas de ChileCompra sin convenio con una organización. El modelo 'es-specific' se menciona sin nombre completo. Los LLMs con prompts se mencionan solo como trabajo futuro, no se aplican.</t>
         </is>
@@ -1030,6 +1041,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-celedon.pdf</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="inlineStr">
+        <is>
           <t>La tesis aplica además AR, MA, ARMA, ARIMA, Random Forest, HistGradientBoosting, Elastic Net, Naive Seasonal, Diebold-Mariano con Newey-West y Holm, Model Confidence Set con bootstrap estacionario y pruebas ADF, KPSS y Ljung-Box; se omitieron de techniques por el límite de 10. La organización no se nombra en el texto. El texto incluye dedicatoria y agradecimientos extensos con nombres personales.</t>
         </is>
       </c>
@@ -1207,6 +1223,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-cabezas.pdf</t>
+        </is>
+      </c>
+      <c r="AN4" s="2" t="inlineStr">
+        <is>
           <t>El texto extraído comienza en el capítulo de metodología: no incluye portada, resumen, introducción ni marco teórico. Hay inconsistencia en el período de datos (1998-2023 en la descripción del enfoque, 1960-2023 en resultados). Las tablas y gráficos no están en el texto, por lo que no se dispone de RMSE ni de métricas de Random Forest en prueba.</t>
         </is>
       </c>
@@ -1388,6 +1409,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-torres.pdf</t>
+        </is>
+      </c>
+      <c r="AN5" s="2" t="inlineStr">
+        <is>
           <t>Las secciones referidas en la discusión (8.2.5, 8.2.6, 8.3.2) no coinciden con la numeración del informe. Hay inconsistencias menores en cifras entre secciones: el coeficiente de pct_diputados aparece como +0,2037 en la tabla OLS y +0,279 en conclusiones; la importancia de XGBoost se cita como 0,45 en conclusiones pero 0,188 por gain en la tabla. Año en portada: 2026.</t>
         </is>
       </c>
@@ -1569,6 +1595,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-gutierrez.pdf</t>
+        </is>
+      </c>
+      <c r="AN6" s="2" t="inlineStr">
+        <is>
           <t>Trabajo orientado a los Servicios de Salud Reloncaví, Chiloé y Osorno como contraparte institucional, pero los datos usados son públicos (DEIS) y no se declara convenio formal, por lo que organization se deja en null. La valorización económica (396 a 793 millones de pesos anuales) es un ejercicio ilustrativo, no un resultado del modelo. Fecha de la portada: junio 2026; profesor guía Richard Weber.</t>
         </is>
       </c>
@@ -1750,6 +1781,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-delrio.pdf</t>
+        </is>
+      </c>
+      <c r="AN7" s="2" t="inlineStr">
+        <is>
           <t>Tesis fechada 2026 (Actividad Formativa Equivalente), profesor guía Charles Thraves. Las predicciones sobre 2025 son retrospectivas: el resultado ya era conocido y la asignación manual de ese ciclo se ajustó al resultado observado (sesgo retrospectivo declarado por el autor). El modelo Beta=0 no alcanza optimalidad certificada en CBC y no es replicable entre corridas. Los anexos del texto solo contienen nombres de figuras, sin contenido.</t>
         </is>
       </c>
@@ -1931,6 +1967,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-hernandez.pdf</t>
+        </is>
+      </c>
+      <c r="AN8" s="2" t="inlineStr">
+        <is>
           <t>La portada indica 'Borrador Final' (abril 2026). Es una tesis de ingeniería de datos geoespaciales y producto (plataformas Catastral.cl y combustible.tremen.tech), no de modelamiento predictivo: no se entrenan modelos de ML; CLIP se usa como clasificador satelital preentrenado en el caso aplicado. El texto menciona Newmark Chile 'en el Capítulo 1' pero ese contexto no aparece en el documento. Algunas referencias cruzadas de sección son inconsistentes (p.ej. 'Sección 4.2.2' por 7.4.2).</t>
         </is>
       </c>
@@ -2115,6 +2156,11 @@
         </is>
       </c>
       <c r="AM9" s="2" t="inlineStr">
+        <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-canete.pdf</t>
+        </is>
+      </c>
+      <c r="AN9" s="2" t="inlineStr">
         <is>
           <t>La empresa no se nombra, aunque las gerencias listadas en el anexo (Transporte de Pasajeros, Extensiones, Obras Civiles) y la categoría de sindicato S_Metro sugieren un operador de transporte urbano. El texto no menciona lenguaje ni librerías. Hay una inconsistencia de signo: la metodología define persuasibles con uplift positivo, pero en los resultados los persuasibles son los de uplift score menor a -0,05 (moda en -1,0), ya que el outcome es la renuncia. La tabla 4 y el gráfico 8 están en anexos; los gráficos no se recuperan en el texto extraído.</t>
         </is>
@@ -2297,6 +2343,11 @@
       </c>
       <c r="AM10" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-araneda.pdf</t>
+        </is>
+      </c>
+      <c r="AN10" s="2" t="inlineStr">
+        <is>
           <t>El texto extraído no incluye las tablas en su lugar original: aparecen al final en formato de columnas separadas por barras verticales. El lenguaje Python no se menciona de forma explícita; se infiere por las librerías citadas (scikit-learn, transformers de Hugging Face, pysentimiento). Se evaluaron además BETO (nlptown), TextBlob y VADER como modelos de sentimiento, descartados por menor desempeño. Fecha de la portada: junio 2025.</t>
         </is>
       </c>
@@ -2482,6 +2533,11 @@
       </c>
       <c r="AM11" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-barros.pdf</t>
+        </is>
+      </c>
+      <c r="AN11" s="2" t="inlineStr">
+        <is>
           <t>La portada del texto extraído dice 'Determinación de las variables que explican eficiencia en establecimientos educacionales de Chile' (2025, profesora guía Felix Lizama); se usó el título oficial entregado. El resumen ejecutivo es más bien una declaración de objetivos; las cifras provienen de los capítulos de resultados y anexos. El tamaño de la muestra (912) se infiere de la tabla descriptiva del anexo 5 (valores únicos de DMU), no se declara explícitamente. Hay inconsistencias internas sobre el signo del efecto de la razón de horas de aula por alumno: el cuerpo y el anexo 10 lo describen como inverso, mientras el análisis por cuartiles y el anexo 9 lo describen como positivo. Las métricas se denominan 'de clasificación' aunque el problema es de regresión. Más de la mitad del texto son anexos con descripciones de gráficos SHAP.</t>
         </is>
       </c>
@@ -2667,6 +2723,11 @@
       </c>
       <c r="AM12" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-sepulveda.pdf</t>
+        </is>
+      </c>
+      <c r="AN12" s="2" t="inlineStr">
+        <is>
           <t>El texto tiene inconsistencias internas: la síntesis de P4 reporta 720 reclamos de seguridad alimentaria con 45/32/23 % de estrategias y notas 3,4/2,7/2,1, mientras que la sección correspondiente reporta 72 casos, 26,1 % evasivas, 73,9 % técnicas y cero transparentes (se usó esta última versión en los highlights). La base completa aparece como 5.465 y también como 5.468 evaluaciones. Hay párrafos duplicados en la sección de seguridad alimentaria y dos secciones tituladas Conclusiones. El OE5 se cita en la metodología pero no está en la lista de objetivos. No se nombra explícitamente el lenguaje de programación; el anexo muestra prompts en sintaxis tipo Python (SYSTEM_CONTENT = """..."""). Declara uso de Claude, ChatGPT y Gemini para mejorar la redacción.</t>
         </is>
       </c>
@@ -2852,6 +2913,11 @@
       </c>
       <c r="AM13" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-gajardo.pdf</t>
+        </is>
+      </c>
+      <c r="AN13" s="2" t="inlineStr">
+        <is>
           <t>El texto no nombra explícitamente el lenguaje; se infiere Python por las referencias a MinMaxScaler, seasonal_decompose, DataFrame, Adam y EarlyStopping. Se menciona que el modelo se orienta a un portfolio manager de un banco de inversión, pero no se identifica ninguna organización. Las tablas de machine learning (5 a 10) reportan RMSE pero el texto las llama repetidamente 'rentabilidad', lo que genera confusión; el resumen ejecutivo repite ese uso. Hay dos tablas numeradas como Tabla 2 y los gráficos ARIMA/SARIMAX y los boxplots del anexo no se extrajeron del PDF.</t>
         </is>
       </c>
@@ -3037,6 +3103,11 @@
       </c>
       <c r="AM14" s="2" t="inlineStr">
         <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-ceroni.pdf</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="inlineStr">
+        <is>
           <t>Documento rotulado como Taller AFE, Informe 3 (AFE para optar al grado), profesor guía Richard Weber, 2025. Resumen ejecutivo en español e inglés incluido. Las tablas y gráficos aparecen como texto al final. Inconsistencia menor: el texto dice que todos los R cuadrado por estilo superan 0,82, pero la tabla muestra Witbier con 0,77. Los modelos de clasificación (KNN, Random Forest, redes neuronales, SVM) se probaron como análisis alternativo y se descartaron.</t>
         </is>
       </c>
@@ -3225,6 +3296,11 @@
         </is>
       </c>
       <c r="AM15" s="2" t="inlineStr">
+        <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-yanez.pdf</t>
+        </is>
+      </c>
+      <c r="AN15" s="2" t="inlineStr">
         <is>
           <t>Informe final fechado en enero de 2025. El texto extraído perdió las ecuaciones y los contenidos de varias figuras y tablas; algunas tablas de resultados (A/E mensuales 2024) solo aparecen como títulos. Se detecta una inconsistencia menor: el MSE 824,35 se reporta para GRU y luego se atribuye a LSTM y GRU en conjunto. El autor no entrega el MSE numérico del LSTM de serie temporal.</t>
         </is>
@@ -4345,12 +4421,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Ingeniería Industrial, Universidad de Chile</t>
+          <t>Departamento de Ingeniería Industrial (DII), Facultad de Ciencias Físicas y Matemáticas (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial Engineering, Universidad de Chile</t>
+          <t>Department of Industrial Engineering (DII), School of Physical and Mathematical Sciences (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -4383,12 +4459,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Administración, Facultad de Economía y Negocios, Universidad de Chile</t>
+          <t>Departamento de Administración, Facultad de Economía y Negocios (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Department of Management, School of Economics and Business, Universidad de Chile</t>
+          <t>Department of Management, School of Economics and Business (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4421,12 +4497,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Administración, Facultad de Economía y Negocios, Universidad de Chile</t>
+          <t>Departamento de Administración, Facultad de Economía y Negocios (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Department of Management, School of Economics and Business, Universidad de Chile</t>
+          <t>Department of Management, School of Economics and Business (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4459,12 +4535,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Control de Gestión y Sistemas de Información, Facultad de Economía y Negocios, Universidad de Chile</t>
+          <t>Departamento de Control de Gestión y Sistemas de Información, Facultad de Economía y Negocios (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Department of Management Control and Information Systems, School of Economics and Business, Universidad de Chile</t>
+          <t>Department of Management Control and Information Systems, School of Economics and Business (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4497,12 +4573,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Ingeniería Industrial, Universidad de Chile</t>
+          <t>Departamento de Ingeniería Industrial (DII), Facultad de Ciencias Físicas y Matemáticas (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial Engineering, Universidad de Chile</t>
+          <t>Department of Industrial Engineering (DII), School of Physical and Mathematical Sciences (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4535,12 +4611,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Ingeniería Industrial, Universidad de Chile</t>
+          <t>Departamento de Ingeniería Industrial (DII), Facultad de Ciencias Físicas y Matemáticas (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial Engineering, Universidad de Chile</t>
+          <t>Department of Industrial Engineering (DII), School of Physical and Mathematical Sciences (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4611,12 +4687,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Administración, Facultad de Economía y Negocios, Universidad de Chile</t>
+          <t>Departamento de Administración, Facultad de Economía y Negocios (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Department of Management, School of Economics and Business, Universidad de Chile</t>
+          <t>Department of Management, School of Economics and Business (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4649,12 +4725,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Facultad de Economía y Negocios, Universidad de Chile</t>
+          <t>Facultad de Economía y Negocios (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>School of Economics and Business, Universidad de Chile</t>
+          <t>School of Economics and Business (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -4687,12 +4763,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Ingeniería Industrial, Universidad de Chile</t>
+          <t>Departamento de Ingeniería Industrial (DII), Facultad de Ciencias Físicas y Matemáticas (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial Engineering, Universidad de Chile</t>
+          <t>Department of Industrial Engineering (DII), School of Physical and Mathematical Sciences (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -4725,12 +4801,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Administración, Facultad de Economía y Negocios, Universidad de Chile</t>
+          <t>Departamento de Administración, Facultad de Economía y Negocios (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Department of Management, School of Economics and Business, Universidad de Chile</t>
+          <t>Department of Management, School of Economics and Business (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4801,12 +4877,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Control de Gestión y Sistemas de Información, Facultad de Economía y Negocios, Universidad de Chile</t>
+          <t>Departamento de Control de Gestión y Sistemas de Información, Facultad de Economía y Negocios (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Department of Management Control and Information Systems, School of Economics and Business, Universidad de Chile</t>
+          <t>Department of Management Control and Information Systems, School of Economics and Business (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4839,12 +4915,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Ingeniería Industrial, Universidad de Chile</t>
+          <t>Departamento de Ingeniería Industrial (DII), Facultad de Ciencias Físicas y Matemáticas (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial Engineering, Universidad de Chile</t>
+          <t>Department of Industrial Engineering (DII), School of Physical and Mathematical Sciences (FCFM), Universidad de Chile</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4877,12 +4953,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Facultad de Economía y Negocios, Universidad de Chile</t>
+          <t>Facultad de Economía y Negocios (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>School of Economics and Business, Universidad de Chile</t>
+          <t>School of Economics and Business (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/catalogo_tesis_MAN.xlsx
+++ b/catalogo_tesis_MAN.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -867,7 +867,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon</t>
+          <t>2026-astudillo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>INMEDIATO</t>
+          <t>INMEDIATO (confirmado por David Díaz, 2026-10-02)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Bastián Antonio Celedón Aguirre</t>
+          <t>Nicolás Andrés Astudillo Molina</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -895,7 +895,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -910,150 +910,146 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Predictive Analytics: forecast multi escenario del pipeline comercial con Machine Learning y XAI</t>
+          <t>Determinantes sociales del empleo forestal en Chile: un enfoque de machine learning aplicado a datos CASEN 2022</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Predictive Analytics: multi-scenario forecasting of the commercial pipeline with Machine Learning and XAI</t>
+          <t>Social determinants of forestry employment in Chile: a machine learning approach applied to CASEN 2022 data</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>ciencia y tecnología; servicios</t>
+          <t>industria; sector público</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>series de tiempo / forecasting; regresión</t>
+          <t>clasificación</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>SARIMAX; SARIMA; ARIMAX; Prophet; Temporal Fusion Transformer; Chronos-2; CatBoost; XGBoost; LightGBM; SHAP</t>
+          <t>Logistic Regression; Random Forest; Gradient Boosting; XGBoost; LightGBM; K-Nearest Neighbors; Multilayer Perceptron; SHAP; Stratified K-Fold Cross-Validation; Bootstrap Confidence Intervals</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Python; Darts</t>
+          <t>Python; scikit-learn; XGBoost; LightGBM; TensorFlow/Keras; SHAP</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Cierres ganados semanales del CRM corporativo (datos internos anonimizados del CRM de un corporativo de tecnologías de información (B2B))</t>
+          <t>Encuesta CASEN 2022 (CASEN 2022, Ministerio de Desarrollo Social y Familia (Centro de Encuestas y Estudios Longitudinales))</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>Corporativo de Tecnologías de Información con foco en integración tecnológica B2B (no identificado)</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>La tesis mejora el forecast de ingresos de una empresa privada de tecnología B2B para planificación comercial y financiera, sin una externalidad social evidente.</t>
+          <t>La tesis aborda directamente un problema de empleo y equidad: identifica las barreras de género, educación y territorio que condicionan el acceso al trabajo forestal y propone focalizar políticas públicas de capacitación, inclusión de género y reportería ESG en el sector.</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>The thesis improves revenue forecasting for a private B2B technology company for commercial and financial planning, with no evident social externality.</t>
+          <t>The thesis directly addresses an employment and equity problem: it identifies the gender, education, and territorial barriers that shape access to forestry work and proposes targeting public policies on training, gender inclusion, and ESG reporting in the sector.</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>forecasting comercial B2B; series de tiempo; SARIMAX; pipeline CRM; champion-challenger; XAI; SHAP</t>
+          <t>empleo forestal; determinantes sociales; CASEN 2022; machine learning; SHAP; ESG; clasificación binaria</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>B2B sales forecasting; time series; SARIMAX; CRM pipeline; champion-challenger; XAI; SHAP</t>
+          <t>forestry employment; social determinants; CASEN 2022; machine learning; SHAP; ESG; binary classification</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>La tesis desarrolla y evalúa un forecasting semanal multiescenario para el pipeline comercial de un corporativo de tecnologías de información B2B, cuyo forecast vigente depende de la señal cualitativa Committed del CRM. Con datos anonimizados de cierres ganados entre enero de 2023 y junio de 2026 (183 semanas, agregadas a frecuencia semanal en millones de dólares), se compara el Committed con referencias ingenuas, la progresión AR, MA, ARMA, ARIMA, ARIMAX, SARIMA y SARIMAX, los modelos avanzados Prophet, Temporal Fusion Transformer y Chronos-2, y seis algoritmos tabulares explicados con SHAP. La evaluación usa ocho ventanas de origen móvil (105 semanas fuera de muestra), covariables reconstruidas ex ante, métricas de error, sesgo, techo y dispersión, y contrastes Diebold-Mariano con Newey-West y Holm. SARIMAX ex ante con variables de fase resulta champion: WAPE agrupado de 55,38 %, techo de 67,74 % y desviación de 8,55, frente a 74,30 %, 102,24 % y 22,70 del Committed, reduciendo 412,55 MM USD de error absoluto en el panel histórico y 156,70 MM USD en Q2/2026. CatBoost logra la mejor mediana (53,46 %) pero con techo de 100,17 %, por lo que queda como challenger explicable. Se recomienda una arquitectura champion-challenger con revisión humana, monitoreo de MegaDeals y evolución futura hacia un Forecast Decision Agent prescriptivo.</t>
+          <t>La industria forestal chilena es estratégica para el empleo rural y las exportaciones, pero sus trabajadores enfrentan condiciones precarias, riesgos ocupacionales y brechas de género y etnia. Los estudios previos sobre los determinantes individuales del empleo forestal han descansado en modelos probit, que imponen formas funcionales aditivas y lineales. Esta tesis aplica siete algoritmos de clasificación supervisada (regresión logística, Random Forest, Gradient Boosting, XGBoost, LightGBM, KNN y perceptrón multicapa) sobre 73.676 ocupados de 25 a 65 años de la encuesta CASEN 2022, de los cuales 14.565 (19,8 %) trabajan en el sector forestal. Se comparan dos enfoques: el A replica 19 variables binarias organizadas en cinco dimensiones ESG derivadas de la NCG 461 de la CMF, y el B incorpora 42 variables enriquecidas con región, ruralidad, escolaridad, ingreso logarítmico, tipo de empleo y horas trabajadas. Con partición 70/30 estratificada, submuestreo 50/50 solo en entrenamiento y validación cruzada de cinco pliegues, el enfoque A alcanza un AUC-ROC de 0,751 y el B de 0,875, mejora de +0,124 significativa según intervalos bootstrap al 95 %. Los valores SHAP identifican la escolaridad, el género femenino, el tipo de empleo y el ingreso como determinantes principales, con efectos no lineales en edad y educación. Los resultados aportan una base para focalizar políticas de capacitación, inclusión de género y reportería ESG en el sector.</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>This thesis develops and evaluates a weekly, multi-scenario forecasting capability for the commercial pipeline of an information technology corporation focused on B2B technology integration, whose current forecast relies on the qualitative Committed signal recorded in the CRM. Using anonymized won-deal data from January 2023 to June 2026 (183 weeks, aggregated weekly in millions of US dollars), the Committed signal is compared against naive baselines, the AR, MA, ARMA, ARIMA, ARIMAX, SARIMA and SARIMAX progression, the advanced models Prophet, Temporal Fusion Transformer and Chronos-2, and six tabular algorithms explained with SHAP. Evaluation uses eight rolling-origin windows (105 out-of-sample weeks), ex ante reconstructed covariates, error, bias, ceiling and dispersion metrics, and Diebold-Mariano tests with Newey-West and Holm corrections. SARIMAX ex ante with phase variables emerges as champion: pooled WAPE of 55.38%, ceiling of 67.74% and dispersion of 8.55, versus 74.30%, 102.24% and 22.70 for Committed, cutting absolute error by USD 412.55 million over the historical panel and USD 156.70 million in Q2/2026. CatBoost attains the best median (53.46%) but with a 100.17% ceiling, so it remains an explainable challenger. The thesis recommends a champion-challenger architecture with human review, MegaDeal monitoring and future evolution toward a prescriptive Forecast Decision Agent.</t>
+          <t>The Chilean forestry industry is a strategic sector for rural employment and exports, yet its workers face precarious labor conditions, occupational risks, and gender and ethnic gaps. Previous studies of the individual determinants of forestry employment have relied on probit models, which impose additive and linear functional forms. This thesis applies seven supervised classification algorithms (logistic regression, Random Forest, Gradient Boosting, XGBoost, LightGBM, KNN, and a multilayer perceptron) to 73,676 employed individuals aged 25 to 65 from the CASEN 2022 survey, of whom 14,565 (19.8%) work in the forestry sector. Two approaches are compared: approach A replicates 19 binary variables organized into five ESG dimensions derived from CMF regulation NCG 461, and approach B adds 42 enriched variables including region, rurality, years of schooling, log income, employment type, and hours worked. Using a stratified 70/30 split, 50/50 undersampling applied only to the training set, and five-fold cross-validation, approach A reaches an AUC-ROC of 0.751 and approach B 0.875, a +0.124 improvement that is significant according to 95% bootstrap confidence intervals. SHAP values identify schooling, female gender, employment type, and income as the main determinants, with nonlinear effects of age and education. The results provide a basis for targeting training policies, gender inclusion programs, and ESG reporting in the sector.</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>SARIMAX ex ante con fase es el champion: WAPE agrupado de 55,38 %, techo de 67,74 % y desviación de 8,55, muy por debajo del Committed.</t>
+          <t>Siete algoritmos de clasificación se entrenan sobre 73.676 ocupados de la CASEN 2022, de los cuales 14.565 (19,8 %) son trabajadores forestales.</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>La evaluación usa ocho ventanas de origen móvil entre Q2/2024 y Q1/2026, con 105 semanas fuera de muestra y covariables del CRM reconstruidas ex ante.</t>
+          <t>Con las 19 variables binarias del conjunto base, los siete modelos convergen a un AUC-ROC entre 0,700 y 0,751, poder predictivo moderado.</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>En el panel histórico SARIMAX reduce 412,55 MM USD de error absoluto frente al Committed (25,46 %) y 156,70 MM USD en Q2/2026 (52,59 %).</t>
+          <t>Con 42 variables enriquecidas, el Gradient Boosting alcanza un AUC-ROC de 0,875, mejora de +0,124 con intervalos bootstrap al 95 % sin solapamiento.</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>CatBoost obtiene la mejor mediana de WAPE (53,46 %) pero un techo de 100,17 %, por lo que se conserva como challenger explicable con SHAP.</t>
+          <t>La regresión logística sube de 0,735 a 0,846 de AUC con las mismas variables: la mejora proviene de la información, no de la complejidad algorítmica.</t>
         </is>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>El 10 % de las oportunidades concentra 87,3 % de los ingresos y los rezagos de 26 y 13 semanas dominan la importancia SHAP.</t>
+          <t>SHAP con LightGBM sitúa la escolaridad (0,503), el género femenino (0,455) y el tipo de empleo (0,332) como determinantes principales, con edad en U invertida.</t>
         </is>
       </c>
       <c r="AG3" s="2" t="inlineStr">
         <is>
-          <t>SARIMAX ex ante with phase is the champion: pooled WAPE of 55.38%, ceiling of 67.74% and dispersion of 8.55, well below Committed.</t>
+          <t>Seven classification algorithms are trained on 73,676 employed individuals from CASEN 2022, of whom 14,565 (19.8%) are forestry workers.</t>
         </is>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>Evaluation uses eight rolling-origin windows from Q2/2024 to Q1/2026, with 105 out-of-sample weeks and CRM covariates reconstructed ex ante.</t>
+          <t>With the 19 binary variables of the base set, all seven models converge to an AUC-ROC between 0.700 and 0.751, moderate predictive power.</t>
         </is>
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>Over the historical panel SARIMAX cuts absolute error by USD 412.55 million versus Committed (25.46%) and by USD 156.70 million in Q2/2026 (52.59%).</t>
+          <t>With 42 enriched variables, Gradient Boosting reaches an AUC-ROC of 0.875, a +0.124 improvement with non-overlapping 95% bootstrap confidence intervals.</t>
         </is>
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>CatBoost achieves the best median WAPE (53.46%) but a 100.17% ceiling, so it is kept as an explainable challenger with SHAP.</t>
+          <t>Logistic regression rises from 0.735 to 0.846 AUC with the same variables: the gain comes from the added information, not algorithmic complexity.</t>
         </is>
       </c>
       <c r="AK3" s="2" t="inlineStr">
         <is>
-          <t>The top 10% of opportunities concentrate 87.3% of revenue, and 26-week and 13-week lags dominate CatBoost's SHAP importance.</t>
+          <t>SHAP with LightGBM ranks schooling (0.503), female gender (0.455), and employment type (0.332) as the main determinants, with an inverted U effect of age.</t>
         </is>
       </c>
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2026-celedon.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-astudillo.pdf</t>
         </is>
       </c>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>La tesis aplica además AR, MA, ARMA, ARIMA, Random Forest, HistGradientBoosting, Elastic Net, Naive Seasonal, Diebold-Mariano con Newey-West y Holm, Model Confidence Set con bootstrap estacionario y pruebas ADF, KPSS y Ljung-Box; se omitieron de techniques por el límite de 10. La organización no se nombra en el texto. El texto incluye dedicatoria y agradecimientos extensos con nombres personales.</t>
+          <t>El texto extraído coloca las tablas (métricas, intervalos bootstrap, importancia SHAP, variables del enfoque B) al final del archivo, después de la bibliografía. El texto contiene una inconsistencia menor: en la sección 6.1.4 y en la Tabla 8 la escolaridad es la variable más importante (mediana de |SHAP| 0,503) y el tipo de empleo ocupa el tercer lugar, pero en 6.2.5 y en la Tabla 11 se describe el tipo de empleo como la variable más importante. El modelo de mayor AUC en el enfoque B es Gradient Boosting (0,875), pero el análisis SHAP usa LightGBM (0,874) por compatibilidad con TreeExplainer. La tesis se vincula a un artículo previo del alumno con enfoque probit (Alvear y Astudillo, 2025, Forest Policy and Economics). Los hiperparámetros se fijaron sin búsqueda sistemática. Año de la memoria: 2026.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-cabezas</t>
+          <t>2026-celedon</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1068,7 +1064,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Cristian Rodrigo Cabezas Lepilla</t>
+          <t>Bastián Antonio Celedón Aguirre</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -1081,7 +1077,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -1089,153 +1085,157 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Charles Mark Thraves Cortés-Monroy</t>
+          <t>David Alejandro Díaz Solís</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Tasa de natalidad y política pública: modelos predictivos con datos de panel mundial y machine learning supervisado</t>
+          <t>Predictive Analytics: forecast multi escenario del pipeline comercial con Machine Learning y XAI</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Birth rate and public policy: predictive models with global panel data and supervised machine learning</t>
+          <t>Predictive Analytics: multi-scenario forecasting of the commercial pipeline with Machine Learning and XAI</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>sector público; política</t>
+          <t>ciencia y tecnología; servicios</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>regresión; análisis descriptivo e inferencial</t>
+          <t>series de tiempo / forecasting; regresión</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Linear Regression (OLS); Ridge Regression; Random Forest; Gradient Boosting; SHAP; Pearson Correlation; Log Transformation</t>
+          <t>SARIMAX; SARIMA; ARIMAX; Prophet; Temporal Fusion Transformer; Chronos-2; CatBoost; XGBoost; LightGBM; SHAP</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Python; Google Colab</t>
+          <t>Python; Darts</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>Indicadores de desarrollo mundial del Banco Mundial (panel de países, 1960-2023) (World Bank Open Data)</t>
+          <t>Cierres ganados semanales del CRM corporativo (datos internos anonimizados del CRM de un corporativo de tecnologías de información (B2B))</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>Corporativo de Tecnologías de Información con foco en integración tecnológica B2B (no identificado)</t>
+        </is>
+      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>La tesis aborda directamente un problema de política pública: la caída de la natalidad y sus determinantes socioeconómicos, proponiendo el modelo como herramienta para decisiones de política basadas en evidencia.</t>
+          <t>La tesis mejora el forecast de ingresos de una empresa privada de tecnología B2B para planificación comercial y financiera, sin una externalidad social evidente.</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>The thesis directly addresses a public policy problem: the decline in birth rates and its socioeconomic determinants, proposing the model as a tool for evidence-based policy decisions.</t>
+          <t>The thesis improves revenue forecasting for a private B2B technology company for commercial and financial planning, with no evident social externality.</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>tasa de natalidad; política pública; datos de panel; machine learning supervisado; Gradient Boosting; SHAP; transición demográfica</t>
+          <t>forecasting comercial B2B; series de tiempo; SARIMAX; pipeline CRM; champion-challenger; XAI; SHAP</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>birth rate; public policy; panel data; supervised machine learning; Gradient Boosting; SHAP; demographic transition</t>
+          <t>B2B sales forecasting; time series; SARIMAX; CRM pipeline; champion-challenger; XAI; SHAP</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>La tesis aborda la caída sostenida de la tasa de natalidad y su relevancia para el diseño de políticas públicas, con Chile como contexto de aplicación. Siguiendo CRISP-DM, se construye un modelo predictivo de la tasa de natalidad a partir de variables sociodemográficas y económicas internacionales. Los datos provienen de World Bank Open Data (1960-2023), en formato de panel de países y años, con indicadores de salud, educación, empleo y desarrollo económico. Tras filtrar casos completos, la base pasó de 14.047 a 923 registros, con mayor peso de países de ingreso alto (61 % de la muestra final). Se aplicaron transformaciones logarítmicas a las variables sesgadas y una partición por país (70 % entrenamiento, 30 % prueba) para evaluar la generalización a países no vistos. Se compararon regresión lineal múltiple (OLS), Ridge, Random Forest y Gradient Boosting mediante R², MAE y RMSE. Gradient Boosting obtuvo el mejor desempeño, con R² de 0,903 y MAE de 0,084 en prueba, mientras que los modelos lineales alcanzaron un R² de 0,839. El análisis SHAP identificó la esperanza de vida y la educación terciaria como los factores que más reducen la natalidad, y el empleo agrícola como el que más la eleva, en línea con la teoría de la transición demográfica. La herramienta se propone como apoyo a políticas públicas basadas en evidencia.</t>
+          <t>La tesis desarrolla y evalúa un forecasting semanal multiescenario para el pipeline comercial de un corporativo de tecnologías de información B2B, cuyo forecast vigente depende de la señal cualitativa Committed del CRM. Con datos anonimizados de cierres ganados entre enero de 2023 y junio de 2026 (183 semanas, agregadas a frecuencia semanal en millones de dólares), se compara el Committed con referencias ingenuas, la progresión AR, MA, ARMA, ARIMA, ARIMAX, SARIMA y SARIMAX, los modelos avanzados Prophet, Temporal Fusion Transformer y Chronos-2, y seis algoritmos tabulares explicados con SHAP. La evaluación usa ocho ventanas de origen móvil (105 semanas fuera de muestra), covariables reconstruidas ex ante, métricas de error, sesgo, techo y dispersión, y contrastes Diebold-Mariano con Newey-West y Holm. SARIMAX ex ante con variables de fase resulta champion: WAPE agrupado de 55,38 %, techo de 67,74 % y desviación de 8,55, frente a 74,30 %, 102,24 % y 22,70 del Committed, reduciendo 412,55 MM USD de error absoluto en el panel histórico y 156,70 MM USD en Q2/2026. CatBoost logra la mejor mediana (53,46 %) pero con techo de 100,17 %, por lo que queda como challenger explicable. Se recomienda una arquitectura champion-challenger con revisión humana, monitoreo de MegaDeals y evolución futura hacia un Forecast Decision Agent prescriptivo.</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>The thesis addresses the sustained decline in birth rates and its relevance for public policy design, with Chile as the application context. Following the CRISP-DM methodology, a predictive model of the birth rate is built from international sociodemographic and economic variables. Data come from World Bank Open Data (1960-2023), structured as a country-year panel with indicators on health, education, employment, economic development and demographic characteristics. After complete-case filtering, the dataset shrank from 14,047 to 923 records, with a larger share of high-income countries (61% of the final sample). Logarithmic transformations were applied to skewed variables, and a country-based split (70% training, 30% test) was used to assess generalization to unseen countries. Multiple linear regression (OLS), Ridge, Random Forest and Gradient Boosting were compared using R², MAE and RMSE. Gradient Boosting performed best, with a test R² of 0.903 and MAE of 0.084, while the linear models reached an R² of 0.839. SHAP analysis identified life expectancy and tertiary education as the factors that most reduce the birth rate, and agricultural employment as the one that most increases it, consistent with demographic transition theory. The tool is proposed as support for evidence-based public policy decisions.</t>
+          <t>This thesis develops and evaluates a weekly, multi-scenario forecasting capability for the commercial pipeline of an information technology corporation focused on B2B technology integration, whose current forecast relies on the qualitative Committed signal recorded in the CRM. Using anonymized won-deal data from January 2023 to June 2026 (183 weeks, aggregated weekly in millions of US dollars), the Committed signal is compared against naive baselines, the AR, MA, ARMA, ARIMA, ARIMAX, SARIMA and SARIMAX progression, the advanced models Prophet, Temporal Fusion Transformer and Chronos-2, and six tabular algorithms explained with SHAP. Evaluation uses eight rolling-origin windows (105 out-of-sample weeks), ex ante reconstructed covariates, error, bias, ceiling and dispersion metrics, and Diebold-Mariano tests with Newey-West and Holm corrections. SARIMAX ex ante with phase variables emerges as champion: pooled WAPE of 55.38%, ceiling of 67.74% and dispersion of 8.55, versus 74.30%, 102.24% and 22.70 for Committed, cutting absolute error by USD 412.55 million over the historical panel and USD 156.70 million in Q2/2026. CatBoost attains the best median (53.46%) but with a 100.17% ceiling, so it remains an explainable challenger. The thesis recommends a champion-challenger architecture with human review, MegaDeal monitoring and future evolution toward a prescriptive Forecast Decision Agent.</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>Se construye un modelo predictivo de la tasa de natalidad con datos de panel del Banco Mundial para múltiples países entre 1960 y 2023.</t>
+          <t>SARIMAX ex ante con fase es el champion: WAPE agrupado de 55,38 %, techo de 67,74 % y desviación de 8,55, muy por debajo del Committed.</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>El filtrado de casos completos redujo la base de 14.047 a 923 registros y elevó la participación de países de ingreso alto a 61 %.</t>
+          <t>La evaluación usa ocho ventanas de origen móvil entre Q2/2024 y Q1/2026, con 105 semanas fuera de muestra y covariables del CRM reconstruidas ex ante.</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>La partición se hizo por país (70 % entrenamiento, 30 % prueba) para evaluar la generalización del modelo a países no observados en el entrenamiento.</t>
+          <t>En el panel histórico SARIMAX reduce 412,55 MM USD de error absoluto frente al Committed (25,46 %) y 156,70 MM USD en Q2/2026 (52,59 %).</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>Gradient Boosting fue el mejor modelo con R² de 0,903 y MAE de 0,084 en prueba, frente a 0,839 de R² en OLS y Ridge.</t>
+          <t>CatBoost obtiene la mejor mediana de WAPE (53,46 %) pero un techo de 100,17 %, por lo que se conserva como challenger explicable con SHAP.</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>El análisis SHAP muestra que la esperanza de vida y la educación terciaria reducen la natalidad, mientras el empleo agrícola la incrementa.</t>
+          <t>El 10 % de las oportunidades concentra 87,3 % de los ingresos y los rezagos de 26 y 13 semanas dominan la importancia SHAP.</t>
         </is>
       </c>
       <c r="AG4" s="2" t="inlineStr">
         <is>
-          <t>A predictive model of the birth rate is built with World Bank panel data covering multiple countries between 1960 and 2023.</t>
+          <t>SARIMAX ex ante with phase is the champion: pooled WAPE of 55.38%, ceiling of 67.74% and dispersion of 8.55, well below Committed.</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>Complete-case filtering reduced the dataset from 14,047 to 923 records, raising the share of high-income countries from 39% to 61%.</t>
+          <t>Evaluation uses eight rolling-origin windows from Q2/2024 to Q1/2026, with 105 out-of-sample weeks and CRM covariates reconstructed ex ante.</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>The split was done by country (70% training, 30% test) to assess the model's generalization to countries not seen during training.</t>
+          <t>Over the historical panel SARIMAX cuts absolute error by USD 412.55 million versus Committed (25.46%) and by USD 156.70 million in Q2/2026 (52.59%).</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>Gradient Boosting was the best model with a test R² of 0.903 and MAE of 0.084, versus an R² of 0.839 for OLS and Ridge.</t>
+          <t>CatBoost achieves the best median WAPE (53.46%) but a 100.17% ceiling, so it is kept as an explainable challenger with SHAP.</t>
         </is>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>SHAP analysis shows that life expectancy and tertiary education reduce the birth rate, while agricultural employment increases it.</t>
+          <t>The top 10% of opportunities concentrate 87.3% of revenue, and 26-week and 13-week lags dominate CatBoost's SHAP importance.</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2026-cabezas.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-celedon.pdf</t>
         </is>
       </c>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>El texto extraído comienza en el capítulo de metodología: no incluye portada, resumen, introducción ni marco teórico. Hay inconsistencia en el período de datos (1998-2023 en la descripción del enfoque, 1960-2023 en resultados). Las tablas y gráficos no están en el texto, por lo que no se dispone de RMSE ni de métricas de Random Forest en prueba.</t>
+          <t>La tesis aplica además AR, MA, ARMA, ARIMA, Random Forest, HistGradientBoosting, Elastic Net, Naive Seasonal, Diebold-Mariano con Newey-West y Holm, Model Confidence Set con bootstrap estacionario y pruebas ADF, KPSS y Ljung-Box; se omitieron de techniques por el límite de 10. La organización no se nombra en el texto. El texto incluye dedicatoria y agradecimientos extensos con nombres personales.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-torres</t>
+          <t>2026-cabezas</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1250,11 +1250,11 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Claudia Alejandra Torres Fritis</t>
+          <t>Cristian Rodrigo Cabezas Lepilla</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -1275,44 +1275,40 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Juan Domingo Velásquez Silva; Richard Weber</t>
-        </is>
-      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Predicción de resultados presidenciales en Chile: un modelo analítico basado en datos electorales de diputados utilizando fastei</t>
+          <t>Tasa de natalidad y política pública: modelos predictivos con datos de panel mundial y machine learning supervisado</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Predicting presidential election results in Chile: an analytical model based on deputy election data using fastei</t>
+          <t>Birth rate and public policy: predictive models with global panel data and supervised machine learning</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>política; sector público</t>
+          <t>sector público; política</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>regresión; clasificación; análisis descriptivo e inferencial</t>
+          <t>regresión; análisis descriptivo e inferencial</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Ecological Inference (EM); OLS Regression; Random Forest; XGBoost; Permutation Importance; ROC / AUC; VIF; Rolling Forward Validation</t>
+          <t>Linear Regression (OLS); Ridge Regression; Random Forest; Gradient Boosting; SHAP; Pearson Correlation; Log Transformation</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>R; fastei; readxl; dplyr; Python; Google Colab; statsmodels; scikit-learn; XGBoost; matplotlib</t>
+          <t>Python; Google Colab</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Votos de diputados por partido y comuna (2001 a 2025) (SERVEL); Votos presidenciales de segunda vuelta por candidato y comuna (2005 a 2025) (SERVEL)</t>
+          <t>Indicadores de desarrollo mundial del Banco Mundial (panel de países, 1960-2023) (World Bank Open Data)</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -1328,100 +1324,100 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>La tesis aborda directamente un problema de política y comportamiento electoral: entrega un pipeline replicable con datos públicos para anticipar resultados presidenciales y entender el voto cruzado y el desgaste del oficialismo.</t>
+          <t>La tesis aborda directamente un problema de política pública: la caída de la natalidad y sus determinantes socioeconómicos, proponiendo el modelo como herramienta para decisiones de política basadas en evidencia.</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>The thesis directly addresses a political and electoral behavior problem: it delivers a replicable pipeline on public data to anticipate presidential results and to understand split-ticket voting and incumbency fatigue.</t>
+          <t>The thesis directly addresses a public policy problem: the decline in birth rates and its socioeconomic determinants, proposing the model as a tool for evidence-based policy decisions.</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>inferencia ecológica; fastei; predicción electoral; segunda vuelta presidencial; Random Forest; XGBoost; Chile</t>
+          <t>tasa de natalidad; política pública; datos de panel; machine learning supervisado; Gradient Boosting; SHAP; transición demográfica</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>ecological inference; fastei; electoral forecasting; presidential runoff; Random Forest; XGBoost; Chile</t>
+          <t>birth rate; public policy; panel data; supervised machine learning; Gradient Boosting; SHAP; demographic transition</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>La tesis evalúa si los resultados de las elecciones de diputados en Chile permiten anticipar el desenlace de la segunda vuelta presidencial. El problema es que, aunque ambas elecciones se realizan el mismo día, el voto cruzado impide agregar directamente los votos por bloque político. Con datos públicos del Servel para seis ciclos electorales (2005 a 2025), se aplica la librería fastei de R, que implementa un algoritmo de inferencia ecológica basado en Esperanza-Maximización, para estimar la probabilidad de que el votante de cada partido apoye a cada candidato presidencial e imputar votos a nivel comunal. Sobre una base de 2.069 observaciones comuna-año se entrenan regresión lineal (OLS), Random Forest y XGBoost para predecir el share del bloque de derecha, incorporando dos variables de contexto: orientación del gobierno saliente y aprobación nacional. La validación se hace con predicción rolling hacia adelante en 2013, 2017, 2021 y 2025. Los tres modelos aciertan al ganador en tres de cuatro elecciones, con error medio de 8 a 10 puntos porcentuales que baja a cerca de 3 puntos en 2025; el AUC de clasificación comunal alcanza 0,974 en Random Forest. Se identifica un efecto de desgaste del oficialismo de derecha cercano a 11 puntos. El pipeline es replicable con solo los votos de diputados por comuna y las dos variables de contexto.</t>
+          <t>La tesis aborda la caída sostenida de la tasa de natalidad y su relevancia para el diseño de políticas públicas, con Chile como contexto de aplicación. Siguiendo CRISP-DM, se construye un modelo predictivo de la tasa de natalidad a partir de variables sociodemográficas y económicas internacionales. Los datos provienen de World Bank Open Data (1960-2023), en formato de panel de países y años, con indicadores de salud, educación, empleo y desarrollo económico. Tras filtrar casos completos, la base pasó de 14.047 a 923 registros, con mayor peso de países de ingreso alto (61 % de la muestra final). Se aplicaron transformaciones logarítmicas a las variables sesgadas y una partición por país (70 % entrenamiento, 30 % prueba) para evaluar la generalización a países no vistos. Se compararon regresión lineal múltiple (OLS), Ridge, Random Forest y Gradient Boosting mediante R², MAE y RMSE. Gradient Boosting obtuvo el mejor desempeño, con R² de 0,903 y MAE de 0,084 en prueba, mientras que los modelos lineales alcanzaron un R² de 0,839. El análisis SHAP identificó la esperanza de vida y la educación terciaria como los factores que más reducen la natalidad, y el empleo agrícola como el que más la eleva, en línea con la teoría de la transición demográfica. La herramienta se propone como apoyo a políticas públicas basadas en evidencia.</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>This thesis assesses whether deputy election results in Chile can anticipate the outcome of the presidential runoff. The problem is that, although both elections are held on the same day, split-ticket voting prevents a direct aggregation of votes by political bloc. Using public SERVEL data for six electoral cycles (2005 to 2025), the fastei R library, which implements an Expectation-Maximization based ecological inference algorithm, is applied to estimate the probability that each party's voter supported each presidential candidate and to impute votes at the municipal level. On a base of 2,069 municipality-year observations, linear regression (OLS), Random Forest and XGBoost are trained to predict the right-wing bloc's vote share, adding two context variables: the outgoing government's orientation and national approval. Validation uses rolling forward prediction for 2013, 2017, 2021 and 2025. All three models correctly pick the winner in three of four elections, with a mean error of 8 to 10 percentage points that falls to about 3 points in 2025; the municipal classification AUC reaches 0.974 for Random Forest. An incumbency fatigue effect for the right of roughly 11 points is identified. The pipeline is replicable with only municipal deputy votes and the two context variables.</t>
+          <t>The thesis addresses the sustained decline in birth rates and its relevance for public policy design, with Chile as the application context. Following the CRISP-DM methodology, a predictive model of the birth rate is built from international sociodemographic and economic variables. Data come from World Bank Open Data (1960-2023), structured as a country-year panel with indicators on health, education, employment, economic development and demographic characteristics. After complete-case filtering, the dataset shrank from 14,047 to 923 records, with a larger share of high-income countries (61% of the final sample). Logarithmic transformations were applied to skewed variables, and a country-based split (70% training, 30% test) was used to assess generalization to unseen countries. Multiple linear regression (OLS), Ridge, Random Forest and Gradient Boosting were compared using R², MAE and RMSE. Gradient Boosting performed best, with a test R² of 0.903 and MAE of 0.084, while the linear models reached an R² of 0.839. SHAP analysis identified life expectancy and tertiary education as the factors that most reduce the birth rate, and agricultural employment as the one that most increases it, consistent with demographic transition theory. The tool is proposed as support for evidence-based public policy decisions.</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>Se construye una base comunal de 2.069 observaciones (seis elecciones, 2005 a 2025) imputando votos presidenciales con inferencia ecológica fastei.</t>
+          <t>Se construye un modelo predictivo de la tasa de natalidad con datos de panel del Banco Mundial para múltiples países entre 1960 y 2023.</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>Los tres modelos (OLS, Random Forest y XGBoost) aciertan al ganador en 3 de 4 elecciones con predicción rolling hacia adelante.</t>
+          <t>El filtrado de casos completos redujo la base de 14.047 a 923 registros y elevó la participación de países de ingreso alto a 61 %.</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>Random Forest alcanza un AUC de 0,974 y XGBoost de 0,917 al clasificar comunas por ganador, frente a 0,694 de la regresión lineal.</t>
+          <t>La partición se hizo por país (70 % entrenamiento, 30 % prueba) para evaluar la generalización del modelo a países no observados en el entrenamiento.</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>El coeficiente de gobierno saliente de derecha es de menos 11 puntos porcentuales, evidencia de desgaste del oficialismo.</t>
+          <t>Gradient Boosting fue el mejor modelo con R² de 0,903 y MAE de 0,084 en prueba, frente a 0,839 de R² en OLS y Ridge.</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
-          <t>El error de predicción nacional cae de 9 a 10 puntos en 2013 a 2021 a cerca de 3 puntos en 2025 al acumular elecciones.</t>
+          <t>El análisis SHAP muestra que la esperanza de vida y la educación terciaria reducen la natalidad, mientras el empleo agrícola la incrementa.</t>
         </is>
       </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>A municipal base of 2,069 observations (six elections, 2005 to 2025) is built by imputing presidential votes with fastei ecological inference.</t>
+          <t>A predictive model of the birth rate is built with World Bank panel data covering multiple countries between 1960 and 2023.</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>All three models (OLS, Random Forest and XGBoost) correctly pick the winner in 3 of 4 elections under rolling forward prediction.</t>
+          <t>Complete-case filtering reduced the dataset from 14,047 to 923 records, raising the share of high-income countries from 39% to 61%.</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>Random Forest reaches an AUC of 0.974 and XGBoost 0.917 when classifying municipalities by winner, versus 0.694 for linear regression.</t>
+          <t>The split was done by country (70% training, 30% test) to assess the model's generalization to countries not seen during training.</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>The coefficient for an outgoing right-wing government is minus 11 percentage points, evidence of incumbency fatigue.</t>
+          <t>Gradient Boosting was the best model with a test R² of 0.903 and MAE of 0.084, versus an R² of 0.839 for OLS and Ridge.</t>
         </is>
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>National prediction error drops from 9 to 10 points in 2013 to 2021 to about 3 points in 2025 as elections accumulate.</t>
+          <t>SHAP analysis shows that life expectancy and tertiary education reduce the birth rate, while agricultural employment increases it.</t>
         </is>
       </c>
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2026-torres.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-cabezas.pdf</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>Las secciones referidas en la discusión (8.2.5, 8.2.6, 8.3.2) no coinciden con la numeración del informe. Hay inconsistencias menores en cifras entre secciones: el coeficiente de pct_diputados aparece como +0,2037 en la tabla OLS y +0,279 en conclusiones; la importancia de XGBoost se cita como 0,45 en conclusiones pero 0,188 por gain en la tabla. Año en portada: 2026.</t>
+          <t>El texto extraído comienza en el capítulo de metodología: no incluye portada, resumen, introducción ni marco teórico. Hay inconsistencia en el período de datos (1998-2023 en la descripción del enfoque, 1960-2023 en resultados). Las tablas y gráficos no están en el texto, por lo que no se dispone de RMSE ni de métricas de Random Forest en prueba.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-gutierrez</t>
+          <t>2026-torres</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1436,11 +1432,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Jorge Andrés Gutiérrez Soto</t>
+          <t>Claudia Alejandra Torres Fritis</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -1449,7 +1445,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -1457,48 +1453,48 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Richard Weber</t>
+          <t>Charles Mark Thraves Cortés-Monroy</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Charles Mark Thraves Cortés-Monroy; Carla Marina Vairetti</t>
+          <t>Juan Domingo Velásquez Silva; Richard Weber</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Pronóstico de demanda de consultas de urgencias respiratorias para la planificación operativa de la red asistencial en la Región de Los Lagos</t>
+          <t>Predicción de resultados presidenciales en Chile: un modelo analítico basado en datos electorales de diputados utilizando fastei</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Forecasting respiratory emergency visit demand for operational planning of the healthcare network in the Los Lagos Region</t>
+          <t>Predicting presidential election results in Chile: an analytical model based on deputy election data using fastei</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>salud; sector público</t>
+          <t>política; sector público</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>series de tiempo / forecasting; regresión; clustering / segmentación</t>
+          <t>regresión; clasificación; análisis descriptivo e inferencial</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>OLS Regression; CatBoost; LSTM; Fourier Terms; Walk-Forward Validation; ACF/PACF; Ljung-Box Test; K-Means</t>
+          <t>Ecological Inference (EM); OLS Regression; Random Forest; XGBoost; Permutation Importance; ROC / AUC; VIF; Rolling Forward Validation</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Python; pandas; NumPy; statsmodels; CatBoost; PyTorch; plotly; joblib</t>
+          <t>R; fastei; readxl; dplyr; Python; Google Colab; statsmodels; scikit-learn; XGBoost; matplotlib</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Consultas de urgencia por causas respiratorias, Región de Los Lagos (DEIS, Ministerio de Salud de Chile (glosa Total Causas Sistema Respiratorio)); Calendario oficial de vacaciones de invierno, Región de Los Lagos (Ministerio de Educación (MINEDUC))</t>
+          <t>Votos de diputados por partido y comuna (2001 a 2025) (SERVEL); Votos presidenciales de segunda vuelta por candidato y comuna (2005 a 2025) (SERVEL)</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1514,100 +1510,100 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>La tesis aborda directamente la planificación de capacidad del sistema público de salud en la Región de Los Lagos, buscando anticipar peaks de urgencias respiratorias para reducir saturación y tiempos de espera de la población usuaria.</t>
+          <t>La tesis aborda directamente un problema de política y comportamiento electoral: entrega un pipeline replicable con datos públicos para anticipar resultados presidenciales y entender el voto cruzado y el desgaste del oficialismo.</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>The thesis directly addresses capacity planning in the public health system of the Los Lagos Region, aiming to anticipate respiratory emergency peaks to reduce saturation and waiting times for the user population.</t>
+          <t>The thesis directly addresses a political and electoral behavior problem: it delivers a replicable pipeline on public data to anticipate presidential results and to understand split-ticket voting and incumbency fatigue.</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>pronóstico de demanda; urgencias respiratorias; series de tiempo; gradient boosting; walk-forward; salud pública; Región de Los Lagos</t>
+          <t>inferencia ecológica; fastei; predicción electoral; segunda vuelta presidencial; Random Forest; XGBoost; Chile</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>demand forecasting; respiratory emergencies; time series; gradient boosting; walk-forward; public health; Los Lagos Region</t>
+          <t>ecological inference; fastei; electoral forecasting; presidential runoff; Random Forest; XGBoost; Chile</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>La red asistencial pública de la Región de Los Lagos (Servicios de Salud Osorno, Reloncaví y Chiloé) enfrenta cada invierno alzas estacionales de urgencias respiratorias que tensionan su capacidad, y la planificación suele basarse en esquemas reactivos o promedios históricos. La tesis evalúa si es posible pronosticar la demanda diaria de consultas de urgencia respiratoria a 30 días con precisión suficiente para apoyar decisiones de dotación, insumos y coordinación de la red. Se utiliza la serie diaria del DEIS (Ministerio de Salud) entre 2015 y 2025, con 4.018 observaciones y una media de 802 consultas diarias, modelando el quiebre del COVID-19 con dummies por tramos. El análisis exploratorio identifica estacionalidad anual e intrasemanal, autocorrelación residual y un efecto calendario móvil por las vacaciones de invierno. Se comparan un baseline estacional, una regresión lineal estructurada (OLS), CatBoost y dos variantes de LSTM bajo walk-forward mensual recursivo sobre 2024 y 2025. CatBoost obtiene el mejor desempeño en las cuatro métricas (R² fuera de muestra de 0,79, MAPE de 11,91 %, MAE de 100 consultas), frente a 19,58 % de MAPE del baseline y 16,25 % del OLS, con un error cercano al 7 % en la primera semana. El trabajo propone un protocolo de alertas tempranas en cuatro niveles y cuantifica de forma ilustrativa el valor de la reducción del error, del orden de 26.400 consultas anuales mejor anticipadas.</t>
+          <t>La tesis evalúa si los resultados de las elecciones de diputados en Chile permiten anticipar el desenlace de la segunda vuelta presidencial. El problema es que, aunque ambas elecciones se realizan el mismo día, el voto cruzado impide agregar directamente los votos por bloque político. Con datos públicos del Servel para seis ciclos electorales (2005 a 2025), se aplica la librería fastei de R, que implementa un algoritmo de inferencia ecológica basado en Esperanza-Maximización, para estimar la probabilidad de que el votante de cada partido apoye a cada candidato presidencial e imputar votos a nivel comunal. Sobre una base de 2.069 observaciones comuna-año se entrenan regresión lineal (OLS), Random Forest y XGBoost para predecir el share del bloque de derecha, incorporando dos variables de contexto: orientación del gobierno saliente y aprobación nacional. La validación se hace con predicción rolling hacia adelante en 2013, 2017, 2021 y 2025. Los tres modelos aciertan al ganador en tres de cuatro elecciones, con error medio de 8 a 10 puntos porcentuales que baja a cerca de 3 puntos en 2025; el AUC de clasificación comunal alcanza 0,974 en Random Forest. Se identifica un efecto de desgaste del oficialismo de derecha cercano a 11 puntos. El pipeline es replicable con solo los votos de diputados por comuna y las dos variables de contexto.</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>The public healthcare network of the Los Lagos Region (Osorno, Reloncaví and Chiloé Health Services) faces seasonal surges in respiratory emergency visits every winter that strain its operational capacity, and planning is usually done with reactive schemes or historical averages. The thesis evaluates whether daily respiratory emergency visit demand can be forecast with a 30-day horizon and sufficient accuracy to support staffing, supply and network coordination decisions. It uses the daily series from DEIS (Ministry of Health) between 2015 and 2025, with 4,018 observations and a mean of 802 daily visits, including the COVID-19 structural break modeled through segment dummies and ramps. The exploratory analysis identifies annual and intra-weekly seasonality, residual temporal dependence and a moving calendar effect associated with winter school holidays. A seasonal baseline, a structured linear regression (OLS), Gradient Boosting (CatBoost) and two LSTM variants are compared under a recursive monthly walk-forward scheme over 2024 and 2025. CatBoost achieves the best performance on all four metrics (out-of-sample R² of 0.79, MAPE of 11.91%, MAE of 100 visits), against a baseline MAPE of 19.58% and 16.25% for OLS, with an error close to 7% in the first week of the horizon. The work proposes a four-level early warning protocol and illustratively quantifies the value of the error reduction, on the order of 26,400 visits per year better anticipated.</t>
+          <t>This thesis assesses whether deputy election results in Chile can anticipate the outcome of the presidential runoff. The problem is that, although both elections are held on the same day, split-ticket voting prevents a direct aggregation of votes by political bloc. Using public SERVEL data for six electoral cycles (2005 to 2025), the fastei R library, which implements an Expectation-Maximization based ecological inference algorithm, is applied to estimate the probability that each party's voter supported each presidential candidate and to impute votes at the municipal level. On a base of 2,069 municipality-year observations, linear regression (OLS), Random Forest and XGBoost are trained to predict the right-wing bloc's vote share, adding two context variables: the outgoing government's orientation and national approval. Validation uses rolling forward prediction for 2013, 2017, 2021 and 2025. All three models correctly pick the winner in three of four elections, with a mean error of 8 to 10 percentage points that falls to about 3 points in 2025; the municipal classification AUC reaches 0.974 for Random Forest. An incumbency fatigue effect for the right of roughly 11 points is identified. The pipeline is replicable with only municipal deputy votes and the two context variables.</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>CatBoost alcanza un R² fuera de muestra de 0,79 y un MAPE de 11,91 % en 24 meses de walk-forward mensual (2024 y 2025).</t>
+          <t>Se construye una base comunal de 2.069 observaciones (seis elecciones, 2005 a 2025) imputando votos presidenciales con inferencia ecológica fastei.</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>La serie DEIS cubre 4.018 días entre 2015 y 2025, con media de 802 consultas diarias y peaks invernales superiores a 2.500 consultas.</t>
+          <t>Los tres modelos (OLS, Random Forest y XGBoost) aciertan al ganador en 3 de 4 elecciones con predicción rolling hacia adelante.</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>El baseline por semana epidemiológica obtiene MAPE de 19,58 % y el OLS 16,25 %; CatBoost reduce el MAE en 42 % frente al baseline.</t>
+          <t>Random Forest alcanza un AUC de 0,974 y XGBoost de 0,917 al clasificar comunas por ganador, frente a 0,694 de la regresión lineal.</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>La LSTM, con las mismas 163 variables que CatBoost, obtiene un R² de 0,62 y queda por debajo incluso del modelo lineal.</t>
+          <t>El coeficiente de gobierno saliente de derecha es de menos 11 puntos porcentuales, evidencia de desgaste del oficialismo.</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
         <is>
-          <t>El MAPE de CatBoost sube de 7,19 % en t+1 a 20 % en t+30; se propone un protocolo de alertas tempranas en cuatro niveles.</t>
+          <t>El error de predicción nacional cae de 9 a 10 puntos en 2013 a 2021 a cerca de 3 puntos en 2025 al acumular elecciones.</t>
         </is>
       </c>
       <c r="AG6" s="2" t="inlineStr">
         <is>
-          <t>CatBoost reaches an out-of-sample R² of 0.79 and a MAPE of 11.91% over 24 months of monthly walk-forward validation (2024 and 2025).</t>
+          <t>A municipal base of 2,069 observations (six elections, 2005 to 2025) is built by imputing presidential votes with fastei ecological inference.</t>
         </is>
       </c>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>The DEIS series covers 4,018 days between 2015 and 2025, with a mean of 802 daily visits and winter peaks above 2,500 visits.</t>
+          <t>All three models (OLS, Random Forest and XGBoost) correctly pick the winner in 3 of 4 elections under rolling forward prediction.</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>The epidemiological-week baseline yields a MAPE of 19.58% and OLS 16.25%, so CatBoost cuts MAE by 42% relative to the baseline.</t>
+          <t>Random Forest reaches an AUC of 0.974 and XGBoost 0.917 when classifying municipalities by winner, versus 0.694 for linear regression.</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>The LSTM, fed the same 163 variables as CatBoost, obtains an R² of 0.62 and falls below even the linear model.</t>
+          <t>The coefficient for an outgoing right-wing government is minus 11 percentage points, evidence of incumbency fatigue.</t>
         </is>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>CatBoost's MAPE rises from 7.19% at t+1 to 20% at t+30, and a four-level early warning protocol is proposed.</t>
+          <t>National prediction error drops from 9 to 10 points in 2013 to 2021 to about 3 points in 2025 as elections accumulate.</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2026-gutierrez.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-torres.pdf</t>
         </is>
       </c>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>Trabajo orientado a los Servicios de Salud Reloncaví, Chiloé y Osorno como contraparte institucional, pero los datos usados son públicos (DEIS) y no se declara convenio formal, por lo que organization se deja en null. La valorización económica (396 a 793 millones de pesos anuales) es un ejercicio ilustrativo, no un resultado del modelo. Fecha de la portada: junio 2026; profesor guía Richard Weber.</t>
+          <t>Las secciones referidas en la discusión (8.2.5, 8.2.6, 8.3.2) no coinciden con la numeración del informe. Hay inconsistencias menores en cifras entre secciones: el coeficiente de pct_diputados aparece como +0,2037 en la tabla OLS y +0,279 en conclusiones; la importancia de XGBoost se cita como 0,45 en conclusiones pero 0,188 por gain en la tabla. Año en portada: 2026.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-delrio</t>
+          <t>2026-gutierrez</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1622,11 +1618,11 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Felipe Andrés del Río Nova</t>
+          <t>Jorge Andrés Gutiérrez Soto</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -1643,48 +1639,48 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Charles Mark Thraves Cortés-Monroy</t>
+          <t>Richard Weber</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Carla Marina Vairetti; Richard Weber</t>
+          <t>Charles Mark Thraves Cortés-Monroy; Carla Marina Vairetti</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Predicción de elección presidencial a partir de resultados de elecciones municipales</t>
+          <t>Pronóstico de demanda de consultas de urgencias respiratorias para la planificación operativa de la red asistencial en la Región de Los Lagos</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Predicting presidential election outcomes from municipal election results</t>
+          <t>Forecasting respiratory emergency visit demand for operational planning of the healthcare network in the Los Lagos Region</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>política; sector público</t>
+          <t>salud; sector público</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>regresión; reducción de dimensionalidad; optimización</t>
+          <t>series de tiempo / forecasting; regresión; clustering / segmentación</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Partial Least Squares; Principal Component Regression; Ecological Inference (RxC model); Expectation-Maximization; LAD Regression with Cardinality Constraint (MILP); Leave-One-Out Cross-Validation</t>
+          <t>OLS Regression; CatBoost; LSTM; Fourier Terms; Walk-Forward Validation; ACF/PACF; Ljung-Box Test; K-Means</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Python; Pyomo; CBC (COIN-OR); R; FASTEI</t>
+          <t>Python; pandas; NumPy; statsmodels; CatBoost; PyTorch; plotly; joblib</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Resultados oficiales de elecciones municipales y presidenciales de Chile por comuna (Servicio Electoral de Chile (SERVEL))</t>
+          <t>Consultas de urgencia por causas respiratorias, Región de Los Lagos (DEIS, Ministerio de Salud de Chile (glosa Total Causas Sistema Respiratorio)); Calendario oficial de vacaciones de invierno, Región de Los Lagos (Ministerio de Educación (MINEDUC))</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1700,100 +1696,100 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>La tesis aborda un problema de política y decisión pública: anticipar resultados presidenciales con datos electorales oficiales y abiertos, ofreciendo una alternativa reproducible a las encuestas de opinión para organizaciones políticas, instituciones públicas y analistas.</t>
+          <t>La tesis aborda directamente la planificación de capacidad del sistema público de salud en la Región de Los Lagos, buscando anticipar peaks de urgencias respiratorias para reducir saturación y tiempos de espera de la población usuaria.</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>The thesis addresses a public policy and political decision problem: anticipating presidential outcomes from official open electoral data, offering a reproducible alternative to opinion polls for political organizations, public institutions and analysts.</t>
+          <t>The thesis directly addresses capacity planning in the public health system of the Los Lagos Region, aiming to anticipate respiratory emergency peaks to reduce saturation and waiting times for the user population.</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>predicción electoral; inferencia ecológica; alta dimensionalidad; mínimos cuadrados parciales; regresión por componentes principales; selección de variables; SERVEL</t>
+          <t>pronóstico de demanda; urgencias respiratorias; series de tiempo; gradient boosting; walk-forward; salud pública; Región de Los Lagos</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>election forecasting; ecological inference; high dimensionality; partial least squares; principal component regression; variable selection; SERVEL</t>
+          <t>demand forecasting; respiratory emergencies; time series; gradient boosting; walk-forward; public health; Los Lagos Region</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>La tesis evalúa si los resultados de elecciones municipales en Chile contienen información suficiente para anticipar la segunda vuelta presidencial, como alternativa a las encuestas de opinión, cuya precisión ha sido cuestionada. Se construyó una base longitudinal a partir de registros oficiales del SERVEL, estandarizada a 346 comunas y seis ciclos electorales (2005 a 2025), lo que configura un problema de alta dimensionalidad con solo ocho observaciones de entrenamiento. Los votos municipales por partido se vincularon a candidaturas presidenciales mediante dos modalidades: una asignación manual experta y una inferencia ecológica con el modelo RxC implementado en la librería FASTEI de R. Sobre cada matriz se aplicaron tres modelos: Partial Least Squares, Principal Component Regression y un modelo de selección de comunas con restricción de cardinalidad (Beta=0), formulado como MILP y resuelto con CBC desde Pyomo. La validación fue temporal: ciclos históricos para entrenar, 2021 para validar y 2025 como prueba. Cinco de seis configuraciones anticiparon el triunfo de la oposición en 2025, y PLS con inferencia ecológica obtuvo el menor error, de 1,24 puntos porcentuales. La asignación ecológica superó a la manual en todos los modelos. Los hallazgos son preliminares por el reducido número de observaciones, el sobreajuste detectado y el carácter retrospectivo de la evaluación.</t>
+          <t>La red asistencial pública de la Región de Los Lagos (Servicios de Salud Osorno, Reloncaví y Chiloé) enfrenta cada invierno alzas estacionales de urgencias respiratorias que tensionan su capacidad, y la planificación suele basarse en esquemas reactivos o promedios históricos. La tesis evalúa si es posible pronosticar la demanda diaria de consultas de urgencia respiratoria a 30 días con precisión suficiente para apoyar decisiones de dotación, insumos y coordinación de la red. Se utiliza la serie diaria del DEIS (Ministerio de Salud) entre 2015 y 2025, con 4.018 observaciones y una media de 802 consultas diarias, modelando el quiebre del COVID-19 con dummies por tramos. El análisis exploratorio identifica estacionalidad anual e intrasemanal, autocorrelación residual y un efecto calendario móvil por las vacaciones de invierno. Se comparan un baseline estacional, una regresión lineal estructurada (OLS), CatBoost y dos variantes de LSTM bajo walk-forward mensual recursivo sobre 2024 y 2025. CatBoost obtiene el mejor desempeño en las cuatro métricas (R² fuera de muestra de 0,79, MAPE de 11,91 %, MAE de 100 consultas), frente a 19,58 % de MAPE del baseline y 16,25 % del OLS, con un error cercano al 7 % en la primera semana. El trabajo propone un protocolo de alertas tempranas en cuatro niveles y cuantifica de forma ilustrativa el valor de la reducción del error, del orden de 26.400 consultas anuales mejor anticipadas.</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>This thesis evaluates whether Chilean municipal election results contain enough information to anticipate the presidential runoff, as an alternative to opinion polls whose accuracy has been questioned. A longitudinal database was built from official SERVEL records, standardized to 346 municipalities and six electoral cycles (2005 to 2025), which yields a high-dimensional problem with only eight training observations. Municipal votes by party were linked to presidential candidacies through two allocation schemes: a manual expert assignment and ecological inference using the RxC model implemented in the FASTEI library for R. On each resulting matrix, three models were applied: Partial Least Squares, Principal Component Regression, and a municipality selection model with a cardinality constraint (Beta=0), formulated as a MILP and solved with CBC through Pyomo. Validation followed a temporal split: historical cycles for training, 2021 for validation and 2025 as the test set. Five of six configurations correctly anticipated the opposition victory in 2025, and PLS with ecological inference achieved the lowest error, 1.24 percentage points. Ecological allocation outperformed manual allocation across all models. The findings are preliminary given the small number of observations, the overfitting detected and the retrospective nature of the evaluation.</t>
+          <t>The public healthcare network of the Los Lagos Region (Osorno, Reloncaví and Chiloé Health Services) faces seasonal surges in respiratory emergency visits every winter that strain its operational capacity, and planning is usually done with reactive schemes or historical averages. The thesis evaluates whether daily respiratory emergency visit demand can be forecast with a 30-day horizon and sufficient accuracy to support staffing, supply and network coordination decisions. It uses the daily series from DEIS (Ministry of Health) between 2015 and 2025, with 4,018 observations and a mean of 802 daily visits, including the COVID-19 structural break modeled through segment dummies and ramps. The exploratory analysis identifies annual and intra-weekly seasonality, residual temporal dependence and a moving calendar effect associated with winter school holidays. A seasonal baseline, a structured linear regression (OLS), Gradient Boosting (CatBoost) and two LSTM variants are compared under a recursive monthly walk-forward scheme over 2024 and 2025. CatBoost achieves the best performance on all four metrics (out-of-sample R² of 0.79, MAPE of 11.91%, MAE of 100 visits), against a baseline MAPE of 19.58% and 16.25% for OLS, with an error close to 7% in the first week of the horizon. The work proposes a four-level early warning protocol and illustratively quantifies the value of the error reduction, on the order of 26,400 visits per year better anticipated.</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>Se construyó una base longitudinal de 346 comunas y seis ciclos electorales a partir de registros oficiales del SERVEL, con 12 observaciones totales.</t>
+          <t>CatBoost alcanza un R² fuera de muestra de 0,79 y un MAPE de 11,91 % en 24 meses de walk-forward mensual (2024 y 2025).</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>Se compararon dos modalidades de asignación de votos: manual experta e inferencia ecológica RxC con la librería FASTEI de R.</t>
+          <t>La serie DEIS cubre 4.018 días entre 2015 y 2025, con media de 802 consultas diarias y peaks invernales superiores a 2.500 consultas.</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>Se aplicaron PLS, PCR y un modelo MILP de selección de tres comunas (Beta=0) con partición temporal: validación 2021 y prueba 2025.</t>
+          <t>El baseline por semana epidemiológica obtiene MAPE de 19,58 % y el OLS 16,25 %; CatBoost reduce el MAE en 42 % frente al baseline.</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>Cinco de seis configuraciones anticiparon el triunfo de la oposición en 2025; PLS con FASTEI logró el menor error, de 1,24 puntos porcentuales.</t>
+          <t>La LSTM, con las mismas 163 variables que CatBoost, obtiene un R² de 0,62 y queda por debajo incluso del modelo lineal.</t>
         </is>
       </c>
       <c r="AF7" s="2" t="inlineStr">
         <is>
-          <t>La inferencia ecológica superó a la asignación manual en los tres modelos, con brechas de validación de 3,8, 5,1 y 2,5 puntos porcentuales.</t>
+          <t>El MAPE de CatBoost sube de 7,19 % en t+1 a 20 % en t+30; se propone un protocolo de alertas tempranas en cuatro niveles.</t>
         </is>
       </c>
       <c r="AG7" s="2" t="inlineStr">
         <is>
-          <t>A longitudinal database of 346 municipalities and six electoral cycles was built from official SERVEL records, with 12 observations in total.</t>
+          <t>CatBoost reaches an out-of-sample R² of 0.79 and a MAPE of 11.91% over 24 months of monthly walk-forward validation (2024 and 2025).</t>
         </is>
       </c>
       <c r="AH7" s="2" t="inlineStr">
         <is>
-          <t>Two vote allocation schemes were compared: manual expert assignment and RxC ecological inference using the FASTEI library for R.</t>
+          <t>The DEIS series covers 4,018 days between 2015 and 2025, with a mean of 802 daily visits and winter peaks above 2,500 visits.</t>
         </is>
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>PLS, PCR and a MILP model selecting three municipalities (Beta=0) were applied with a temporal split: validation on 2021 and test on 2025.</t>
+          <t>The epidemiological-week baseline yields a MAPE of 19.58% and OLS 16.25%, so CatBoost cuts MAE by 42% relative to the baseline.</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>Five of six configurations anticipated the opposition victory in 2025; PLS with FASTEI achieved the lowest error, 1.24 percentage points.</t>
+          <t>The LSTM, fed the same 163 variables as CatBoost, obtains an R² of 0.62 and falls below even the linear model.</t>
         </is>
       </c>
       <c r="AK7" s="2" t="inlineStr">
         <is>
-          <t>Ecological inference outperformed manual allocation across the three models, with validation gaps of 3.8, 5.1 and 2.5 percentage points.</t>
+          <t>CatBoost's MAPE rises from 7.19% at t+1 to 20% at t+30, and a four-level early warning protocol is proposed.</t>
         </is>
       </c>
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2026-delrio.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-gutierrez.pdf</t>
         </is>
       </c>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>Tesis fechada 2026 (Actividad Formativa Equivalente), profesor guía Charles Thraves. Las predicciones sobre 2025 son retrospectivas: el resultado ya era conocido y la asignación manual de ese ciclo se ajustó al resultado observado (sesgo retrospectivo declarado por el autor). El modelo Beta=0 no alcanza optimalidad certificada en CBC y no es replicable entre corridas. Los anexos del texto solo contienen nombres de figuras, sin contenido.</t>
+          <t>Trabajo orientado a los Servicios de Salud Reloncaví, Chiloé y Osorno como contraparte institucional, pero los datos usados son públicos (DEIS) y no se declara convenio formal, por lo que organization se deja en null. La valorización económica (396 a 793 millones de pesos anuales) es un ejercicio ilustrativo, no un resultado del modelo. Fecha de la portada: junio 2026; profesor guía Richard Weber.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-hernandez</t>
+          <t>2026-delrio</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1808,11 +1804,11 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Cristian Luis Hernández Milla</t>
+          <t>Felipe Andrés del Río Nova</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -1821,7 +1817,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -1829,48 +1825,48 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Richard Weber</t>
+          <t>Charles Mark Thraves Cortés-Monroy</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Ariel Isaac La Paz Lillo; Juan Domingo Velásquez Silva</t>
+          <t>Carla Marina Vairetti; Richard Weber</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Datos públicos como catalizador de la industria: el caso de los datos catastrales del Servicio de Impuestos Internos en Chile</t>
+          <t>Predicción de elección presidencial a partir de resultados de elecciones municipales</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Public data as an industry catalyst: the case of the cadastral data of Chile's Internal Revenue Service</t>
+          <t>Predicting presidential election outcomes from municipal election results</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>sector público; finanzas</t>
+          <t>política; sector público</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>análisis descriptivo e inferencial; optimización</t>
+          <t>regresión; reducción de dimensionalidad; optimización</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Web Scraping; API Harvesting; Raster Polygonization (GDAL); Compactness Index (Isoperimetric Quotient); Spatial Join (Point-in-Polygon); Nearest-Polygon Matching; Haversine Distance; BPR Traffic Model; CLIP ViT-B/32; Weighted Scoring Model</t>
+          <t>Partial Least Squares; Principal Component Regression; Ecological Inference (RxC model); Expectation-Maximization; LAD Regression with Cardinality Constraint (MILP); Leave-One-Out Cross-Validation</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Python 3.11; GDAL 3.8; GeoPandas 0.14; Rasterio 1.3; Shapely; boto3; WireGuard (Mullvad); Linux network namespaces; Hetzner Object Storage (S3); PostgreSQL 16; PostGIS 3.5; FastAPI; Uvicorn; Nginx; Cloudflare; React 19; Vite 7; Leaflet; Recharts; Docker; ijson; QGIS; Google Routes API; OpenStreetMap; HERE Maps</t>
+          <t>Python; Pyomo; CBC (COIN-OR); R; FASTEI</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>Rol Semestral de Contribuciones de Bienes Raíces (archivo BRTMPNACROL) (Servicio de Impuestos Internos (SII), Chile); API getPredioNacional del SII (Servicio de Impuestos Internos (SII), Chile); Servicio WMS de cartografía catastral del SII (Servicio de Impuestos Internos (SII), Chile); Dataset predial nacional consolidado (producto de la tesis) (Catastral.cl)</t>
+          <t>Resultados oficiales de elecciones municipales y presidenciales de Chile por comuna (Servicio Electoral de Chile (SERVEL))</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1886,100 +1882,100 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>La tesis aborda directamente un problema de acceso a información pública: libera datos catastrales formalmente públicos pero inaccesibles y los distribuye gratis a investigadores, municipios, periodistas y ciudadanos, reduciendo la asimetría de información en el mercado inmobiliario.</t>
+          <t>La tesis aborda un problema de política y decisión pública: anticipar resultados presidenciales con datos electorales oficiales y abiertos, ofreciendo una alternativa reproducible a las encuestas de opinión para organizaciones políticas, instituciones públicas y analistas.</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>The thesis directly addresses a public-information access problem: it unlocks cadastral data that are formally public but inaccessible and distributes them free of charge to researchers, municipalities, journalists and citizens, reducing information asymmetry in the real estate market.</t>
+          <t>The thesis addresses a public policy and political decision problem: anticipating presidential outcomes from official open electoral data, offering a reproducible alternative to opinion polls for political organizations, public institutions and analysts.</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>datos abiertos; datos catastrales; web scraping; vectorización raster; ingeniería de datos geoespaciales; SII Chile; mercado inmobiliario</t>
+          <t>predicción electoral; inferencia ecológica; alta dimensionalidad; mínimos cuadrados parciales; regresión por componentes principales; selección de variables; SERVEL</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>open data; cadastral data; web scraping; raster vectorization; geospatial data engineering; SII Chile; real estate market</t>
+          <t>election forecasting; ecological inference; high dimensionality; partial least squares; principal component regression; variable selection; SERVEL</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>El SII de Chile administra unos 9,5 millones de predios con avalúos, superficies, destinos y geometrías, datos públicos por ley pero inutilizables para análisis masivo por tres barreras técnicas: un archivo de ancho fijo de 3 GB, una API de consulta unitaria con bloqueo de IPs y un servicio WMS que entrega los polígonos solo como imágenes PNG. La tesis implementa un pipeline de ingeniería de datos geoespaciales que supera las tres barreras: parseo del archivo heredado, extracción distribuida con 30 túneles WireGuard, descarga de tiles WMS a zoom 19, polygonización raster con GDAL, filtrado por valor DN y compactness, y spatial join con GeoPandas mediante el concepto de rol base. El resultado es un dataset nacional de 9,55 millones de predios en las 343 comunas, 5,67 millones de ellos (60,3 %) con polígono vectorial de unos 30 cm de resolución, más 16 semestres de series históricas de avalúo. Una validación en Lebu (n = 1.396) muestra un error mediano de 0,4 m entre coordenada oficial y centroide. El dataset se distribuye en la plataforma Catastral.cl (FastAPI, PostGIS, React) bajo un modelo de pago social y sirve de capa base a un sistema de localización de estaciones de servicio. Se concluye que las barreras son técnicas, no legales, y que la inaccesibilidad cuesta más de 2 millones de USD anuales.</t>
+          <t>La tesis evalúa si los resultados de elecciones municipales en Chile contienen información suficiente para anticipar la segunda vuelta presidencial, como alternativa a las encuestas de opinión, cuya precisión ha sido cuestionada. Se construyó una base longitudinal a partir de registros oficiales del SERVEL, estandarizada a 346 comunas y seis ciclos electorales (2005 a 2025), lo que configura un problema de alta dimensionalidad con solo ocho observaciones de entrenamiento. Los votos municipales por partido se vincularon a candidaturas presidenciales mediante dos modalidades: una asignación manual experta y una inferencia ecológica con el modelo RxC implementado en la librería FASTEI de R. Sobre cada matriz se aplicaron tres modelos: Partial Least Squares, Principal Component Regression y un modelo de selección de comunas con restricción de cardinalidad (Beta=0), formulado como MILP y resuelto con CBC desde Pyomo. La validación fue temporal: ciclos históricos para entrenar, 2021 para validar y 2025 como prueba. Cinco de seis configuraciones anticiparon el triunfo de la oposición en 2025, y PLS con inferencia ecológica obtuvo el menor error, de 1,24 puntos porcentuales. La asignación ecológica superó a la manual en todos los modelos. Los hallazgos son preliminares por el reducido número de observaciones, el sobreajuste detectado y el carácter retrospectivo de la evaluación.</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>Chile's Internal Revenue Service (SII) administers about 9.5 million properties with appraisals, areas, land uses and geometries, data that are formally public under Law 20,285 but unusable for large-scale analysis because of three technical barriers: a 3 GB fixed-width file, a single-property API with IP blocking, and a WMS service that delivers parcel polygons only as PNG images. The thesis implements a geospatial data engineering pipeline that overcomes all three barriers: parsing of the legacy file, distributed extraction through 30 WireGuard tunnels, download of WMS tiles at zoom 19, raster polygonization with GDAL, filtering by DN value and compactness, and a GeoPandas spatial join based on the base-roll concept. The result is a national dataset of 9.55 million properties across all 343 municipalities, 5.67 million of them (60.3%) with a vector polygon at roughly 30 cm resolution, plus 16 semesters of appraisal history. A validation in Lebu (n = 1,396) shows a median error of 0.4 m between the official coordinate and the polygon centroid. The dataset is distributed through the Catastral.cl platform (FastAPI, PostGIS, React) under a social-payment model and serves as the base layer for a fuel-station site-selection system. The thesis concludes that the barriers are technical rather than legal, and that inaccessibility costs over USD 2 million per year.</t>
+          <t>This thesis evaluates whether Chilean municipal election results contain enough information to anticipate the presidential runoff, as an alternative to opinion polls whose accuracy has been questioned. A longitudinal database was built from official SERVEL records, standardized to 346 municipalities and six electoral cycles (2005 to 2025), which yields a high-dimensional problem with only eight training observations. Municipal votes by party were linked to presidential candidacies through two allocation schemes: a manual expert assignment and ecological inference using the RxC model implemented in the FASTEI library for R. On each resulting matrix, three models were applied: Partial Least Squares, Principal Component Regression, and a municipality selection model with a cardinality constraint (Beta=0), formulated as a MILP and solved with CBC through Pyomo. Validation followed a temporal split: historical cycles for training, 2021 for validation and 2025 as the test set. Five of six configurations correctly anticipated the opposition victory in 2025, and PLS with ecological inference achieved the lowest error, 1.24 percentage points. Ecological allocation outperformed manual allocation across all models. The findings are preliminary given the small number of observations, the overfitting detected and the retrospective nature of the evaluation.</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>El pipeline extrajo 9,55 millones de predios de las 343 comunas de Chile en unas 76 horas usando 30 túneles WireGuard con rotación de IP.</t>
+          <t>Se construyó una base longitudinal de 346 comunas y seis ciclos electorales a partir de registros oficiales del SERVEL, con 12 observaciones totales.</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>La vectorización raster con GDAL produjo polígonos de unos 30 cm de resolución para 5,67 millones de predios, el 60,3 % del catastro nacional.</t>
+          <t>Se compararon dos modalidades de asignación de votos: manual experta e inferencia ecológica RxC con la librería FASTEI de R.</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>En 1.396 predios de Lebu, el error mediano entre coordenada oficial y centroide fue de 0,4 m, y el 95,6 % quedó bajo 20 m.</t>
+          <t>Se aplicaron PLS, PCR y un modelo MILP de selección de tres comunas (Beta=0) con partición temporal: validación 2021 y prueba 2025.</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t>Catastral.cl sirve 9,4 millones de predios y 136 millones de filas históricas con PostGIS, FastAPI y React bajo un modelo de pago social.</t>
+          <t>Cinco de seis configuraciones anticiparon el triunfo de la oposición en 2025; PLS con FASTEI logró el menor error, de 1,24 puntos porcentuales.</t>
         </is>
       </c>
       <c r="AF8" s="2" t="inlineStr">
         <is>
-          <t>La inaccesibilidad del dato catastral cuesta más de 2 millones de USD anuales, pagados a intermediarios que cobran entre 2.000 y 6.000 USD por comuna.</t>
+          <t>La inferencia ecológica superó a la asignación manual en los tres modelos, con brechas de validación de 3,8, 5,1 y 2,5 puntos porcentuales.</t>
         </is>
       </c>
       <c r="AG8" s="2" t="inlineStr">
         <is>
-          <t>The pipeline extracted 9.55 million properties from all 343 Chilean municipalities in about 76 hours using 30 WireGuard tunnels with IP rotation.</t>
+          <t>A longitudinal database of 346 municipalities and six electoral cycles was built from official SERVEL records, with 12 observations in total.</t>
         </is>
       </c>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>Raster vectorization with GDAL produced polygons at roughly 30 cm resolution for 5.67 million properties, 60.3% of the national cadastre.</t>
+          <t>Two vote allocation schemes were compared: manual expert assignment and RxC ecological inference using the FASTEI library for R.</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>Across 1,396 properties in Lebu, the median error between official coordinate and polygon centroid was 0.4 m, with 95.6% under 20 m.</t>
+          <t>PLS, PCR and a MILP model selecting three municipalities (Beta=0) were applied with a temporal split: validation on 2021 and test on 2025.</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>Catastral.cl serves 9.4 million properties and 136 million historical rows with PostGIS, FastAPI and React under a social-payment model.</t>
+          <t>Five of six configurations anticipated the opposition victory in 2025; PLS with FASTEI achieved the lowest error, 1.24 percentage points.</t>
         </is>
       </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>Cadastral data inaccessibility costs over USD 2 million per year, paid to intermediaries charging USD 2,000 to 6,000 per municipality.</t>
+          <t>Ecological inference outperformed manual allocation across the three models, with validation gaps of 3.8, 5.1 and 2.5 percentage points.</t>
         </is>
       </c>
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2026-hernandez.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-delrio.pdf</t>
         </is>
       </c>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>La portada indica 'Borrador Final' (abril 2026). Es una tesis de ingeniería de datos geoespaciales y producto (plataformas Catastral.cl y combustible.tremen.tech), no de modelamiento predictivo: no se entrenan modelos de ML; CLIP se usa como clasificador satelital preentrenado en el caso aplicado. El texto menciona Newmark Chile 'en el Capítulo 1' pero ese contexto no aparece en el documento. Algunas referencias cruzadas de sección son inconsistentes (p.ej. 'Sección 4.2.2' por 7.4.2).</t>
+          <t>Tesis fechada 2026 (Actividad Formativa Equivalente), profesor guía Charles Thraves. Las predicciones sobre 2025 son retrospectivas: el resultado ya era conocido y la asignación manual de ese ciclo se ajustó al resultado observado (sesgo retrospectivo declarado por el autor). El modelo Beta=0 no alcanza optimalidad certificada en CBC y no es replicable entre corridas. Los anexos del texto solo contienen nombres de figuras, sin contenido.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2025-canete</t>
+          <t>2026-hernandez</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1994,7 +1990,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Nicolás Alejandro Cañete Ponce</t>
+          <t>Cristian Luis Hernández Milla</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -2007,169 +2003,165 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Jaime Andrés Miranda Pino</t>
+          <t>Richard Weber</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Richard Weber; Sebastián Alejandro Maldonado Alarcón</t>
+          <t>Ariel Isaac La Paz Lillo; Juan Domingo Velásquez Silva</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Retención de talento con People Analytics: un enfoque basado en Machine Learning y Uplift Modeling</t>
+          <t>Datos públicos como catalizador de la industria: el caso de los datos catastrales del Servicio de Impuestos Internos en Chile</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Talent retention with People Analytics: an approach based on Machine Learning and Uplift Modeling</t>
+          <t>Public data as an industry catalyst: the case of the cadastral data of Chile's Internal Revenue Service</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>recursos humanos; transporte</t>
+          <t>sector público; finanzas</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>clasificación; uplift / causal</t>
+          <t>análisis descriptivo e inferencial; optimización</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>LightGBM; XGBoost; Gradient Boosting; CatBoost; Random Forest; Logistic Regression; Decision Tree; T-Learner; SMOTE; Feature Importance</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Web Scraping; API Harvesting; Raster Polygonization (GDAL); Compactness Index (Isoperimetric Quotient); Spatial Join (Point-in-Polygon); Nearest-Polygon Matching; Haversine Distance; BPR Traffic Model; CLIP ViT-B/32; Weighted Scoring Model</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Python 3.11; GDAL 3.8; GeoPandas 0.14; Rasterio 1.3; Shapely; boto3; WireGuard (Mullvad); Linux network namespaces; Hetzner Object Storage (S3); PostgreSQL 16; PostGIS 3.5; FastAPI; Uvicorn; Nginx; Cloudflare; React 19; Vite 7; Leaflet; Recharts; Docker; ijson; QGIS; Google Routes API; OpenStreetMap; HERE Maps</t>
+        </is>
+      </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Dotación histórica de trabajadores (datos internos de una empresa de transporte (subsistemas de Recursos Humanos)); Evaluaciones de desempeño (datos internos de una empresa de transporte (subsistemas de Recursos Humanos)); Ausentismos (licencias y vacaciones) (datos internos de una empresa de transporte (subsistemas de Recursos Humanos)); Compensaciones (incrementos de renta y retenciones) (datos internos de una empresa de transporte (subsistemas de Recursos Humanos))</t>
+          <t>Rol Semestral de Contribuciones de Bienes Raíces (archivo BRTMPNACROL) (Servicio de Impuestos Internos (SII), Chile); API getPredioNacional del SII (Servicio de Impuestos Internos (SII), Chile); Servicio WMS de cartografía catastral del SII (Servicio de Impuestos Internos (SII), Chile); Dataset predial nacional consolidado (producto de la tesis) (Catastral.cl)</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>Empresa de transporte chilena (no identificada por nombre en el texto)</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>indirect</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>La aplicación es interna a una empresa, orientada a eficiencia en la gestión de personas, pero genera beneficio derivado para los trabajadores al focalizar intervenciones de retención y evitar acciones ineficaces o contraproducentes.</t>
+          <t>La tesis aborda directamente un problema de acceso a información pública: libera datos catastrales formalmente públicos pero inaccesibles y los distribuye gratis a investigadores, municipios, periodistas y ciudadanos, reduciendo la asimetría de información en el mercado inmobiliario.</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>The application is internal to a company and aimed at HR management efficiency, but it yields a derived benefit for employees by targeting retention interventions and avoiding ineffective or counterproductive actions.</t>
+          <t>The thesis directly addresses a public-information access problem: it unlocks cadastral data that are formally public but inaccessible and distributes them free of charge to researchers, municipalities, journalists and citizens, reducing information asymmetry in the real estate market.</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>people analytics; fuga de talento; uplift modeling; inferencia causal; gradient boosting; recursos humanos; KDD</t>
+          <t>datos abiertos; datos catastrales; web scraping; vectorización raster; ingeniería de datos geoespaciales; SII Chile; mercado inmobiliario</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>people analytics; employee turnover; uplift modeling; causal inference; gradient boosting; human resources; KDD</t>
+          <t>open data; cadastral data; web scraping; raster vectorization; geospatial data engineering; SII Chile; real estate market</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>La fuga voluntaria de talento es costosa (el reemplazo de un profesional calificado puede alcanzar hasta el 200 % de su salario anual) y las estrategias de retención genéricas desperdician recursos en trabajadores que no responden a ellas. Esta AFE desarrolla, siguiendo la metodología KDD, un marco que combina modelos predictivos de renuncia con Uplift Modeling para identificar a los trabajadores persuasibles de una empresa de transporte chilena. Se integran cuatro subsistemas de Recursos Humanos (dotación histórica 2022-2024 de 5.636 trabajadores, evaluaciones de desempeño, ausentismos y compensaciones) y, tras acotar el análisis a los estamentos Profesionales y Jefes, se obtiene una base de 1.056 observaciones con 13 % de renuncias. Con validación cruzada estratificada de 5 folds, SMOTE, reducción de cardinalidad por tasa de renuncia y one-hot encoding dentro de cada fold, se comparan siete clasificadores. Los modelos de Gradient Boosting dominan: LightGBM logra el mejor F1 (0,476, precision 0,423, recall 0,547) y XGBoost el mejor AUC (0,796). Antigüedad, edad, nota de desempeño y saldo de vacaciones son las variables más relevantes. Un T-Learner con LightGBM (28 tratados vs 1.028 controles) produce uplift scores multimodales que segmentan a 74 persuasibles, 584 neutros y 398 detractores o sure things, lo que permite focalizar las acciones de retención. La principal limitación es el tamaño reducido del grupo tratado.</t>
+          <t>El SII de Chile administra unos 9,5 millones de predios con avalúos, superficies, destinos y geometrías, datos públicos por ley pero inutilizables para análisis masivo por tres barreras técnicas: un archivo de ancho fijo de 3 GB, una API de consulta unitaria con bloqueo de IPs y un servicio WMS que entrega los polígonos solo como imágenes PNG. La tesis implementa un pipeline de ingeniería de datos geoespaciales que supera las tres barreras: parseo del archivo heredado, extracción distribuida con 30 túneles WireGuard, descarga de tiles WMS a zoom 19, polygonización raster con GDAL, filtrado por valor DN y compactness, y spatial join con GeoPandas mediante el concepto de rol base. El resultado es un dataset nacional de 9,55 millones de predios en las 343 comunas, 5,67 millones de ellos (60,3 %) con polígono vectorial de unos 30 cm de resolución, más 16 semestres de series históricas de avalúo. Una validación en Lebu (n = 1.396) muestra un error mediano de 0,4 m entre coordenada oficial y centroide. El dataset se distribuye en la plataforma Catastral.cl (FastAPI, PostGIS, React) bajo un modelo de pago social y sirve de capa base a un sistema de localización de estaciones de servicio. Se concluye que las barreras son técnicas, no legales, y que la inaccesibilidad cuesta más de 2 millones de USD anuales.</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>Voluntary employee turnover is costly (replacing a skilled professional can reach up to 200% of annual salary) and generic retention strategies waste resources on employees who do not respond to them. This thesis develops, following the KDD methodology, a framework that combines resignation prediction models with Uplift Modeling to identify persuadable employees at a Chilean transport company. Four HR subsystems are integrated (2022-2024 headcount history of 5,636 employees, performance evaluations, absenteeism and compensation) and, after narrowing the analysis to the Professional and Manager job levels, a dataset of 1,056 observations with a 13% resignation rate is obtained. Using 5-fold stratified cross-validation, SMOTE, resignation-rate based cardinality reduction and one-hot encoding inside each fold, seven classifiers are compared. Gradient Boosting models dominate: LightGBM achieves the best F1 (0.476, precision 0.423, recall 0.547) and XGBoost the best AUC (0.796). Tenure, age, performance score and vacation balance are the most relevant variables. A T-Learner with LightGBM (28 treated vs 1,028 controls) yields multimodal uplift scores that segment 74 persuadables, 584 neutrals and 398 detractors or sure things, allowing retention actions to be targeted. The main limitation is the small size of the treated group.</t>
+          <t>Chile's Internal Revenue Service (SII) administers about 9.5 million properties with appraisals, areas, land uses and geometries, data that are formally public under Law 20,285 but unusable for large-scale analysis because of three technical barriers: a 3 GB fixed-width file, a single-property API with IP blocking, and a WMS service that delivers parcel polygons only as PNG images. The thesis implements a geospatial data engineering pipeline that overcomes all three barriers: parsing of the legacy file, distributed extraction through 30 WireGuard tunnels, download of WMS tiles at zoom 19, raster polygonization with GDAL, filtering by DN value and compactness, and a GeoPandas spatial join based on the base-roll concept. The result is a national dataset of 9.55 million properties across all 343 municipalities, 5.67 million of them (60.3%) with a vector polygon at roughly 30 cm resolution, plus 16 semesters of appraisal history. A validation in Lebu (n = 1,396) shows a median error of 0.4 m between the official coordinate and the polygon centroid. The dataset is distributed through the Catastral.cl platform (FastAPI, PostGIS, React) under a social-payment model and serves as the base layer for a fuel-station site-selection system. The thesis concludes that the barriers are technical rather than legal, and that inaccessibility costs over USD 2 million per year.</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>Integra cuatro bases de Recursos Humanos de una empresa de transporte en un dataset final de 1.056 profesionales y jefes con 13 % de renuncias.</t>
+          <t>El pipeline extrajo 9,55 millones de predios de las 343 comunas de Chile en unas 76 horas usando 30 túneles WireGuard con rotación de IP.</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>Compara siete clasificadores con validación cruzada de 5 folds y SMOTE aplicado dentro de cada fold para evitar data leakage.</t>
+          <t>La vectorización raster con GDAL produjo polígonos de unos 30 cm de resolución para 5,67 millones de predios, el 60,3 % del catastro nacional.</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>LightGBM obtiene el mejor F1-score (0,476) y XGBoost el mayor AUC (0,796), confirmando la superioridad de Gradient Boosting.</t>
+          <t>En 1.396 predios de Lebu, el error mediano entre coordenada oficial y centroide fue de 0,4 m, y el 95,6 % quedó bajo 20 m.</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>Antigüedad, edad, nota de desempeño y saldo de vacaciones emergen como las variables más importantes en LightGBM.</t>
+          <t>Catastral.cl sirve 9,4 millones de predios y 136 millones de filas históricas con PostGIS, FastAPI y React bajo un modelo de pago social.</t>
         </is>
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>Un T-Learner con LightGBM identifica 74 trabajadores persuasibles, 584 neutros y 398 detractores con solo 28 casos tratados.</t>
+          <t>La inaccesibilidad del dato catastral cuesta más de 2 millones de USD anuales, pagados a intermediarios que cobran entre 2.000 y 6.000 USD por comuna.</t>
         </is>
       </c>
       <c r="AG9" s="2" t="inlineStr">
         <is>
-          <t>Integrates four HR databases from a transport company into a final dataset of 1,056 professionals and managers with a 13% resignation rate.</t>
+          <t>The pipeline extracted 9.55 million properties from all 343 Chilean municipalities in about 76 hours using 30 WireGuard tunnels with IP rotation.</t>
         </is>
       </c>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>Compares seven classifiers with 5-fold cross-validation and SMOTE applied inside each fold to prevent data leakage.</t>
+          <t>Raster vectorization with GDAL produced polygons at roughly 30 cm resolution for 5.67 million properties, 60.3% of the national cadastre.</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>LightGBM achieves the best F1-score (0.476) and XGBoost the highest AUC (0.796), confirming the superiority of Gradient Boosting.</t>
+          <t>Across 1,396 properties in Lebu, the median error between official coordinate and polygon centroid was 0.4 m, with 95.6% under 20 m.</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>Tenure, age, performance score and vacation balance emerge as the most important variables in LightGBM.</t>
+          <t>Catastral.cl serves 9.4 million properties and 136 million historical rows with PostGIS, FastAPI and React under a social-payment model.</t>
         </is>
       </c>
       <c r="AK9" s="2" t="inlineStr">
         <is>
-          <t>A T-Learner with LightGBM identifies 74 persuadable employees, 584 neutrals and 398 detractors with only 28 treated cases.</t>
-        </is>
-      </c>
-      <c r="AL9" s="2" t="inlineStr">
-        <is>
-          <t>https://repositorio.uchile.cl/handle/2250/210195</t>
-        </is>
-      </c>
+          <t>Cadastral data inaccessibility costs over USD 2 million per year, paid to intermediaries charging USD 2,000 to 6,000 per municipality.</t>
+        </is>
+      </c>
+      <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2025-canete.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2026-hernandez.pdf</t>
         </is>
       </c>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>La empresa no se nombra, aunque las gerencias listadas en el anexo (Transporte de Pasajeros, Extensiones, Obras Civiles) y la categoría de sindicato S_Metro sugieren un operador de transporte urbano. El texto no menciona lenguaje ni librerías. Hay una inconsistencia de signo: la metodología define persuasibles con uplift positivo, pero en los resultados los persuasibles son los de uplift score menor a -0,05 (moda en -1,0), ya que el outcome es la renuncia. La tabla 4 y el gráfico 8 están en anexos; los gráficos no se recuperan en el texto extraído.</t>
+          <t>La portada indica 'Borrador Final' (abril 2026). Es una tesis de ingeniería de datos geoespaciales y producto (plataformas Catastral.cl y combustible.tremen.tech), no de modelamiento predictivo: no se entrenan modelos de ML; CLIP se usa como clasificador satelital preentrenado en el caso aplicado. El texto menciona Newmark Chile 'en el Capítulo 1' pero ese contexto no aparece en el documento. Algunas referencias cruzadas de sección son inconsistentes (p.ej. 'Sección 4.2.2' por 7.4.2).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2025-araneda</t>
+          <t>2025-canete</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -2184,7 +2176,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ignacio Andrés Araneda Gallardo</t>
+          <t>Nicolás Alejandro Cañete Ponce</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -2197,7 +2189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -2205,52 +2197,56 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Richard Weber</t>
+          <t>Jaime Andrés Miranda Pino</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Richard Weber; Sebastián Alejandro Maldonado Alarcón</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Desarrollo de una Metodología Analítica para Identificar Factores Determinantes del Review Score en E-commerce: Aplicación a la Base de Datos de Olist, Brasil</t>
+          <t>Retención de talento con People Analytics: un enfoque basado en Machine Learning y Uplift Modeling</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Development of an Analytical Methodology to Identify the Determinants of Review Score in E-commerce: Application to the Olist Database, Brazil</t>
+          <t>Talent retention with People Analytics: an approach based on Machine Learning and Uplift Modeling</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>e-commerce; retail</t>
+          <t>recursos humanos; transporte</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>clasificación; NLP / LLMs; clustering / segmentación; análisis descriptivo e inferencial</t>
+          <t>clasificación; uplift / causal</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Random Forest; Gradient Boosting; AdaBoost; XGBoost; LSTM; SHAP; BERTopic; Sentence-BERT; BERTweet (PySentimiento); XLM-RoBERTa</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Python; scikit-learn; Hugging Face Transformers; pysentimiento; BERTopic; TextBlob; VADER; Kaggle</t>
-        </is>
-      </c>
+          <t>LightGBM; XGBoost; Gradient Boosting; CatBoost; Random Forest; Logistic Regression; Decision Tree; T-Learner; SMOTE; Feature Importance</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Base de datos de e-commerce de Olist, Brasil (Olist (Kaggle))</t>
+          <t>Dotación histórica de trabajadores (datos internos de una empresa de transporte (subsistemas de Recursos Humanos)); Evaluaciones de desempeño (datos internos de una empresa de transporte (subsistemas de Recursos Humanos)); Ausentismos (licencias y vacaciones) (datos internos de una empresa de transporte (subsistemas de Recursos Humanos)); Compensaciones (incrementos de renta y retenciones) (datos internos de una empresa de transporte (subsistemas de Recursos Humanos))</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>Empresa de transporte chilena (no identificada por nombre en el texto)</t>
+        </is>
+      </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
           <t>indirect</t>
@@ -2258,104 +2254,104 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Aplicación comercial sobre datos públicos, con beneficio derivado para los consumidores: la metodología permite anticipar insatisfacción, mejorar el cumplimiento de entregas y la veracidad de las descripciones de producto.</t>
+          <t>La aplicación es interna a una empresa, orientada a eficiencia en la gestión de personas, pero genera beneficio derivado para los trabajadores al focalizar intervenciones de retención y evitar acciones ineficaces o contraproducentes.</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>Commercial application on public data with a derived benefit for consumers: the methodology helps anticipate dissatisfaction and improve delivery compliance and the accuracy of product descriptions.</t>
+          <t>The application is internal to a company and aimed at HR management efficiency, but it yields a derived benefit for employees by targeting retention interventions and avoiding ineffective or counterproductive actions.</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>comercio electrónico; reseñas de clientes; análisis de sentimientos; clasificación binaria; SHAP; BERTopic; logística de entrega</t>
+          <t>people analytics; fuga de talento; uplift modeling; inferencia causal; gradient boosting; recursos humanos; KDD</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>e-commerce; customer reviews; sentiment analysis; binary classification; SHAP; BERTopic; delivery logistics</t>
+          <t>people analytics; employee turnover; uplift modeling; causal inference; gradient boosting; human resources; KDD</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>En el comercio electrónico las reseñas de los clientes condicionan la reputación de los vendedores y las decisiones de compra, pero las plataformas suelen carecer de metodologías que integren esa información con variables logísticas y de producto. Esta tesis desarrolla una metodología analítica para identificar los factores determinantes del review score, aplicada a la base pública de Olist (Brasil) en Kaggle, que tras integrar siete tablas reunió 119.143 registros y 39 atributos. El trabajo combina análisis exploratorio, ingeniería de variables (diferencia entre fecha estimada y real de entrega, estado de entrega, volumen del producto), selección con SelectKBest, balanceo con SMOTE y clasificación binaria de reseñas negativas (1 y 2) frente a positivas (3 a 5) con Random Forest, Gradient Boosting, AdaBoost, XGBoost, LSTM y RNN. El sentimiento de los comentarios en portugués se cuantificó con PySentimiento y RoBERTa, y los temas de insatisfacción se descubrieron con BERTopic. Random Forest fue el mejor modelo, con precisión y F1 de 87,5 % sin sentimiento y 91,1 % al incorporar el puntaje de PySentimiento. SHAP confirmó que el tiempo de entrega y el sentimiento del comentario son los factores más influyentes, y BERTopic mostró que las quejas se concentran en pedidos no entregados, retrasos y productos distintos a su descripción. La metodología es replicable para anticipar insatisfacción y priorizar mejoras logísticas.</t>
+          <t>La fuga voluntaria de talento es costosa (el reemplazo de un profesional calificado puede alcanzar hasta el 200 % de su salario anual) y las estrategias de retención genéricas desperdician recursos en trabajadores que no responden a ellas. Esta AFE desarrolla, siguiendo la metodología KDD, un marco que combina modelos predictivos de renuncia con Uplift Modeling para identificar a los trabajadores persuasibles de una empresa de transporte chilena. Se integran cuatro subsistemas de Recursos Humanos (dotación histórica 2022-2024 de 5.636 trabajadores, evaluaciones de desempeño, ausentismos y compensaciones) y, tras acotar el análisis a los estamentos Profesionales y Jefes, se obtiene una base de 1.056 observaciones con 13 % de renuncias. Con validación cruzada estratificada de 5 folds, SMOTE, reducción de cardinalidad por tasa de renuncia y one-hot encoding dentro de cada fold, se comparan siete clasificadores. Los modelos de Gradient Boosting dominan: LightGBM logra el mejor F1 (0,476, precision 0,423, recall 0,547) y XGBoost el mejor AUC (0,796). Antigüedad, edad, nota de desempeño y saldo de vacaciones son las variables más relevantes. Un T-Learner con LightGBM (28 tratados vs 1.028 controles) produce uplift scores multimodales que segmentan a 74 persuasibles, 584 neutros y 398 detractores o sure things, lo que permite focalizar las acciones de retención. La principal limitación es el tamaño reducido del grupo tratado.</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>In e-commerce, customer ratings and reviews shape seller reputation and purchase decisions, yet platforms often lack methodologies that integrate this information with logistics and product variables. This thesis develops an analytical methodology to identify the determinants of review score, applied to the public Olist (Brazil) database available on Kaggle, which after merging seven tables yielded 119,143 records and 39 attributes. The work combines exploratory analysis, feature engineering (difference between estimated and actual delivery date, delivery status, product volume and customer-level aggregates), feature selection with SelectKBest, class balancing with SMOTE, and binary classification of negative reviews (1 and 2) versus positive ones (3 to 5) using Random Forest, Gradient Boosting, AdaBoost, XGBoost, LSTM and RNN. The sentiment of Portuguese comments was quantified with the pretrained PySentimiento and RoBERTa models, and dissatisfaction themes were discovered with BERTopic. Random Forest was the best model, with accuracy and F1 of 87.5% without sentiment and 91.1% when the PySentimiento score was included. SHAP confirmed that delivery time and comment sentiment are the most influential factors, and BERTopic showed that complaints concentrate on undelivered orders, delays and products that differ from their description. The methodology is replicable for anticipating dissatisfaction and prioritizing logistics and catalog improvements.</t>
+          <t>Voluntary employee turnover is costly (replacing a skilled professional can reach up to 200% of annual salary) and generic retention strategies waste resources on employees who do not respond to them. This thesis develops, following the KDD methodology, a framework that combines resignation prediction models with Uplift Modeling to identify persuadable employees at a Chilean transport company. Four HR subsystems are integrated (2022-2024 headcount history of 5,636 employees, performance evaluations, absenteeism and compensation) and, after narrowing the analysis to the Professional and Manager job levels, a dataset of 1,056 observations with a 13% resignation rate is obtained. Using 5-fold stratified cross-validation, SMOTE, resignation-rate based cardinality reduction and one-hot encoding inside each fold, seven classifiers are compared. Gradient Boosting models dominate: LightGBM achieves the best F1 (0.476, precision 0.423, recall 0.547) and XGBoost the best AUC (0.796). Tenure, age, performance score and vacation balance are the most relevant variables. A T-Learner with LightGBM (28 treated vs 1,028 controls) yields multimodal uplift scores that segment 74 persuadables, 584 neutrals and 398 detractors or sure things, allowing retention actions to be targeted. The main limitation is the small size of the treated group.</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>La base integrada de Olist reunió 119.143 registros y 39 atributos de clientes, pedidos, productos, pagos, reseñas y vendedores.</t>
+          <t>Integra cuatro bases de Recursos Humanos de una empresa de transporte en un dataset final de 1.056 profesionales y jefes con 13 % de renuncias.</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>Random Forest alcanzó 87,5 % de precisión y F1 sin sentimiento, y 91,1 % al incorporar el puntaje de sentimiento de PySentimiento.</t>
+          <t>Compara siete clasificadores con validación cruzada de 5 folds y SMOTE aplicado dentro de cada fold para evitar data leakage.</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>AdaBoost mostró el mayor salto relativo, pasando de 68,8 % a 83,6 % de precisión al agregar la variable de sentimiento.</t>
+          <t>LightGBM obtiene el mejor F1-score (0,476) y XGBoost el mayor AUC (0,796), confirmando la superioridad de Gradient Boosting.</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>Según SHAP, la diferencia entre fecha estimada y real de entrega y el sentimiento del comentario son los factores más influyentes en reseñas negativas.</t>
+          <t>Antigüedad, edad, nota de desempeño y saldo de vacaciones emergen como las variables más importantes en LightGBM.</t>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>BERTopic con Sentence-BERT y HDBSCAN identificó 8 clústeres (coherencia 0,5878); el peor promedió 1,43 estrellas con 85,7 % de reseñas negativas.</t>
+          <t>Un T-Learner con LightGBM identifica 74 trabajadores persuasibles, 584 neutros y 398 detractores con solo 28 casos tratados.</t>
         </is>
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
-          <t>The integrated Olist database comprised 119,143 records and 39 attributes covering customers, orders, products, payments, reviews and sellers.</t>
+          <t>Integrates four HR databases from a transport company into a final dataset of 1,056 professionals and managers with a 13% resignation rate.</t>
         </is>
       </c>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>Random Forest reached 87.5% accuracy and F1 without sentiment, and 91.1% when the PySentimiento sentiment score was included.</t>
+          <t>Compares seven classifiers with 5-fold cross-validation and SMOTE applied inside each fold to prevent data leakage.</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>AdaBoost showed the largest relative gain, rising from 68.8% to 83.6% accuracy once the sentiment variable was added.</t>
+          <t>LightGBM achieves the best F1-score (0.476) and XGBoost the highest AUC (0.796), confirming the superiority of Gradient Boosting.</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>According to SHAP, the gap between estimated and actual delivery date and comment sentiment are the most influential factors behind negative reviews.</t>
+          <t>Tenure, age, performance score and vacation balance emerge as the most important variables in LightGBM.</t>
         </is>
       </c>
       <c r="AK10" s="2" t="inlineStr">
         <is>
-          <t>BERTopic with Sentence-BERT and HDBSCAN identified 8 clusters (coherence 0.5878); the worst averaged 1.43 stars with 85.7% negative reviews.</t>
+          <t>A T-Learner with LightGBM identifies 74 persuadable employees, 584 neutrals and 398 detractors with only 28 treated cases.</t>
         </is>
       </c>
       <c r="AL10" s="2" t="inlineStr">
         <is>
-          <t>https://repositorio.uchile.cl/handle/2250/207923</t>
+          <t>https://repositorio.uchile.cl/handle/2250/210195</t>
         </is>
       </c>
       <c r="AM10" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2025-araneda.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-canete.pdf</t>
         </is>
       </c>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>El texto extraído no incluye las tablas en su lugar original: aparecen al final en formato de columnas separadas por barras verticales. El lenguaje Python no se menciona de forma explícita; se infiere por las librerías citadas (scikit-learn, transformers de Hugging Face, pysentimiento). Se evaluaron además BETO (nlptown), TextBlob y VADER como modelos de sentimiento, descartados por menor desempeño. Fecha de la portada: junio 2025.</t>
+          <t>La empresa no se nombra, aunque las gerencias listadas en el anexo (Transporte de Pasajeros, Extensiones, Obras Civiles) y la categoría de sindicato S_Metro sugieren un operador de transporte urbano. El texto no menciona lenguaje ni librerías. Hay una inconsistencia de signo: la metodología define persuasibles con uplift positivo, pero en los resultados los persuasibles son los de uplift score menor a -0,05 (moda en -1,0), ya que el outcome es la renuncia. La tabla 4 y el gráfico 8 están en anexos; los gráficos no se recuperan en el texto extraído.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2025-barros</t>
+          <t>2025-araneda</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2370,7 +2366,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sandra Carolina Barros Henríquez</t>
+          <t>Ignacio Andrés Araneda Gallardo</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -2383,7 +2379,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -2391,48 +2387,44 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Félix Patricio Lizama Garrido</t>
+          <t>Richard Weber</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>David Alejandro Díaz Solís; Felipe Ignacio Simón Compte</t>
-        </is>
-      </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Análisis de las variables que explican eficiencia en establecimientos educacionales de Chile mediante un enfoque híbrido DEA: Machine Learning</t>
+          <t>Desarrollo de una Metodología Analítica para Identificar Factores Determinantes del Review Score en E-commerce: Aplicación a la Base de Datos de Olist, Brasil</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Analysis of the variables that explain efficiency in Chilean schools using a hybrid DEA: Machine Learning approach</t>
+          <t>Development of an Analytical Methodology to Identify the Determinants of Review Score in E-commerce: Application to the Olist Database, Brazil</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>educación; sector público</t>
+          <t>e-commerce; retail</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>regresión; DEA; análisis descriptivo e inferencial</t>
+          <t>clasificación; NLP / LLMs; clustering / segmentación; análisis descriptivo e inferencial</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>DEA; XGBoost; Random Forest; Multilayer Perceptron (MLP); Support Vector Regression (SVM); SHAP; Grid Search; Min-Max Scaling; One-Hot Encoding; ANOVA / Kruskal-Wallis</t>
+          <t>Random Forest; Gradient Boosting; AdaBoost; XGBoost; LSTM; SHAP; BERTopic; Sentence-BERT; BERTweet (PySentimiento); XLM-RoBERTa</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Python; scikit-learn; Pandas; NumPy; Matplotlib</t>
+          <t>Python; scikit-learn; Hugging Face Transformers; pysentimiento; BERTopic; TextBlob; VADER; Kaggle</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Eficiencia DEA de establecimientos educacionales chilenos (González, 2024) (Trabajo DEA previo (González, 2024) construido con datos oficiales: SIMCE e IDPS (Mineduc / Agencia de Calidad), IVE, encuesta Mineduc-EduInclusiva y BD Superintendencia de Educación)</t>
+          <t>Base de datos de e-commerce de Olist, Brasil (Olist (Kaggle))</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -2443,109 +2435,109 @@
       <c r="T11" s="2" t="inlineStr"/>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>indirect</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>La tesis aborda directamente un problema de política pública educativa: la eficiencia y la equidad de los establecimientos públicos y subvencionados chilenos, incorporando convivencia escolar y vulnerabilidad, y cierra con recomendaciones de política pública.</t>
+          <t>Aplicación comercial sobre datos públicos, con beneficio derivado para los consumidores: la metodología permite anticipar insatisfacción, mejorar el cumplimiento de entregas y la veracidad de las descripciones de producto.</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>The thesis directly addresses an education policy problem: the efficiency and equity of Chilean public and subsidized schools, incorporating school climate and vulnerability, and closes with public policy recommendations.</t>
+          <t>Commercial application on public data with a derived benefit for consumers: the methodology helps anticipate dissatisfaction and improve delivery compliance and the accuracy of product descriptions.</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>eficiencia escolar; DEA; machine learning; SHAP; convivencia escolar; educación pública; política educativa</t>
+          <t>comercio electrónico; reseñas de clientes; análisis de sentimientos; clasificación binaria; SHAP; BERTopic; logística de entrega</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>school efficiency; DEA; machine learning; SHAP; school climate; public education; education policy</t>
+          <t>e-commerce; customer reviews; sentiment analysis; binary classification; SHAP; BERTopic; delivery logistics</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>La tesis estudia qué factores explican la eficiencia técnica de los establecimientos educacionales públicos y subvencionados de Chile, incorporando la convivencia escolar, ausente en los estudios DEA previos. Se toma como variable objetivo la eficiencia continua (entre 0 y 1) estimada en un trabajo anterior con Análisis Envolvente de Datos (DEA) sobre unos 912 establecimientos, y se entrenan modelos de regresión (Random Forest, XGBoost, XGBoost+, MLP y SVM) ajustados con GridSearch. Se realizan dos etapas: primero con las 7 variables de input y output del DEA (razones de profesores de convivencia, lenguaje y matemáticas por alumno, experiencia del equipo de convivencia, SIMCE e IDPS) y luego con 45 variables complementarias seleccionadas por un experto en educación a partir de datos de Mineduc, la Superintendencia de Educación y la encuesta EduInclusiva. XGBoost obtuvo R² de 0,76 con variables DEA y XGBoost+ R² de 0,769 con variables experto. La interpretación con SHAP revela relaciones no lineales, saturación en la dotación docente, un umbral crítico de vulnerabilidad (IVE 0,55 a 0,6), ventaja de los establecimientos subvencionados y urbanos, economías de escala por matrícula y el peso del ambiente de respeto dentro del IDPS. Se confirma la hipótesis de que el enfoque híbrido DEA y machine learning mejora la capacidad explicativa y se derivan siete recomendaciones de política pública.</t>
+          <t>En el comercio electrónico las reseñas de los clientes condicionan la reputación de los vendedores y las decisiones de compra, pero las plataformas suelen carecer de metodologías que integren esa información con variables logísticas y de producto. Esta tesis desarrolla una metodología analítica para identificar los factores determinantes del review score, aplicada a la base pública de Olist (Brasil) en Kaggle, que tras integrar siete tablas reunió 119.143 registros y 39 atributos. El trabajo combina análisis exploratorio, ingeniería de variables (diferencia entre fecha estimada y real de entrega, estado de entrega, volumen del producto), selección con SelectKBest, balanceo con SMOTE y clasificación binaria de reseñas negativas (1 y 2) frente a positivas (3 a 5) con Random Forest, Gradient Boosting, AdaBoost, XGBoost, LSTM y RNN. El sentimiento de los comentarios en portugués se cuantificó con PySentimiento y RoBERTa, y los temas de insatisfacción se descubrieron con BERTopic. Random Forest fue el mejor modelo, con precisión y F1 de 87,5 % sin sentimiento y 91,1 % al incorporar el puntaje de PySentimiento. SHAP confirmó que el tiempo de entrega y el sentimiento del comentario son los factores más influyentes, y BERTopic mostró que las quejas se concentran en pedidos no entregados, retrasos y productos distintos a su descripción. La metodología es replicable para anticipar insatisfacción y priorizar mejoras logísticas.</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>This thesis studies which factors explain the technical efficiency of public and state-subsidized schools in Chile, explicitly incorporating school climate (convivencia escolar), a dimension absent from previous DEA studies. The target variable is the continuous efficiency score (between 0 and 1) estimated in an earlier Data Envelopment Analysis (DEA) study covering roughly 912 schools, and regression models (Random Forest, XGBoost, XGBoost+, MLP neural networks and SVM) are trained with GridSearch hyperparameter tuning. Two stages are carried out: first with the 7 DEA input and output variables (ratios of school-climate, language and mathematics teachers per student, experience of the school-climate team, SIMCE scores and IDPS) and then with 45 complementary variables selected by an education expert from Mineduc, the Superintendencia de Educación and the EduInclusiva survey. XGBoost reached an R² of 0.76 with DEA variables and XGBoost+ an R² of 0.769 with expert variables. SHAP interpretation reveals non-linear relationships, saturation in teacher staffing, a critical vulnerability threshold (IVE 0.55 to 0.6), an advantage for subsidized and urban schools, economies of scale from enrollment, and the weight of the respect dimension within the IDPS. The hypothesis that the hybrid DEA and machine learning approach improves explanatory power is confirmed, and seven public policy recommendations are derived.</t>
+          <t>In e-commerce, customer ratings and reviews shape seller reputation and purchase decisions, yet platforms often lack methodologies that integrate this information with logistics and product variables. This thesis develops an analytical methodology to identify the determinants of review score, applied to the public Olist (Brazil) database available on Kaggle, which after merging seven tables yielded 119,143 records and 39 attributes. The work combines exploratory analysis, feature engineering (difference between estimated and actual delivery date, delivery status, product volume and customer-level aggregates), feature selection with SelectKBest, class balancing with SMOTE, and binary classification of negative reviews (1 and 2) versus positive ones (3 to 5) using Random Forest, Gradient Boosting, AdaBoost, XGBoost, LSTM and RNN. The sentiment of Portuguese comments was quantified with the pretrained PySentimiento and RoBERTa models, and dissatisfaction themes were discovered with BERTopic. Random Forest was the best model, with accuracy and F1 of 87.5% without sentiment and 91.1% when the PySentimiento score was included. SHAP confirmed that delivery time and comment sentiment are the most influential factors, and BERTopic showed that complaints concentrate on undelivered orders, delays and products that differ from their description. The methodology is replicable for anticipating dissatisfaction and prioritizing logistics and catalog improvements.</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>Con las 7 variables del DEA, XGBoost explicó el 76 % de la variabilidad de la eficiencia (R² 0,76, MSE 0,010, MAE 0,08).</t>
+          <t>La base integrada de Olist reunió 119.143 registros y 39 atributos de clientes, pedidos, productos, pagos, reseñas y vendedores.</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>Con 45 variables seleccionadas por un experto en educación, XGBoost+ alcanzó R² 0,769, MSE 0,016 y MAE 0,095 sobre unos 912 establecimientos.</t>
+          <t>Random Forest alcanzó 87,5 % de precisión y F1 sin sentimiento, y 91,1 % al incorporar el puntaje de sentimiento de PySentimiento.</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>La razón de profesionales de convivencia por alumno fue la variable más influyente del modelo DEA, con efecto positivo que se satura y revierte.</t>
+          <t>AdaBoost mostró el mayor salto relativo, pasando de 68,8 % a 83,6 % de precisión al agregar la variable de sentimiento.</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>Entre las variables experto destacan horas de aula por alumno, dependencia subvencionada, umbral crítico de vulnerabilidad (IVE 0,55 a 0,6), matrícula y zona urbana.</t>
+          <t>Según SHAP, la diferencia entre fecha estimada y real de entrega y el sentimiento del comentario son los factores más influyentes en reseñas negativas.</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>Al descomponer el IDPS, el ambiente de respeto concentra el efecto de la convivencia, con mejoras solo en puntajes altos; se derivan siete recomendaciones.</t>
+          <t>BERTopic con Sentence-BERT y HDBSCAN identificó 8 clústeres (coherencia 0,5878); el peor promedió 1,43 estrellas con 85,7 % de reseñas negativas.</t>
         </is>
       </c>
       <c r="AG11" s="2" t="inlineStr">
         <is>
-          <t>Using the 7 DEA variables, XGBoost explained 76% of efficiency variability (R² 0.76, MSE 0.010, MAE 0.08).</t>
+          <t>The integrated Olist database comprised 119,143 records and 39 attributes covering customers, orders, products, payments, reviews and sellers.</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>Using 45 variables selected by an education expert, XGBoost+ reached R² 0.769, MSE 0.016 and MAE 0.095 across roughly 912 schools.</t>
+          <t>Random Forest reached 87.5% accuracy and F1 without sentiment, and 91.1% when the PySentimiento sentiment score was included.</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>The ratio of school-climate professionals per student was the most influential DEA-model variable, with a positive effect that saturates and then reverses.</t>
+          <t>AdaBoost showed the largest relative gain, rising from 68.8% to 83.6% accuracy once the sentiment variable was added.</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>Among expert variables, classroom hours per student, subsidized administration, a critical vulnerability threshold (IVE 0.55 to 0.6), enrollment and urban location stand out.</t>
+          <t>According to SHAP, the gap between estimated and actual delivery date and comment sentiment are the most influential factors behind negative reviews.</t>
         </is>
       </c>
       <c r="AK11" s="2" t="inlineStr">
         <is>
-          <t>Decomposing the IDPS shows the respect dimension concentrates the climate effect, with clear gains only at high scores; seven policy recommendations follow.</t>
+          <t>BERTopic with Sentence-BERT and HDBSCAN identified 8 clusters (coherence 0.5878); the worst averaged 1.43 stars with 85.7% negative reviews.</t>
         </is>
       </c>
       <c r="AL11" s="2" t="inlineStr">
         <is>
-          <t>https://repositorio.uchile.cl/handle/2250/207928</t>
+          <t>https://repositorio.uchile.cl/handle/2250/207923</t>
         </is>
       </c>
       <c r="AM11" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2025-barros.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-araneda.pdf</t>
         </is>
       </c>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>La portada del texto extraído dice 'Determinación de las variables que explican eficiencia en establecimientos educacionales de Chile' (2025, profesora guía Felix Lizama); se usó el título oficial entregado. El resumen ejecutivo es más bien una declaración de objetivos; las cifras provienen de los capítulos de resultados y anexos. El tamaño de la muestra (912) se infiere de la tabla descriptiva del anexo 5 (valores únicos de DMU), no se declara explícitamente. Hay inconsistencias internas sobre el signo del efecto de la razón de horas de aula por alumno: el cuerpo y el anexo 10 lo describen como inverso, mientras el análisis por cuartiles y el anexo 9 lo describen como positivo. Las métricas se denominan 'de clasificación' aunque el problema es de regresión. Más de la mitad del texto son anexos con descripciones de gráficos SHAP.</t>
+          <t>El texto extraído no incluye las tablas en su lugar original: aparecen al final en formato de columnas separadas por barras verticales. El lenguaje Python no se menciona de forma explícita; se infiere por las librerías citadas (scikit-learn, transformers de Hugging Face, pysentimiento). Se evaluaron además BETO (nlptown), TextBlob y VADER como modelos de sentimiento, descartados por menor desempeño. Fecha de la portada: junio 2025.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2025-sepulveda</t>
+          <t>2025-barros</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2560,7 +2552,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Juan Ernesto Osvaldo Sepúlveda Alonso</t>
+          <t>Sandra Carolina Barros Henríquez</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -2573,7 +2565,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -2581,48 +2573,48 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>David Alejandro Díaz Solís</t>
+          <t>Félix Patricio Lizama Garrido</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Felipe Ignacio Simón Compte; Félix Patricio Lizama Garrido</t>
+          <t>David Alejandro Díaz Solís; Felipe Ignacio Simón Compte</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Análisis de recuperación de servicios en el sector de fabricantes de productos alimenticios: un estudio mediante modelos de lenguaje de gran escala</t>
+          <t>Análisis de las variables que explican eficiencia en establecimientos educacionales de Chile mediante un enfoque híbrido DEA: Machine Learning</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Service recovery analysis in the food product manufacturing sector: a study using large language models</t>
+          <t>Analysis of the variables that explain efficiency in Chilean schools using a hybrid DEA: Machine Learning approach</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>alimentos; servicios</t>
+          <t>educación; sector público</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>NLP / LLMs; análisis descriptivo e inferencial</t>
+          <t>regresión; DEA; análisis descriptivo e inferencial</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Gemini; Gemma; Zero-shot LLM classification; LLM-based machine translation; Cohen's Kappa; Pearson correlation; t-test; Cohen's d; Threshold optimization (binarization cutoffs)</t>
+          <t>DEA; XGBoost; Random Forest; Multilayer Perceptron (MLP); Support Vector Regression (SVM); SHAP; Grid Search; Min-Max Scaling; One-Hot Encoding; ANOVA / Kruskal-Wallis</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Google Gemini; Google Gemma; Google academic research API access</t>
+          <t>Python; scikit-learn; Pandas; NumPy; Matplotlib</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Reclamos SENACON, categoría Fabricantes de Productos Alimenticios (SENACON / Consumidor.gov.br, Ministério da Justiça, Brasil)</t>
+          <t>Eficiencia DEA de establecimientos educacionales chilenos (González, 2024) (Trabajo DEA previo (González, 2024) construido con datos oficiales: SIMCE e IDPS (Mineduc / Agencia de Calidad), IVE, encuesta Mineduc-EduInclusiva y BD Superintendencia de Educación)</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -2633,109 +2625,109 @@
       <c r="T12" s="2" t="inlineStr"/>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>indirect</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Usa datos públicos de protección al consumidor y aporta evidencia sobre cómo las empresas gestionan reclamos de seguridad alimentaria, con implicancias para consumidores y regulación, pero el foco es la efectividad empresarial de las respuestas.</t>
+          <t>La tesis aborda directamente un problema de política pública educativa: la eficiencia y la equidad de los establecimientos públicos y subvencionados chilenos, incorporando convivencia escolar y vulnerabilidad, y cierra con recomendaciones de política pública.</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>It uses public consumer protection data and provides evidence on how companies handle food safety complaints, with implications for consumers and regulation, but the focus is on the business effectiveness of responses.</t>
+          <t>The thesis directly addresses an education policy problem: the efficiency and equity of Chilean public and subsidized schools, incorporating school climate and vulnerability, and closes with public policy recommendations.</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>recuperación de servicios; justicia percibida; modelos de lenguaje de gran escala; zero-shot learning; gestión de reclamos; industria alimentaria; SENACON</t>
+          <t>eficiencia escolar; DEA; machine learning; SHAP; convivencia escolar; educación pública; política educativa</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>service recovery; perceived justice; large language models; zero-shot learning; complaint management; food industry; SENACON</t>
+          <t>school efficiency; DEA; machine learning; SHAP; school climate; public education; education policy</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>La tesis estudia qué elementos de las respuestas empresariales a reclamos se asocian con mayor satisfacción del consumidor en fabricantes de alimentos de Brasil. Se basa en la teoría de justicia percibida y en la plataforma pública SENACON, que registra reclamo, respuesta y evaluación del consumidor (escala 1 a 5). La base completa comprende 5.465 reclamos del período 2020 a 2024, concentrados en Nescafé Dolce Gusto, Nestlé y Nespresso (70 % del total), y una muestra estratificada de 300 casos fue codificada manualmente por dos expertos como gold standard. Los modelos Gemini y Gemma, en modo zero-shot y con textos traducidos al inglés, puntuaron compensación y empatía en escalas de 0 a 100; Gemini alcanzó 92,7 % de accuracy en compensación (kappa 0,77) y 81,0 % en empatía. Las correlaciones con la satisfacción resultaron prácticamente nulas (r = 0,02 para compensación, r = 0,06 para empatía; diferencia de +0,09 puntos, p = 0,74), por lo que la hipótesis central se rechaza. El tiempo de respuesta muestra un efecto descriptivo y el canal y el tipo de problema moderan la efectividad. El trabajo aporta un protocolo replicable de validación híbrida humano-LLM y evidencia de que la calidad y contextualización de la respuesta importan más que la mera presencia de empatía o compensación.</t>
+          <t>La tesis estudia qué factores explican la eficiencia técnica de los establecimientos educacionales públicos y subvencionados de Chile, incorporando la convivencia escolar, ausente en los estudios DEA previos. Se toma como variable objetivo la eficiencia continua (entre 0 y 1) estimada en un trabajo anterior con Análisis Envolvente de Datos (DEA) sobre unos 912 establecimientos, y se entrenan modelos de regresión (Random Forest, XGBoost, XGBoost+, MLP y SVM) ajustados con GridSearch. Se realizan dos etapas: primero con las 7 variables de input y output del DEA (razones de profesores de convivencia, lenguaje y matemáticas por alumno, experiencia del equipo de convivencia, SIMCE e IDPS) y luego con 45 variables complementarias seleccionadas por un experto en educación a partir de datos de Mineduc, la Superintendencia de Educación y la encuesta EduInclusiva. XGBoost obtuvo R² de 0,76 con variables DEA y XGBoost+ R² de 0,769 con variables experto. La interpretación con SHAP revela relaciones no lineales, saturación en la dotación docente, un umbral crítico de vulnerabilidad (IVE 0,55 a 0,6), ventaja de los establecimientos subvencionados y urbanos, economías de escala por matrícula y el peso del ambiente de respeto dentro del IDPS. Se confirma la hipótesis de que el enfoque híbrido DEA y machine learning mejora la capacidad explicativa y se derivan siete recomendaciones de política pública.</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>This thesis examines which communicational elements of corporate responses to complaints are associated with higher consumer satisfaction in Brazil's food product manufacturing sector. It builds on perceived justice theory (distributive, interactional and procedural) and uses the public SENACON platform (consumidor.gov.br), which records the complaint, the company's response and the consumer's rating on a 1 to 5 scale. The full dataset comprises 5,465 complaints from 2020 to 2024, concentrated in Nescafé Dolce Gusto, Nestlé and Nespresso (70% of the total), and a stratified sample of 300 cases was manually coded by two experts as a gold standard. The Gemini and Gemma models, in zero-shot mode and with texts translated into English, scored compensation and empathy on 0 to 100 scales; Gemini reached 92.7% accuracy on compensation (kappa 0.77) and 81.0% on empathy. Correlations with satisfaction were practically null (r = 0.02 for compensation, r = 0.06 for empathy; a difference of +0.09 points, p = 0.74), so the central hypothesis is rejected. Response time shows a descriptive effect (2.74 to 2.58 points), and sales channel and problem type moderate effectiveness. The work contributes a replicable human-LLM hybrid validation protocol and evidence that response quality and contextualization matter more than the mere presence of empathy or compensation.</t>
+          <t>This thesis studies which factors explain the technical efficiency of public and state-subsidized schools in Chile, explicitly incorporating school climate (convivencia escolar), a dimension absent from previous DEA studies. The target variable is the continuous efficiency score (between 0 and 1) estimated in an earlier Data Envelopment Analysis (DEA) study covering roughly 912 schools, and regression models (Random Forest, XGBoost, XGBoost+, MLP neural networks and SVM) are trained with GridSearch hyperparameter tuning. Two stages are carried out: first with the 7 DEA input and output variables (ratios of school-climate, language and mathematics teachers per student, experience of the school-climate team, SIMCE scores and IDPS) and then with 45 complementary variables selected by an education expert from Mineduc, the Superintendencia de Educación and the EduInclusiva survey. XGBoost reached an R² of 0.76 with DEA variables and XGBoost+ an R² of 0.769 with expert variables. SHAP interpretation reveals non-linear relationships, saturation in teacher staffing, a critical vulnerability threshold (IVE 0.55 to 0.6), an advantage for subsidized and urban schools, economies of scale from enrollment, and the weight of the respect dimension within the IDPS. The hypothesis that the hybrid DEA and machine learning approach improves explanatory power is confirmed, and seven public policy recommendations are derived.</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>Se analizaron 5.465 reclamos de fabricantes de alimentos registrados en SENACON entre 2020 y 2024, con 300 casos codificados manualmente como gold standard.</t>
+          <t>Con las 7 variables del DEA, XGBoost explicó el 76 % de la variabilidad de la eficiencia (R² 0,76, MSE 0,010, MAE 0,08).</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>Gemini en modo zero-shot alcanzó 92,7 % de accuracy y kappa 0,77 en compensación, y 81,0 % de accuracy en empatía frente a codificadores humanos.</t>
+          <t>Con 45 variables seleccionadas por un experto en educación, XGBoost+ alcanzó R² 0,769, MSE 0,016 y MAE 0,095 sobre unos 912 establecimientos.</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>La presencia de compensación o empatía casi no se correlaciona con la satisfacción (r = 0,02 y r = 0,06), rechazando la hipótesis central.</t>
+          <t>La razón de profesionales de convivencia por alumno fue la variable más influyente del modelo DEA, con efecto positivo que se satura y revierte.</t>
         </is>
       </c>
       <c r="AE12" s="2" t="inlineStr">
         <is>
-          <t>La satisfacción cae de 2,74 a 2,58 puntos cuando la respuesta demora más de 10 días, aunque la correlación lineal es débil.</t>
+          <t>Entre las variables experto destacan horas de aula por alumno, dependencia subvencionada, umbral crítico de vulnerabilidad (IVE 0,55 a 0,6), matrícula y zona urbana.</t>
         </is>
       </c>
       <c r="AF12" s="2" t="inlineStr">
         <is>
-          <t>En reclamos de seguridad alimentaria ninguna respuesta fue plenamente transparente; 73,9 % usó comunicación técnica sin asumir responsabilidad y 26,1 % fue evasiva.</t>
+          <t>Al descomponer el IDPS, el ambiente de respeto concentra el efecto de la convivencia, con mejoras solo en puntajes altos; se derivan siete recomendaciones.</t>
         </is>
       </c>
       <c r="AG12" s="2" t="inlineStr">
         <is>
-          <t>5,465 complaints against food manufacturers recorded in SENACON between 2020 and 2024 were analyzed, with 300 cases manually coded as a gold standard.</t>
+          <t>Using the 7 DEA variables, XGBoost explained 76% of efficiency variability (R² 0.76, MSE 0.010, MAE 0.08).</t>
         </is>
       </c>
       <c r="AH12" s="2" t="inlineStr">
         <is>
-          <t>Gemini in zero-shot mode reached 92.7% accuracy and kappa 0.77 on compensation, and 81.0% accuracy on empathy against human coders.</t>
+          <t>Using 45 variables selected by an education expert, XGBoost+ reached R² 0.769, MSE 0.016 and MAE 0.095 across roughly 912 schools.</t>
         </is>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>The presence of compensation or empathy is barely correlated with consumer satisfaction (r = 0.02 and r = 0.06), rejecting the central hypothesis.</t>
+          <t>The ratio of school-climate professionals per student was the most influential DEA-model variable, with a positive effect that saturates and then reverses.</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>Satisfaction falls from 2.74 to 2.58 points when the response takes more than 10 days, although the linear correlation is weak.</t>
+          <t>Among expert variables, classroom hours per student, subsidized administration, a critical vulnerability threshold (IVE 0.55 to 0.6), enrollment and urban location stand out.</t>
         </is>
       </c>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>In food safety complaints no response was fully transparent; 73.9% used technical communication without accepting responsibility and 26.1% were evasive.</t>
+          <t>Decomposing the IDPS shows the respect dimension concentrates the climate effect, with clear gains only at high scores; seven policy recommendations follow.</t>
         </is>
       </c>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>https://repositorio.uchile.cl/handle/2250/207953</t>
+          <t>https://repositorio.uchile.cl/handle/2250/207928</t>
         </is>
       </c>
       <c r="AM12" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2025-sepulveda.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-barros.pdf</t>
         </is>
       </c>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>El texto tiene inconsistencias internas: la síntesis de P4 reporta 720 reclamos de seguridad alimentaria con 45/32/23 % de estrategias y notas 3,4/2,7/2,1, mientras que la sección correspondiente reporta 72 casos, 26,1 % evasivas, 73,9 % técnicas y cero transparentes (se usó esta última versión en los highlights). La base completa aparece como 5.465 y también como 5.468 evaluaciones. Hay párrafos duplicados en la sección de seguridad alimentaria y dos secciones tituladas Conclusiones. El OE5 se cita en la metodología pero no está en la lista de objetivos. No se nombra explícitamente el lenguaje de programación; el anexo muestra prompts en sintaxis tipo Python (SYSTEM_CONTENT = """..."""). Declara uso de Claude, ChatGPT y Gemini para mejorar la redacción.</t>
+          <t>La portada del texto extraído dice 'Determinación de las variables que explican eficiencia en establecimientos educacionales de Chile' (2025, profesora guía Felix Lizama); se usó el título oficial entregado. El resumen ejecutivo es más bien una declaración de objetivos; las cifras provienen de los capítulos de resultados y anexos. El tamaño de la muestra (912) se infiere de la tabla descriptiva del anexo 5 (valores únicos de DMU), no se declara explícitamente. Hay inconsistencias internas sobre el signo del efecto de la razón de horas de aula por alumno: el cuerpo y el anexo 10 lo describen como inverso, mientras el análisis por cuartiles y el anexo 9 lo describen como positivo. Las métricas se denominan 'de clasificación' aunque el problema es de regresión. Más de la mitad del texto son anexos con descripciones de gráficos SHAP.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2025-gajardo</t>
+          <t>2025-sepulveda</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2750,11 +2742,11 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Juan Francisco Gajardo Mejías</t>
+          <t>Juan Ernesto Osvaldo Sepúlveda Alonso</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -2763,7 +2755,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -2771,48 +2763,48 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Sebastián Alejandro Maldonado Alarcón</t>
+          <t>David Alejandro Díaz Solís</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>David Alejandro Díaz Solís; Alejandro Adrián Bernales Silva</t>
+          <t>Felipe Ignacio Simón Compte; Félix Patricio Lizama Garrido</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Modelamiento predictivo de aportes y rescates de fondos mutuos de renta fija local</t>
+          <t>Análisis de recuperación de servicios en el sector de fabricantes de productos alimenticios: un estudio mediante modelos de lenguaje de gran escala</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Predictive modeling of contributions and redemptions in local fixed-income mutual funds</t>
+          <t>Service recovery analysis in the food product manufacturing sector: a study using large language models</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>finanzas; banca</t>
+          <t>alimentos; servicios</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>series de tiempo / forecasting; regresión; análisis descriptivo e inferencial</t>
+          <t>NLP / LLMs; análisis descriptivo e inferencial</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>ARIMA; SARIMAX; Decision Tree; Random Forest; XGBoost; SVM; LSTM; GRU; ADF test; Seasonal decomposition</t>
+          <t>Gemini; Gemma; Zero-shot LLM classification; LLM-based machine translation; Cohen's Kappa; Pearson correlation; t-test; Cohen's d; Threshold optimization (binarization cutoffs)</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Python; Excel</t>
+          <t>Google Gemini; Google Gemma; Google academic research API access</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Aportes, rescates y rentabilidades de fondos mutuos de renta fija local (AAFM) (Web scraping del sitio de la Asociación de Administradoras de Fondos Mutuos de Chile (AAFM))</t>
+          <t>Reclamos SENACON, categoría Fabricantes de Productos Alimenticios (SENACON / Consumidor.gov.br, Ministério da Justiça, Brasil)</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -2828,104 +2820,104 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>La aplicación es comercial (gestión de fondos, emisión de deuda e inversión), pero anticipar rescates masivos ayuda a reducir riesgos de liquidez y ventas forzadas, lo que contribuye a la estabilidad del sistema financiero chileno.</t>
+          <t>Usa datos públicos de protección al consumidor y aporta evidencia sobre cómo las empresas gestionan reclamos de seguridad alimentaria, con implicancias para consumidores y regulación, pero el foco es la efectividad empresarial de las respuestas.</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>The application is commercial (fund management, debt issuance and investment), but anticipating mass redemptions helps reduce liquidity risk and fire sales, which contributes to the stability of the Chilean financial system.</t>
+          <t>It uses public consumer protection data and provides evidence on how companies handle food safety complaints, with implications for consumers and regulation, but the focus is on the business effectiveness of responses.</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>fondos mutuos; renta fija; aportes y rescates; series de tiempo; SARIMAX; XGBoost; redes recurrentes</t>
+          <t>recuperación de servicios; justicia percibida; modelos de lenguaje de gran escala; zero-shot learning; gestión de reclamos; industria alimentaria; SENACON</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>mutual funds; fixed income; contributions and redemptions; time series; SARIMAX; XGBoost; recurrent neural networks</t>
+          <t>service recovery; perceived justice; large language models; zero-shot learning; complaint management; food industry; SENACON</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>Los gestores de fondos mutuos de renta fija en Chile no cuentan con modelos que anticipen aportes y rescates, pese a que estos flujos afectan la liquidez, los precios de la deuda y el momento óptimo para emitir bonos. La tesis construye un modelo predictivo del porcentaje de aporte/rescate sobre patrimonio para las nueve categorías de fondos de renta fija local definidas por la AAFM, usando como variables explicativas las rentabilidades pasadas nominales y reales a distintos plazos. Los datos se obtuvieron por web scraping del sitio de la AAFM y cubren unos 15 años de operación diaria, con entre 3.200 y 3.700 observaciones por categoría. Tras limpieza, test ADF y descomposición aditiva, se compararon ARIMA y SARIMAX con rentabilidades como exógenas, y luego Decision Tree, Random Forest, XGBoost, SVM, GRU y LSTM. SARIMAX superó a ARIMA en la mayoría de las categorías (en fondos menores a 365 días en pesos el RMSE a 1 día bajó de 0,059 a 0,0014) y XGBoost resultó el modelo más robusto para predicción multihorizonte, con RMSE entre 0,23 y 0,50 puntos porcentuales en fondos de duración media y larga. Los fondos menores a 90 días siguen siendo impredecibles (RMSE cercano a 10,8). El trabajo entrega una guía de selección de modelos por perfil de fondo útil para portfolio managers, emisores de deuda y bancos de inversión.</t>
+          <t>La tesis estudia qué elementos de las respuestas empresariales a reclamos se asocian con mayor satisfacción del consumidor en fabricantes de alimentos de Brasil. Se basa en la teoría de justicia percibida y en la plataforma pública SENACON, que registra reclamo, respuesta y evaluación del consumidor (escala 1 a 5). La base completa comprende 5.465 reclamos del período 2020 a 2024, concentrados en Nescafé Dolce Gusto, Nestlé y Nespresso (70 % del total), y una muestra estratificada de 300 casos fue codificada manualmente por dos expertos como gold standard. Los modelos Gemini y Gemma, en modo zero-shot y con textos traducidos al inglés, puntuaron compensación y empatía en escalas de 0 a 100; Gemini alcanzó 92,7 % de accuracy en compensación (kappa 0,77) y 81,0 % en empatía. Las correlaciones con la satisfacción resultaron prácticamente nulas (r = 0,02 para compensación, r = 0,06 para empatía; diferencia de +0,09 puntos, p = 0,74), por lo que la hipótesis central se rechaza. El tiempo de respuesta muestra un efecto descriptivo y el canal y el tipo de problema moderan la efectividad. El trabajo aporta un protocolo replicable de validación híbrida humano-LLM y evidencia de que la calidad y contextualización de la respuesta importan más que la mera presencia de empatía o compensación.</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>Fixed-income mutual fund managers in Chile lack models that anticipate when clients will contribute or redeem, even though these flows affect liquidity, the price of debt instruments and the optimal timing for issuing bonds or buying portfolios. The thesis builds a predictive model of the contribution/redemption percentage over fund assets for the nine local fixed-income fund categories defined by the AAFM, using past nominal and real returns at several horizons as explanatory variables. Data were obtained by web scraping the AAFM website and cover about 15 years of daily operations, with between 3,200 and 3,700 observations per category. After cleaning, ADF tests and additive decomposition, ARIMA and SARIMAX with returns as exogenous variables were compared, followed by Decision Tree, Random Forest, XGBoost, SVM, GRU and LSTM. SARIMAX outperformed ARIMA in most categories (for funds under 365 days in pesos the 1-day RMSE fell from 0.059 to 0.0014) and XGBoost proved the most robust model for multi-horizon prediction, with RMSE between 0.23 and 0.50 percentage points in medium- and long-duration funds. Funds under 90 days remain unpredictable (RMSE close to 10.8). The work delivers a model selection guide by fund profile useful for portfolio managers, debt issuers and investment banks.</t>
+          <t>This thesis examines which communicational elements of corporate responses to complaints are associated with higher consumer satisfaction in Brazil's food product manufacturing sector. It builds on perceived justice theory (distributive, interactional and procedural) and uses the public SENACON platform (consumidor.gov.br), which records the complaint, the company's response and the consumer's rating on a 1 to 5 scale. The full dataset comprises 5,465 complaints from 2020 to 2024, concentrated in Nescafé Dolce Gusto, Nestlé and Nespresso (70% of the total), and a stratified sample of 300 cases was manually coded by two experts as a gold standard. The Gemini and Gemma models, in zero-shot mode and with texts translated into English, scored compensation and empathy on 0 to 100 scales; Gemini reached 92.7% accuracy on compensation (kappa 0.77) and 81.0% on empathy. Correlations with satisfaction were practically null (r = 0.02 for compensation, r = 0.06 for empathy; a difference of +0.09 points, p = 0.74), so the central hypothesis is rejected. Response time shows a descriptive effect (2.74 to 2.58 points), and sales channel and problem type moderate effectiveness. The work contributes a replicable human-LLM hybrid validation protocol and evidence that response quality and contextualization matter more than the mere presence of empathy or compensation.</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>Se modelaron nueve categorías de fondos de renta fija local con unos 15 años de datos diarios obtenidos por web scraping de la AAFM.</t>
+          <t>Se analizaron 5.465 reclamos de fabricantes de alimentos registrados en SENACON entre 2020 y 2024, con 300 casos codificados manualmente como gold standard.</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>Todas las series de porcentaje de aporte/rescate resultaron estacionarias según el test ADF, con p-valores inferiores a 0,01.</t>
+          <t>Gemini en modo zero-shot alcanzó 92,7 % de accuracy y kappa 0,77 en compensación, y 81,0 % de accuracy en empatía frente a codificadores humanos.</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>SARIMAX con rentabilidades pasadas como exógenas superó a ARIMA en la mayoría de las categorías, bajando el RMSE a 1 día de 0,059 a 0,0014.</t>
+          <t>La presencia de compensación o empatía casi no se correlaciona con la satisfacción (r = 0,02 y r = 0,06), rechazando la hipótesis central.</t>
         </is>
       </c>
       <c r="AE13" s="2" t="inlineStr">
         <is>
-          <t>XGBoost fue el modelo más robusto para predicción multihorizonte, con RMSE entre 0,23 y 0,50 puntos porcentuales en fondos de duración media y larga.</t>
+          <t>La satisfacción cae de 2,74 a 2,58 puntos cuando la respuesta demora más de 10 días, aunque la correlación lineal es débil.</t>
         </is>
       </c>
       <c r="AF13" s="2" t="inlineStr">
         <is>
-          <t>Los fondos de deuda menores a 90 días resultaron impredecibles para todos los modelos, con RMSE cercano a 10,8 puntos porcentuales.</t>
+          <t>En reclamos de seguridad alimentaria ninguna respuesta fue plenamente transparente; 73,9 % usó comunicación técnica sin asumir responsabilidad y 26,1 % fue evasiva.</t>
         </is>
       </c>
       <c r="AG13" s="2" t="inlineStr">
         <is>
-          <t>Nine local fixed-income fund categories were modeled with about 15 years of daily data obtained by web scraping the AAFM website.</t>
+          <t>5,465 complaints against food manufacturers recorded in SENACON between 2020 and 2024 were analyzed, with 300 cases manually coded as a gold standard.</t>
         </is>
       </c>
       <c r="AH13" s="2" t="inlineStr">
         <is>
-          <t>All contribution/redemption percentage series were stationary according to the ADF test, with p-values below 0.01.</t>
+          <t>Gemini in zero-shot mode reached 92.7% accuracy and kappa 0.77 on compensation, and 81.0% accuracy on empathy against human coders.</t>
         </is>
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>SARIMAX with past returns as exogenous variables outperformed ARIMA in most categories, cutting the 1-day RMSE from 0.059 to 0.0014.</t>
+          <t>The presence of compensation or empathy is barely correlated with consumer satisfaction (r = 0.02 and r = 0.06), rejecting the central hypothesis.</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>XGBoost was the most robust model for multi-horizon prediction, with RMSE between 0.23 and 0.50 percentage points in medium- and long-duration funds.</t>
+          <t>Satisfaction falls from 2.74 to 2.58 points when the response takes more than 10 days, although the linear correlation is weak.</t>
         </is>
       </c>
       <c r="AK13" s="2" t="inlineStr">
         <is>
-          <t>Debt funds under 90 days proved unpredictable for every model, with RMSE close to 10.8 percentage points.</t>
+          <t>In food safety complaints no response was fully transparent; 73.9% used technical communication without accepting responsibility and 26.1% were evasive.</t>
         </is>
       </c>
       <c r="AL13" s="2" t="inlineStr">
         <is>
-          <t>https://repositorio.uchile.cl/handle/2250/207933</t>
+          <t>https://repositorio.uchile.cl/handle/2250/207953</t>
         </is>
       </c>
       <c r="AM13" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2025-gajardo.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-sepulveda.pdf</t>
         </is>
       </c>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>El texto no nombra explícitamente el lenguaje; se infiere Python por las referencias a MinMaxScaler, seasonal_decompose, DataFrame, Adam y EarlyStopping. Se menciona que el modelo se orienta a un portfolio manager de un banco de inversión, pero no se identifica ninguna organización. Las tablas de machine learning (5 a 10) reportan RMSE pero el texto las llama repetidamente 'rentabilidad', lo que genera confusión; el resumen ejecutivo repite ese uso. Hay dos tablas numeradas como Tabla 2 y los gráficos ARIMA/SARIMAX y los boxplots del anexo no se extrajeron del PDF.</t>
+          <t>El texto tiene inconsistencias internas: la síntesis de P4 reporta 720 reclamos de seguridad alimentaria con 45/32/23 % de estrategias y notas 3,4/2,7/2,1, mientras que la sección correspondiente reporta 72 casos, 26,1 % evasivas, 73,9 % técnicas y cero transparentes (se usó esta última versión en los highlights). La base completa aparece como 5.465 y también como 5.468 evaluaciones. Hay párrafos duplicados en la sección de seguridad alimentaria y dos secciones tituladas Conclusiones. El OE5 se cita en la metodología pero no está en la lista de objetivos. No se nombra explícitamente el lenguaje de programación; el anexo muestra prompts en sintaxis tipo Python (SYSTEM_CONTENT = """..."""). Declara uso de Claude, ChatGPT y Gemini para mejorar la redacción.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2025-ceroni</t>
+          <t>2025-gajardo</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2940,11 +2932,11 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Nicolás Simón Ceroni Perisic</t>
+          <t>Juan Francisco Gajardo Mejías</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -2953,7 +2945,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -2961,48 +2953,48 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Richard Weber</t>
+          <t>Sebastián Alejandro Maldonado Alarcón</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Jaime Andrés Miranda Pino; David Alejandro Díaz Solís</t>
+          <t>David Alejandro Díaz Solís; Alejandro Adrián Bernales Silva</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>CervecIA: una cerveza obtenida utilizando técnicas analíticas</t>
+          <t>Modelamiento predictivo de aportes y rescates de fondos mutuos de renta fija local</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>CervecIA: a beer obtained using analytical techniques</t>
+          <t>Predictive modeling of contributions and redemptions in local fixed-income mutual funds</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>alimentos; industria</t>
+          <t>finanzas; banca</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>regresión; análisis descriptivo e inferencial</t>
+          <t>series de tiempo / forecasting; regresión; análisis descriptivo e inferencial</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Extra Trees Regressor; PyCaret AutoML; SHAP; Decision Tree; Random Oversampling; Support Vector Machine; Random Forest; KNN; Neural Network</t>
+          <t>ARIMA; SARIMAX; Decision Tree; Random Forest; XGBoost; SVM; LSTM; GRU; ADF test; Seasonal decomposition</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Python; PyCaret; SHAP; scikit-learn; pandas; NumPy; Matplotlib; Seaborn; Requests; Beautiful Soup; SQLite</t>
+          <t>Python; Excel</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Recetas de cerveza de Brewer's Friend (Brewer's Friend (web scraping))</t>
+          <t>Aportes, rescates y rentabilidades de fondos mutuos de renta fija local (AAFM) (Web scraping del sitio de la Asociación de Administradoras de Fondos Mutuos de Chile (AAFM))</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -3018,104 +3010,104 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>La tesis busca reducir las pérdidas de materias primas, agua, energía y emisiones asociadas a los lotes de prueba fallidos en cervecerías artesanales, un beneficio ambiental y de eficiencia derivado de una aplicación comercial.</t>
+          <t>La aplicación es comercial (gestión de fondos, emisión de deuda e inversión), pero anticipar rescates masivos ayuda a reducir riesgos de liquidez y ventas forzadas, lo que contribuye a la estabilidad del sistema financiero chileno.</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>The thesis aims to reduce the waste of raw materials, water, energy and emissions linked to failed test batches in craft breweries, an environmental and efficiency benefit derived from a commercial application.</t>
+          <t>The application is commercial (fund management, debt issuance and investment), but anticipating mass redemptions helps reduce liquidity risk and fire sales, which contributes to the stability of the Chilean financial system.</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>cerveza artesanal; diseño de recetas; web scraping; AutoML; SHAP; regresión; explicabilidad</t>
+          <t>fondos mutuos; renta fija; aportes y rescates; series de tiempo; SARIMAX; XGBoost; redes recurrentes</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>craft beer; recipe design; web scraping; AutoML; SHAP; regression; explainability</t>
+          <t>mutual funds; fixed income; contributions and redemptions; time series; SARIMAX; XGBoost; recurrent neural networks</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>El diseño de recetas de cerveza artesanal se basa en prueba y error: una receta nueva se elabora entre 6 y 10 veces y entre el 5 % y el 10 % de la producción se pierde en lotes fallidos. Esta tesis construye un modelo que predice el puntaje (1 a 5) de una receta a partir de sus maltas, lúpulos y variables de proceso. Mediante web scraping de Brewer's Friend se recopilaron 10.360 recetas (185 estilos, 693 maltas y 273 lúpulos) en una base SQLite. Como 8.934 recetas no tenían puntaje, se estimó con un Extra Trees Regressor a partir de visitas y elaboraciones (R cuadrado de 0,923 y MAPE de 2,82 %). Luego se normalizaron unidades por litro, se agruparon maltas en 18 macrocategorías y se construyó una función en Python que, por estilo, balancea los datos, compara modelos con PyCaret, explica el mejor con SHAP y extrae reglas con un árbol de decisión. Para American Pale Ale (747 recetas) el Extra Trees obtuvo R cuadrado de 0,92 y MAPE de 4 %; en los 10 estilos con más recetas fue siempre el mejor modelo, con MAPE bajo 8 %. Los hallazgos se tradujeron en una receta de 23 litros elaborada realmente, mostrando que la analítica puede apoyar al maestro cervecero en el diseño de recetas.</t>
+          <t>Los gestores de fondos mutuos de renta fija en Chile no cuentan con modelos que anticipen aportes y rescates, pese a que estos flujos afectan la liquidez, los precios de la deuda y el momento óptimo para emitir bonos. La tesis construye un modelo predictivo del porcentaje de aporte/rescate sobre patrimonio para las nueve categorías de fondos de renta fija local definidas por la AAFM, usando como variables explicativas las rentabilidades pasadas nominales y reales a distintos plazos. Los datos se obtuvieron por web scraping del sitio de la AAFM y cubren unos 15 años de operación diaria, con entre 3.200 y 3.700 observaciones por categoría. Tras limpieza, test ADF y descomposición aditiva, se compararon ARIMA y SARIMAX con rentabilidades como exógenas, y luego Decision Tree, Random Forest, XGBoost, SVM, GRU y LSTM. SARIMAX superó a ARIMA en la mayoría de las categorías (en fondos menores a 365 días en pesos el RMSE a 1 día bajó de 0,059 a 0,0014) y XGBoost resultó el modelo más robusto para predicción multihorizonte, con RMSE entre 0,23 y 0,50 puntos porcentuales en fondos de duración media y larga. Los fondos menores a 90 días siguen siendo impredecibles (RMSE cercano a 10,8). El trabajo entrega una guía de selección de modelos por perfil de fondo útil para portfolio managers, emisores de deuda y bancos de inversión.</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>Craft beer recipe design relies on trial and error: a new recipe is brewed 6 to 10 times and between 5% and 10% of production is lost in failed batches, wasting raw materials, water and energy. This thesis builds a model that predicts a recipe's score (1 to 5) from its malts, hops and process variables. Through web scraping of Brewer's Friend, 10,360 recipes were collected (185 styles, 693 malts and 273 hops) into a SQLite database. Since 8,934 recipes had no score, it was estimated with an Extra Trees Regressor from views and brews (R squared of 0.923 and MAPE of 2.82%). Units were then normalized per liter, malts were grouped into 18 macro-categories, and a Python function was built that, per style, balances the data, compares models with PyCaret, explains the best one with SHAP and extracts rules with a decision tree. For American Pale Ale (747 recipes) Extra Trees achieved an R squared of 0.92 and a MAPE of 4%; across the 10 styles with the most recipes it was always the best model, with MAPE below 8%. The findings were turned into a 23-liter recipe that was actually brewed, showing that analytics can support brewmasters in recipe design.</t>
+          <t>Fixed-income mutual fund managers in Chile lack models that anticipate when clients will contribute or redeem, even though these flows affect liquidity, the price of debt instruments and the optimal timing for issuing bonds or buying portfolios. The thesis builds a predictive model of the contribution/redemption percentage over fund assets for the nine local fixed-income fund categories defined by the AAFM, using past nominal and real returns at several horizons as explanatory variables. Data were obtained by web scraping the AAFM website and cover about 15 years of daily operations, with between 3,200 and 3,700 observations per category. After cleaning, ADF tests and additive decomposition, ARIMA and SARIMAX with returns as exogenous variables were compared, followed by Decision Tree, Random Forest, XGBoost, SVM, GRU and LSTM. SARIMAX outperformed ARIMA in most categories (for funds under 365 days in pesos the 1-day RMSE fell from 0.059 to 0.0014) and XGBoost proved the most robust model for multi-horizon prediction, with RMSE between 0.23 and 0.50 percentage points in medium- and long-duration funds. Funds under 90 days remain unpredictable (RMSE close to 10.8). The work delivers a model selection guide by fund profile useful for portfolio managers, debt issuers and investment banks.</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>Se recopilaron 10.360 recetas de cerveza desde Brewer's Friend mediante web scraping en Python, almacenadas en una base SQLite de 8 tablas.</t>
+          <t>Se modelaron nueve categorías de fondos de renta fija local con unos 15 años de datos diarios obtenidos por web scraping de la AAFM.</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>Un Extra Trees Regressor estimó el puntaje faltante de 8.934 recetas a partir de visitas y elaboraciones, con R cuadrado de 0,923.</t>
+          <t>Todas las series de porcentaje de aporte/rescate resultaron estacionarias según el test ADF, con p-valores inferiores a 0,01.</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>Una función automatizada por estilo balancea datos, compara modelos con PyCaret, explica con SHAP y extrae reglas con un árbol de decisión.</t>
+          <t>SARIMAX con rentabilidades pasadas como exógenas superó a ARIMA en la mayoría de las categorías, bajando el RMSE a 1 día de 0,059 a 0,0014.</t>
         </is>
       </c>
       <c r="AE14" s="2" t="inlineStr">
         <is>
-          <t>Para American Pale Ale (747 recetas) el modelo alcanzó R cuadrado de 0,92 y MAPE de 4 %, y fue el mejor en 10 estilos.</t>
+          <t>XGBoost fue el modelo más robusto para predicción multihorizonte, con RMSE entre 0,23 y 0,50 puntos porcentuales en fondos de duración media y larga.</t>
         </is>
       </c>
       <c r="AF14" s="2" t="inlineStr">
         <is>
-          <t>Los hallazgos SHAP (lúpulo Magnum en bajas dosis, malta Pale base moderada) se tradujeron en una receta de 23 litros elaborada realmente.</t>
+          <t>Los fondos de deuda menores a 90 días resultaron impredecibles para todos los modelos, con RMSE cercano a 10,8 puntos porcentuales.</t>
         </is>
       </c>
       <c r="AG14" s="2" t="inlineStr">
         <is>
-          <t>10,360 beer recipes were collected from Brewer's Friend through web scraping in Python and stored in an 8-table SQLite database.</t>
+          <t>Nine local fixed-income fund categories were modeled with about 15 years of daily data obtained by web scraping the AAFM website.</t>
         </is>
       </c>
       <c r="AH14" s="2" t="inlineStr">
         <is>
-          <t>An Extra Trees Regressor estimated the missing score of 8,934 recipes from views and brews, with an R squared of 0.923.</t>
+          <t>All contribution/redemption percentage series were stationary according to the ADF test, with p-values below 0.01.</t>
         </is>
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>An automated per-style function balances the data, compares models with PyCaret, explains them with SHAP and extracts rules with a decision tree.</t>
+          <t>SARIMAX with past returns as exogenous variables outperformed ARIMA in most categories, cutting the 1-day RMSE from 0.059 to 0.0014.</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>For American Pale Ale (747 recipes) the model reached an R squared of 0.92 and MAPE of 4%, the best across 10 styles.</t>
+          <t>XGBoost was the most robust model for multi-horizon prediction, with RMSE between 0.23 and 0.50 percentage points in medium- and long-duration funds.</t>
         </is>
       </c>
       <c r="AK14" s="2" t="inlineStr">
         <is>
-          <t>SHAP findings (Magnum hops in small doses, moderate base Pale malt) were turned into a 23-liter recipe that was actually brewed.</t>
+          <t>Debt funds under 90 days proved unpredictable for every model, with RMSE close to 10.8 percentage points.</t>
         </is>
       </c>
       <c r="AL14" s="2" t="inlineStr">
         <is>
-          <t>https://repositorio.uchile.cl/handle/2250/207929</t>
+          <t>https://repositorio.uchile.cl/handle/2250/207933</t>
         </is>
       </c>
       <c r="AM14" s="2" t="inlineStr">
         <is>
-          <t>https://man-thesis-catalog.vercel.app/pdf/2025-ceroni.pdf</t>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-gajardo.pdf</t>
         </is>
       </c>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>Documento rotulado como Taller AFE, Informe 3 (AFE para optar al grado), profesor guía Richard Weber, 2025. Resumen ejecutivo en español e inglés incluido. Las tablas y gráficos aparecen como texto al final. Inconsistencia menor: el texto dice que todos los R cuadrado por estilo superan 0,82, pero la tabla muestra Witbier con 0,77. Los modelos de clasificación (KNN, Random Forest, redes neuronales, SVM) se probaron como análisis alternativo y se descartaron.</t>
+          <t>El texto no nombra explícitamente el lenguaje; se infiere Python por las referencias a MinMaxScaler, seasonal_decompose, DataFrame, Adam y EarlyStopping. Se menciona que el modelo se orienta a un portfolio manager de un banco de inversión, pero no se identifica ninguna organización. Las tablas de machine learning (5 a 10) reportan RMSE pero el texto las llama repetidamente 'rentabilidad', lo que genera confusión; el resumen ejecutivo repite ese uso. Hay dos tablas numeradas como Tabla 2 y los gráficos ARIMA/SARIMAX y los boxplots del anexo no se extrajeron del PDF.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2025-yanez</t>
+          <t>2025-ceroni</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -3130,7 +3122,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Christian René Andrés Yáñez Cornejo</t>
+          <t>Nicolás Simón Ceroni Perisic</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -3151,156 +3143,346 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>David Alejandro Díaz Solís</t>
+          <t>Richard Weber</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t>Jaime Andrés Miranda Pino; David Alejandro Díaz Solís</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>CervecIA: una cerveza obtenida utilizando técnicas analíticas</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>CervecIA: a beer obtained using analytical techniques</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>alimentos; industria</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>regresión; análisis descriptivo e inferencial</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Extra Trees Regressor; PyCaret AutoML; SHAP; Decision Tree; Random Oversampling; Support Vector Machine; Random Forest; KNN; Neural Network</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Python; PyCaret; SHAP; scikit-learn; pandas; NumPy; Matplotlib; Seaborn; Requests; Beautiful Soup; SQLite</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Recetas de cerveza de Brewer's Friend (Brewer's Friend (web scraping))</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>indirect</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>La tesis busca reducir las pérdidas de materias primas, agua, energía y emisiones asociadas a los lotes de prueba fallidos en cervecerías artesanales, un beneficio ambiental y de eficiencia derivado de una aplicación comercial.</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>The thesis aims to reduce the waste of raw materials, water, energy and emissions linked to failed test batches in craft breweries, an environmental and efficiency benefit derived from a commercial application.</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>cerveza artesanal; diseño de recetas; web scraping; AutoML; SHAP; regresión; explicabilidad</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>craft beer; recipe design; web scraping; AutoML; SHAP; regression; explainability</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>El diseño de recetas de cerveza artesanal se basa en prueba y error: una receta nueva se elabora entre 6 y 10 veces y entre el 5 % y el 10 % de la producción se pierde en lotes fallidos. Esta tesis construye un modelo que predice el puntaje (1 a 5) de una receta a partir de sus maltas, lúpulos y variables de proceso. Mediante web scraping de Brewer's Friend se recopilaron 10.360 recetas (185 estilos, 693 maltas y 273 lúpulos) en una base SQLite. Como 8.934 recetas no tenían puntaje, se estimó con un Extra Trees Regressor a partir de visitas y elaboraciones (R cuadrado de 0,923 y MAPE de 2,82 %). Luego se normalizaron unidades por litro, se agruparon maltas en 18 macrocategorías y se construyó una función en Python que, por estilo, balancea los datos, compara modelos con PyCaret, explica el mejor con SHAP y extrae reglas con un árbol de decisión. Para American Pale Ale (747 recetas) el Extra Trees obtuvo R cuadrado de 0,92 y MAPE de 4 %; en los 10 estilos con más recetas fue siempre el mejor modelo, con MAPE bajo 8 %. Los hallazgos se tradujeron en una receta de 23 litros elaborada realmente, mostrando que la analítica puede apoyar al maestro cervecero en el diseño de recetas.</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>Craft beer recipe design relies on trial and error: a new recipe is brewed 6 to 10 times and between 5% and 10% of production is lost in failed batches, wasting raw materials, water and energy. This thesis builds a model that predicts a recipe's score (1 to 5) from its malts, hops and process variables. Through web scraping of Brewer's Friend, 10,360 recipes were collected (185 styles, 693 malts and 273 hops) into a SQLite database. Since 8,934 recipes had no score, it was estimated with an Extra Trees Regressor from views and brews (R squared of 0.923 and MAPE of 2.82%). Units were then normalized per liter, malts were grouped into 18 macro-categories, and a Python function was built that, per style, balances the data, compares models with PyCaret, explains the best one with SHAP and extracts rules with a decision tree. For American Pale Ale (747 recipes) Extra Trees achieved an R squared of 0.92 and a MAPE of 4%; across the 10 styles with the most recipes it was always the best model, with MAPE below 8%. The findings were turned into a 23-liter recipe that was actually brewed, showing that analytics can support brewmasters in recipe design.</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>Se recopilaron 10.360 recetas de cerveza desde Brewer's Friend mediante web scraping en Python, almacenadas en una base SQLite de 8 tablas.</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>Un Extra Trees Regressor estimó el puntaje faltante de 8.934 recetas a partir de visitas y elaboraciones, con R cuadrado de 0,923.</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>Una función automatizada por estilo balancea datos, compara modelos con PyCaret, explica con SHAP y extrae reglas con un árbol de decisión.</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>Para American Pale Ale (747 recetas) el modelo alcanzó R cuadrado de 0,92 y MAPE de 4 %, y fue el mejor en 10 estilos.</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>Los hallazgos SHAP (lúpulo Magnum en bajas dosis, malta Pale base moderada) se tradujeron en una receta de 23 litros elaborada realmente.</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>10,360 beer recipes were collected from Brewer's Friend through web scraping in Python and stored in an 8-table SQLite database.</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="inlineStr">
+        <is>
+          <t>An Extra Trees Regressor estimated the missing score of 8,934 recipes from views and brews, with an R squared of 0.923.</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t>An automated per-style function balances the data, compares models with PyCaret, explains them with SHAP and extracts rules with a decision tree.</t>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>For American Pale Ale (747 recipes) the model reached an R squared of 0.92 and MAPE of 4%, the best across 10 styles.</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="inlineStr">
+        <is>
+          <t>SHAP findings (Magnum hops in small doses, moderate base Pale malt) were turned into a 23-liter recipe that was actually brewed.</t>
+        </is>
+      </c>
+      <c r="AL15" s="2" t="inlineStr">
+        <is>
+          <t>https://repositorio.uchile.cl/handle/2250/207929</t>
+        </is>
+      </c>
+      <c r="AM15" s="2" t="inlineStr">
+        <is>
+          <t>https://man-thesis-catalog.vercel.app/pdf/2025-ceroni.pdf</t>
+        </is>
+      </c>
+      <c r="AN15" s="2" t="inlineStr">
+        <is>
+          <t>Documento rotulado como Taller AFE, Informe 3 (AFE para optar al grado), profesor guía Richard Weber, 2025. Resumen ejecutivo en español e inglés incluido. Las tablas y gráficos aparecen como texto al final. Inconsistencia menor: el texto dice que todos los R cuadrado por estilo superan 0,82, pero la tabla muestra Witbier con 0,77. Los modelos de clasificación (KNN, Random Forest, redes neuronales, SVM) se probaron como análisis alternativo y se descartaron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2025-yanez</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>INMEDIATO</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Christian René Andrés Yáñez Cornejo</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>MAN WK</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>David Alejandro Díaz Solís</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>Richard Weber; Jaime Andrés Miranda Pino</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Modelos predictivos de mortalidad: comparación de técnicas tradicionales y algoritmos de machine learning</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Predictive mortality models: a comparison of traditional techniques and machine learning algorithms</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>finanzas; servicios</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>clasificación; series de tiempo / forecasting; análisis descriptivo e inferencial</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>XGBoost; LightGBM; Gradient Boosting; Multilayer Perceptron; LSTM; GRU; SARIMA; SHAP; SMOTE; Mortality tables (A/E ratio)</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>Python; PyCaret; Keras; TensorFlow; pandas; matplotlib; scikit-learn; Jupyter Notebook</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Cartera de rentas vitalicias de la aseguradora (datos internos de una compañía multinacional de seguros que opera en Chile); Serie mensual de fallecimientos de la cartera (datos internos de la misma compañía de seguros (archivo muerte_series_temporales.csv))</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>Compañía multinacional de seguros que opera en Chile (no identificada por nombre)</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>indirect</t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>La aplicación es comercial (tarificación y reservas de rentas vitalicias), pero una mejor estimación de la mortalidad protege la suficiencia de reservas y permite precios más justos para los pensionados.</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>The application is commercial (annuity pricing and reserving), but better mortality estimation protects reserve adequacy and allows fairer prices for pensioners.</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>mortalidad; rentas vitalicias; tablas de mortalidad; XGBoost; LSTM; series temporales; seguros</t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>mortality; life annuities; mortality tables; XGBoost; LSTM; time series; insurance</t>
         </is>
       </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>La tesis compara la capacidad de las tablas de mortalidad tradicionales frente a algoritmos de aprendizaje supervisado y modelos de series temporales para proyectar la mortalidad en la cartera de rentas vitalicias de una compañía multinacional de seguros que opera en Chile, con más de 270.000 asegurados segmentados en causantes, beneficiarios e inválidos. Los datos internos a diciembre de 2023 incluyen edad, sexo, nivel de prima, estado conyugal, número de hijos, invalidez y región, y se preprocesaron con PyCaret (one-hot, normalización min-max, SMOTE y validación cruzada estratificada de 10 folds). Se entrenaron XGBoost, LightGBM, Gradient Boosting, una red densa, LSTM y GRU como clasificadores, y SARIMA, LSTM y GRU sobre la serie mensual de fallecimientos 1990 a 2023, con SHAP para interpretar los clasificadores. XGBoost resultó el mejor clasificador (AUC 0,92, recall 0,78 en la clase fallecido) y LSTM el mejor modelo de serie temporal, con un MSE muy inferior al de SARIMA (3.314,68). Evaluados fuera de muestra con datos reales de enero a junio de 2024 mediante la métrica A/E, XGBoost fue el más estable (A/E promedio 103 %) y superó a la tabla de mortalidad en totales, causantes y beneficiarios, mientras que ningún modelo logró predecir bien el segmento de inválidos. Se concluye que los modelos complementan, pero no reemplazan, las tablas actuariales para tarificación y reservas.</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>This thesis compares the ability of traditional mortality tables against supervised learning algorithms and time series models to project mortality in the annuity portfolio of a multinational insurance company operating in Chile, with more than 270,000 policyholders segmented into annuitants, beneficiaries and disabled members. Internal data as of December 2023 include age, sex, premium level, marital status, number of children, disability and region, and were preprocessed with PyCaret (one-hot encoding, min-max normalization, SMOTE and 10-fold stratified cross-validation). XGBoost, LightGBM, Gradient Boosting, a dense network, LSTM and GRU were trained as classifiers, and SARIMA, LSTM and GRU on the monthly series of deaths from 1990 to 2023, with SHAP used to interpret the classifiers. XGBoost was the best classifier (AUC 0.92, recall 0.78 on the deceased class) and LSTM the best time series model, with an MSE far below that of SARIMA (3,314.68). Evaluated out of sample on actual data from January to June 2024 using the A/E metric, XGBoost was the most stable (average A/E of 103%) and outperformed the mortality table for totals, annuitants and beneficiaries, while no model predicted the disabled segment well. The thesis concludes that these models complement, but do not replace, actuarial tables for pricing and reserving.</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>Analiza la cartera de rentas vitalicias de una aseguradora multinacional en Chile con 270.438 asegurados, de los cuales 17,8 % han fallecido.</t>
         </is>
       </c>
-      <c r="AC15" s="2" t="inlineStr">
+      <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>XGBoost fue el mejor clasificador de mortalidad individual, con AUC 0,92, recall 0,78 y accuracy 0,83 en el conjunto de prueba.</t>
         </is>
       </c>
-      <c r="AD15" s="2" t="inlineStr">
+      <c r="AD16" s="2" t="inlineStr">
         <is>
           <t>En series temporales mensuales 1990 a 2023, LSTM y GRU superaron a SARIMA (2,1,2)(1,1,1,12), cuyo MSE fue 3.314,68 frente a 824,35.</t>
         </is>
       </c>
-      <c r="AE15" s="2" t="inlineStr">
+      <c r="AE16" s="2" t="inlineStr">
         <is>
           <t>Validado con datos reales de enero a junio de 2024, XGBoost obtuvo un A/E promedio de 103 %, más estable que la tabla de mortalidad.</t>
         </is>
       </c>
-      <c r="AF15" s="2" t="inlineStr">
+      <c r="AF16" s="2" t="inlineStr">
         <is>
           <t>SHAP confirma que edad, sexo masculino, invalidez, ausencia de cónyuge y prima baja elevan el riesgo de fallecimiento en todos los modelos.</t>
         </is>
       </c>
-      <c r="AG15" s="2" t="inlineStr">
+      <c r="AG16" s="2" t="inlineStr">
         <is>
           <t>Analyzes the annuity portfolio of a multinational insurer in Chile with 270,438 policyholders, of whom 17.8% have died.</t>
         </is>
       </c>
-      <c r="AH15" s="2" t="inlineStr">
+      <c r="AH16" s="2" t="inlineStr">
         <is>
           <t>XGBoost was the best individual mortality classifier, with AUC 0.92, recall 0.78 and accuracy 0.83 on the test set.</t>
         </is>
       </c>
-      <c r="AI15" s="2" t="inlineStr">
+      <c r="AI16" s="2" t="inlineStr">
         <is>
           <t>On monthly time series from 1990 to 2023, LSTM and GRU outperformed SARIMA (2,1,2)(1,1,1,12), whose MSE was 3,314.68 versus 824.35.</t>
         </is>
       </c>
-      <c r="AJ15" s="2" t="inlineStr">
+      <c r="AJ16" s="2" t="inlineStr">
         <is>
           <t>Validated on actual data from January to June 2024, XGBoost achieved an average A/E of 103%, more stable than the mortality table.</t>
         </is>
       </c>
-      <c r="AK15" s="2" t="inlineStr">
+      <c r="AK16" s="2" t="inlineStr">
         <is>
           <t>SHAP confirms that age, male sex, disability, absence of a spouse and low premium raise the risk of death across all models.</t>
         </is>
       </c>
-      <c r="AL15" s="2" t="inlineStr">
+      <c r="AL16" s="2" t="inlineStr">
         <is>
           <t>https://repositorio.uchile.cl/handle/2250/207957</t>
         </is>
       </c>
-      <c r="AM15" s="2" t="inlineStr">
+      <c r="AM16" s="2" t="inlineStr">
         <is>
           <t>https://man-thesis-catalog.vercel.app/pdf/2025-yanez.pdf</t>
         </is>
       </c>
-      <c r="AN15" s="2" t="inlineStr">
+      <c r="AN16" s="2" t="inlineStr">
         <is>
           <t>Informe final fechado en enero de 2025. El texto extraído perdió las ecuaciones y los contenidos de varias figuras y tablas; algunas tablas de resultados (A/E mensuales 2024) solo aparecen como títulos. Se detecta una inconsistencia menor: el MSE 824,35 se reporta para GRU y luego se atribuye a LSTM y GRU en conjunto. El autor no entrega el MSE numérico del LSTM de serie temporal.</t>
         </is>
@@ -3317,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3489,103 +3671,103 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon</t>
+          <t>2026-astudillo</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Bastián Antonio Celedón Aguirre</t>
+          <t>Nicolás Andrés Astudillo Molina</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Cierres ganados semanales del CRM corporativo</t>
+          <t>Encuesta CASEN 2022</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weekly won deals from the corporate CRM</t>
+          <t>CASEN 2022 survey</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>datos internos anonimizados del CRM de un corporativo de tecnologías de información (B2B)</t>
+          <t>CASEN 2022, Ministerio de Desarrollo Social y Familia (Centro de Encuestas y Estudios Longitudinales)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>183 semanas, enero 2023 a junio 2026; ingreso modelable de 3.952 MM USD tras reglas de negocio</t>
+          <t>73.676 ocupados de 25 a 65 años sin factores de expansión; 14.565 (19,8 %) trabajadores forestales según rama1 (códigos 2, 16 y 17); 19 variables en el enfoque A y 42 en el enfoque B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-cabezas</t>
+          <t>2026-celedon</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cristian Rodrigo Cabezas Lepilla</t>
+          <t>Bastián Antonio Celedón Aguirre</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Indicadores de desarrollo mundial del Banco Mundial (panel de países, 1960-2023)</t>
+          <t>Cierres ganados semanales del CRM corporativo</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>World Bank development indicators (country panel, 1960-2023)</t>
+          <t>Weekly won deals from the corporate CRM</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>World Bank Open Data</t>
+          <t>datos internos anonimizados del CRM de un corporativo de tecnologías de información (B2B)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14.047 registros país-año originales, 923 tras filtrar casos completos; 16 variables finales</t>
+          <t>183 semanas, enero 2023 a junio 2026; ingreso modelable de 3.952 MM USD tras reglas de negocio</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-torres</t>
+          <t>2026-cabezas</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Claudia Alejandra Torres Fritis</t>
+          <t>Cristian Rodrigo Cabezas Lepilla</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Votos de diputados por partido y comuna (2001 a 2025)</t>
+          <t>Indicadores de desarrollo mundial del Banco Mundial (panel de países, 1960-2023)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Deputy votes by party and municipality (2001 to 2025)</t>
+          <t>World Bank development indicators (country panel, 1960-2023)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>SERVEL</t>
+          <t>World Bank Open Data</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3596,7 +3778,7 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7 elecciones de diputados, aproximadamente 346 comunas</t>
+          <t>14.047 registros país-año originales, 923 tras filtrar casos completos; 16 variables finales</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3795,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Votos presidenciales de segunda vuelta por candidato y comuna (2005 a 2025)</t>
+          <t>Votos de diputados por partido y comuna (2001 a 2025)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Presidential runoff votes by candidate and municipality (2005 to 2025)</t>
+          <t>Deputy votes by party and municipality (2001 to 2025)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3634,34 +3816,34 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6 elecciones, base comunal final de 2.069 filas x 7 columnas</t>
+          <t>7 elecciones de diputados, aproximadamente 346 comunas</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-gutierrez</t>
+          <t>2026-torres</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Jorge Andrés Gutiérrez Soto</t>
+          <t>Claudia Alejandra Torres Fritis</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Consultas de urgencia por causas respiratorias, Región de Los Lagos</t>
+          <t>Votos presidenciales de segunda vuelta por candidato y comuna (2005 a 2025)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Respiratory emergency visits, Los Lagos Region</t>
+          <t>Presidential runoff votes by candidate and municipality (2005 to 2025)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>DEIS, Ministerio de Salud de Chile (glosa Total Causas Sistema Respiratorio)</t>
+          <t>SERVEL</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -3672,7 +3854,7 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4.018 observaciones diarias, enero 2015 a diciembre 2025; entrenamiento 2015-2023 y evaluación 2024-2025</t>
+          <t>6 elecciones, base comunal final de 2.069 filas x 7 columnas</t>
         </is>
       </c>
     </row>
@@ -3689,17 +3871,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Calendario oficial de vacaciones de invierno, Región de Los Lagos</t>
+          <t>Consultas de urgencia por causas respiratorias, Región de Los Lagos</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Official winter school holiday calendar, Los Lagos Region</t>
+          <t>Respiratory emergency visits, Los Lagos Region</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Ministerio de Educación (MINEDUC)</t>
+          <t>DEIS, Ministerio de Salud de Chile (glosa Total Causas Sistema Respiratorio)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3710,34 +3892,34 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>fechas anuales 2015-2025, excluyendo 2020 y 2021</t>
+          <t>4.018 observaciones diarias, enero 2015 a diciembre 2025; entrenamiento 2015-2023 y evaluación 2024-2025</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-delrio</t>
+          <t>2026-gutierrez</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Felipe Andrés del Río Nova</t>
+          <t>Jorge Andrés Gutiérrez Soto</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Resultados oficiales de elecciones municipales y presidenciales de Chile por comuna</t>
+          <t>Calendario oficial de vacaciones de invierno, Región de Los Lagos</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Official Chilean municipal and presidential election results by municipality</t>
+          <t>Official winter school holiday calendar, Los Lagos Region</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Servicio Electoral de Chile (SERVEL)</t>
+          <t>Ministerio de Educación (MINEDUC)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3748,34 +3930,34 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>346 comunas, seis ciclos (2005, 2009, 2013, 2017, 2021 y 2025, con municipales de 2024); matriz consolidada de 12 filas por 346 comunas</t>
+          <t>fechas anuales 2015-2025, excluyendo 2020 y 2021</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-hernandez</t>
+          <t>2026-delrio</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cristian Luis Hernández Milla</t>
+          <t>Felipe Andrés del Río Nova</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Rol Semestral de Contribuciones de Bienes Raíces (archivo BRTMPNACROL)</t>
+          <t>Resultados oficiales de elecciones municipales y presidenciales de Chile por comuna</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Semiannual Real Estate Tax Roll (BRTMPNACROL file)</t>
+          <t>Official Chilean municipal and presidential election results by municipality</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Impuestos Internos (SII), Chile</t>
+          <t>Servicio Electoral de Chile (SERVEL)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3783,14 +3965,10 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>https://www4.sii.cl/sismunInternet6/?caller=DETALLE_CAT_Y_ROL_COBRO</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>archivo de ancho fijo de unos 3 GB, 117 caracteres por registro, 9,5 millones de predios, versión 2025 semestre 2; 16 semestres históricos 2018-S1 a 2025-S2 (136,6 millones de filas)</t>
+          <t>346 comunas, seis ciclos (2005, 2009, 2013, 2017, 2021 y 2025, con municipales de 2024); matriz consolidada de 12 filas por 346 comunas</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3985,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>API getPredioNacional del SII</t>
+          <t>Rol Semestral de Contribuciones de Bienes Raíces (archivo BRTMPNACROL)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>SII getPredioNacional API</t>
+          <t>Semiannual Real Estate Tax Roll (BRTMPNACROL file)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3825,10 +4003,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www4.sii.cl/sismunInternet6/?caller=DETALLE_CAT_Y_ROL_COBRO</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,55 millones de predios extraídos en 343 comunas, 7,7 GB en CSV, batch marzo 2026</t>
+          <t>archivo de ancho fijo de unos 3 GB, 117 caracteres por registro, 9,5 millones de predios, versión 2025 semestre 2; 16 semestres históricos 2018-S1 a 2025-S2 (136,6 millones de filas)</t>
         </is>
       </c>
     </row>
@@ -3845,12 +4027,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Servicio WMS de cartografía catastral del SII</t>
+          <t>API getPredioNacional del SII</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>SII cadastral WMS map service</t>
+          <t>SII getPredioNacional API</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3863,14 +4045,10 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>https://www4.sii.cl/mapasui/services/ui/wmsProxyService/call</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>tiles PNG de 256x256 px a zoom 19 (unos 0,3 m/px), 343 GeoTIFFs; 5,67 millones de polígonos vectorizados</t>
+          <t>9,55 millones de predios extraídos en 343 comunas, 7,7 GB en CSV, batch marzo 2026</t>
         </is>
       </c>
     </row>
@@ -3887,17 +4065,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Dataset predial nacional consolidado (producto de la tesis)</t>
+          <t>Servicio WMS de cartografía catastral del SII</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Consolidated national property dataset (thesis output)</t>
+          <t>SII cadastral WMS map service</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Catastral.cl</t>
+          <t>Servicio de Impuestos Internos (SII), Chile</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3907,50 +4085,54 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://catastral.cl</t>
+          <t>https://www4.sii.cl/mapasui/services/ui/wmsProxyService/call</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,55 millones de predios, 5,67 millones con geometría, Parquet y GeoJSON por comuna, unos 18 GB comprimidos</t>
+          <t>tiles PNG de 256x256 px a zoom 19 (unos 0,3 m/px), 343 GeoTIFFs; 5,67 millones de polígonos vectorizados</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2025-canete</t>
+          <t>2026-hernandez</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Nicolás Alejandro Cañete Ponce</t>
+          <t>Cristian Luis Hernández Milla</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Dotación histórica de trabajadores</t>
+          <t>Dataset predial nacional consolidado (producto de la tesis)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Historical headcount records</t>
+          <t>Consolidated national property dataset (thesis output)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>datos internos de una empresa de transporte (subsistemas de Recursos Humanos)</t>
+          <t>Catastral.cl</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://catastral.cl</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5.636 trabajadores únicos, 14 variables, enero 2022 a diciembre 2024</t>
+          <t>9,55 millones de predios, 5,67 millones con geometría, Parquet y GeoJSON por comuna, unos 18 GB comprimidos</t>
         </is>
       </c>
     </row>
@@ -3967,12 +4149,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Evaluaciones de desempeño</t>
+          <t>Dotación histórica de trabajadores</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Performance evaluations</t>
+          <t>Historical headcount records</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -3988,7 +4170,7 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14.987 registros, un registro por trabajador por año, 2021 a 2024</t>
+          <t>5.636 trabajadores únicos, 14 variables, enero 2022 a diciembre 2024</t>
         </is>
       </c>
     </row>
@@ -4005,12 +4187,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ausentismos (licencias y vacaciones)</t>
+          <t>Evaluaciones de desempeño</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Absenteeism (sick leave and vacations)</t>
+          <t>Performance evaluations</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4026,7 +4208,7 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31.657 registros mensuales, enero 2021 a diciembre 2024</t>
+          <t>14.987 registros, un registro por trabajador por año, 2021 a 2024</t>
         </is>
       </c>
     </row>
@@ -4043,12 +4225,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Compensaciones (incrementos de renta y retenciones)</t>
+          <t>Ausentismos (licencias y vacaciones)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Compensation (salary increases and retention actions)</t>
+          <t>Absenteeism (sick leave and vacations)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4064,72 +4246,72 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24.268 registros no únicos de incrementos de renta desde el año 2000, retenciones desde 2022</t>
+          <t>31.657 registros mensuales, enero 2021 a diciembre 2024</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2025-araneda</t>
+          <t>2025-canete</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Ignacio Andrés Araneda Gallardo</t>
+          <t>Nicolás Alejandro Cañete Ponce</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Base de datos de e-commerce de Olist, Brasil</t>
+          <t>Compensaciones (incrementos de renta y retenciones)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Olist Brazilian e-commerce database</t>
+          <t>Compensation (salary increases and retention actions)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Olist (Kaggle)</t>
+          <t>datos internos de una empresa de transporte (subsistemas de Recursos Humanos)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>119.143 registros y 39 atributos tras integrar 7 tablas; unos 69.000 registros sin comentario de reseña</t>
+          <t>24.268 registros no únicos de incrementos de renta desde el año 2000, retenciones desde 2022</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2025-barros</t>
+          <t>2025-araneda</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sandra Carolina Barros Henríquez</t>
+          <t>Ignacio Andrés Araneda Gallardo</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Eficiencia DEA de establecimientos educacionales chilenos (González, 2024)</t>
+          <t>Base de datos de e-commerce de Olist, Brasil</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>DEA efficiency of Chilean schools (González, 2024)</t>
+          <t>Olist Brazilian e-commerce database</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Trabajo DEA previo (González, 2024) construido con datos oficiales: SIMCE e IDPS (Mineduc / Agencia de Calidad), IVE, encuesta Mineduc-EduInclusiva y BD Superintendencia de Educación</t>
+          <t>Olist (Kaggle)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4140,34 +4322,34 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>aprox. 912 establecimientos; 7 variables DEA y 45 variables experto tras preprocesamiento; alrededor del 6 % de los establecimientos con eficiencia igual a 1</t>
+          <t>119.143 registros y 39 atributos tras integrar 7 tablas; unos 69.000 registros sin comentario de reseña</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2025-sepulveda</t>
+          <t>2025-barros</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Juan Ernesto Osvaldo Sepúlveda Alonso</t>
+          <t>Sandra Carolina Barros Henríquez</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Reclamos SENACON, categoría Fabricantes de Productos Alimenticios</t>
+          <t>Eficiencia DEA de establecimientos educacionales chilenos (González, 2024)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SENACON complaints, Food Product Manufacturers category</t>
+          <t>DEA efficiency of Chilean schools (González, 2024)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>SENACON / Consumidor.gov.br, Ministério da Justiça, Brasil</t>
+          <t>Trabajo DEA previo (González, 2024) construido con datos oficiales: SIMCE e IDPS (Mineduc / Agencia de Calidad), IVE, encuesta Mineduc-EduInclusiva y BD Superintendencia de Educación</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4175,41 +4357,37 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>https://consumidor.gov.br/pages/publicacao/externo/</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5.465 reclamos, 2020-2024, 41 variables, 27 unidades federativas; submuestra estratificada de 300 casos (julio 2020 a abril 2025) codificada manualmente</t>
+          <t>aprox. 912 establecimientos; 7 variables DEA y 45 variables experto tras preprocesamiento; alrededor del 6 % de los establecimientos con eficiencia igual a 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2025-gajardo</t>
+          <t>2025-sepulveda</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Juan Francisco Gajardo Mejías</t>
+          <t>Juan Ernesto Osvaldo Sepúlveda Alonso</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Aportes, rescates y rentabilidades de fondos mutuos de renta fija local (AAFM)</t>
+          <t>Reclamos SENACON, categoría Fabricantes de Productos Alimenticios</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Contributions, redemptions and returns of local fixed-income mutual funds (AAFM)</t>
+          <t>SENACON complaints, Food Product Manufacturers category</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Web scraping del sitio de la Asociación de Administradoras de Fondos Mutuos de Chile (AAFM)</t>
+          <t>SENACON / Consumidor.gov.br, Ministério da Justiça, Brasil</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4219,39 +4397,39 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.afm.cl/</t>
+          <t>https://consumidor.gov.br/pages/publicacao/externo/</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Unos 15 años de datos diarios; 9 categorías de fondos con entre 3.189 y 3.721 observaciones cada una tras la limpieza</t>
+          <t>5.465 reclamos, 2020-2024, 41 variables, 27 unidades federativas; submuestra estratificada de 300 casos (julio 2020 a abril 2025) codificada manualmente</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2025-ceroni</t>
+          <t>2025-gajardo</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Nicolás Simón Ceroni Perisic</t>
+          <t>Juan Francisco Gajardo Mejías</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Recetas de cerveza de Brewer's Friend</t>
+          <t>Aportes, rescates y rentabilidades de fondos mutuos de renta fija local (AAFM)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Brewer's Friend beer recipes</t>
+          <t>Contributions, redemptions and returns of local fixed-income mutual funds (AAFM)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Brewer's Friend (web scraping)</t>
+          <t>Web scraping del sitio de la Asociación de Administradoras de Fondos Mutuos de Chile (AAFM)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4259,48 +4437,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.afm.cl/</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10.360 recetas, 185 estilos, 693 maltas y 273 lúpulos; 8.934 recetas sin puntaje</t>
+          <t>Unos 15 años de datos diarios; 9 categorías de fondos con entre 3.189 y 3.721 observaciones cada una tras la limpieza</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2025-yanez</t>
+          <t>2025-ceroni</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Christian René Andrés Yáñez Cornejo</t>
+          <t>Nicolás Simón Ceroni Perisic</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Cartera de rentas vitalicias de la aseguradora</t>
+          <t>Recetas de cerveza de Brewer's Friend</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Insurer annuity portfolio</t>
+          <t>Brewer's Friend beer recipes</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>datos internos de una compañía multinacional de seguros que opera en Chile</t>
+          <t>Brewer's Friend (web scraping)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>270.438 asegurados a diciembre de 2023; 48.087 fallecidos; validación con datos reales de enero a junio de 2024</t>
+          <t>10.360 recetas, 185 estilos, 693 maltas y 273 lúpulos; 8.934 recetas sin puntaje</t>
         </is>
       </c>
     </row>
@@ -4317,17 +4499,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Serie mensual de fallecimientos de la cartera</t>
+          <t>Cartera de rentas vitalicias de la aseguradora</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Monthly deaths series of the portfolio</t>
+          <t>Insurer annuity portfolio</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>datos internos de la misma compañía de seguros (archivo muerte_series_temporales.csv)</t>
+          <t>datos internos de una compañía multinacional de seguros que opera en Chile</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -4337,6 +4519,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>270.438 asegurados a diciembre de 2023; 48.087 fallecidos; validación con datos reales de enero a junio de 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2025-yanez</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Christian René Andrés Yáñez Cornejo</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Serie mensual de fallecimientos de la cartera</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Monthly deaths series of the portfolio</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>datos internos de la misma compañía de seguros (archivo muerte_series_temporales.csv)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>408 meses, enero 1990 a diciembre 2023</t>
         </is>
@@ -4469,7 +4689,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://fen.uchile.cl/academicos/jaime-miranda/</t>
+          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/jaime-miranda</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -4507,7 +4727,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://fen.uchile.cl/academicos/felix-lizama/</t>
+          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/felix-lizama</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4697,16 +4917,16 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://daviddiazsolis.com</t>
+          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/david-diaz</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>institutional</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>3</v>
@@ -4735,7 +4955,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://fen.uchile.cl/academicos/felipe-simon/</t>
+          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/felipe-simon</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4811,7 +5031,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://fen.uchile.cl/academicos/alejandro-bernales/</t>
+          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/alejandro-bernales</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -4887,7 +5107,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://fen.uchile.cl/academicos/ariel-la-paz/</t>
+          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/ariel-la-paz</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4963,7 +5183,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://fen.uchile.cl/academicos/juan-diaz/</t>
+          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/juan-diaz</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4989,7 +5209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5017,30 +5237,30 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon; 2026-torres; 2025-canete; 2025-araneda; 2025-barros; 2025-gajardo; 2025-yanez</t>
+          <t>2026-astudillo; 2026-cabezas; 2026-torres; 2025-canete; 2025-araneda; 2025-barros; 2025-gajardo; 2025-ceroni</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-cabezas; 2026-torres; 2025-canete; 2025-araneda; 2025-barros; 2025-gajardo; 2025-ceroni</t>
+          <t>2026-astudillo; 2026-celedon; 2026-torres; 2025-canete; 2025-araneda; 2025-barros; 2025-gajardo; 2025-yanez</t>
         </is>
       </c>
     </row>
@@ -5051,11 +5271,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon; 2026-cabezas; 2025-araneda; 2025-barros; 2025-ceroni; 2025-yanez</t>
+          <t>2026-astudillo; 2026-celedon; 2026-cabezas; 2025-araneda; 2025-barros; 2025-ceroni; 2025-yanez</t>
         </is>
       </c>
     </row>
@@ -5066,18 +5286,18 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-cabezas; 2025-canete; 2025-araneda; 2025-yanez</t>
+          <t>2026-astudillo; 2026-cabezas; 2025-canete; 2025-araneda; 2025-yanez</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -5085,29 +5305,29 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-gutierrez; 2025-araneda; 2025-gajardo; 2025-yanez</t>
+          <t>2026-astudillo; 2026-celedon; 2025-canete; 2025-yanez</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>LSTM</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon; 2026-gutierrez; 2025-canete</t>
+          <t>2026-gutierrez; 2025-araneda; 2025-gajardo; 2025-yanez</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>CatBoost</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -5115,7 +5335,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon; 2025-canete; 2025-yanez</t>
+          <t>2026-celedon; 2026-gutierrez; 2025-canete</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5357,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SARIMAX</t>
+          <t>Logistic Regression</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -5145,14 +5365,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon; 2025-gajardo</t>
+          <t>2026-astudillo; 2025-canete</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>Multilayer Perceptron</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -5160,14 +5380,14 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon; 2025-yanez</t>
+          <t>2026-astudillo; 2025-yanez</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>OLS Regression</t>
+          <t>SARIMAX</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -5175,14 +5395,14 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-torres; 2026-gutierrez</t>
+          <t>2026-celedon; 2025-gajardo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SMOTE</t>
+          <t>SARIMA</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -5190,14 +5410,14 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2025-canete; 2025-yanez</t>
+          <t>2026-celedon; 2025-yanez</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GRU</t>
+          <t>OLS Regression</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -5205,44 +5425,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2025-gajardo; 2025-yanez</t>
+          <t>2026-torres; 2026-gutierrez</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Sentence Transformers</t>
+          <t>SMOTE</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2026-quintanilla</t>
+          <t>2025-canete; 2025-yanez</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>distiluse-base-multilingual-cased-v1</t>
+          <t>GRU</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-quintanilla</t>
+          <t>2025-gajardo; 2025-yanez</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>multilingual-e5-small</t>
+          <t>Sentence Transformers</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -5257,7 +5477,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>mpnet</t>
+          <t>distiluse-base-multilingual-cased-v1</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -5272,7 +5492,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TF-IDF</t>
+          <t>multilingual-e5-small</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -5287,7 +5507,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Centroid Classification</t>
+          <t>mpnet</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -5302,7 +5522,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Cosine Similarity</t>
+          <t>TF-IDF</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -5317,7 +5537,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Silhouette Score</t>
+          <t>Centroid Classification</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -5332,7 +5552,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Rule-based Attribute Extraction</t>
+          <t>Cosine Similarity</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -5347,7 +5567,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Robust Statistics (Median, Percentiles)</t>
+          <t>Silhouette Score</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -5362,7 +5582,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ARIMAX</t>
+          <t>Rule-based Attribute Extraction</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -5370,14 +5590,14 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon</t>
+          <t>2026-quintanilla</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>Robust Statistics (Median, Percentiles)</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -5385,14 +5605,14 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon</t>
+          <t>2026-quintanilla</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Temporal Fusion Transformer</t>
+          <t>K-Nearest Neighbors</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -5400,14 +5620,14 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon</t>
+          <t>2026-astudillo</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Chronos-2</t>
+          <t>Stratified K-Fold Cross-Validation</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -5415,14 +5635,14 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2026-celedon</t>
+          <t>2026-astudillo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Linear Regression (OLS)</t>
+          <t>Bootstrap Confidence Intervals</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -5430,14 +5650,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2026-cabezas</t>
+          <t>2026-astudillo</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Ridge Regression</t>
+          <t>ARIMAX</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -5445,14 +5665,14 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2026-cabezas</t>
+          <t>2026-celedon</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Pearson Correlation</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -5460,14 +5680,14 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2026-cabezas</t>
+          <t>2026-celedon</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Log Transformation</t>
+          <t>Temporal Fusion Transformer</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -5475,14 +5695,14 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026-cabezas</t>
+          <t>2026-celedon</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Ecological Inference (EM)</t>
+          <t>Chronos-2</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -5490,14 +5710,14 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026-torres</t>
+          <t>2026-celedon</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Permutation Importance</t>
+          <t>Linear Regression (OLS)</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -5505,14 +5725,14 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-torres</t>
+          <t>2026-cabezas</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ROC / AUC</t>
+          <t>Ridge Regression</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -5520,14 +5740,14 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026-torres</t>
+          <t>2026-cabezas</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>VIF</t>
+          <t>Pearson Correlation</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -5535,14 +5755,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026-torres</t>
+          <t>2026-cabezas</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Rolling Forward Validation</t>
+          <t>Log Transformation</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -5550,14 +5770,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2026-torres</t>
+          <t>2026-cabezas</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Fourier Terms</t>
+          <t>Ecological Inference (EM)</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -5565,14 +5785,14 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2026-gutierrez</t>
+          <t>2026-torres</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Walk-Forward Validation</t>
+          <t>Permutation Importance</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -5580,14 +5800,14 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2026-gutierrez</t>
+          <t>2026-torres</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ACF/PACF</t>
+          <t>ROC / AUC</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -5595,14 +5815,14 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2026-gutierrez</t>
+          <t>2026-torres</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Ljung-Box Test</t>
+          <t>VIF</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -5610,14 +5830,14 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2026-gutierrez</t>
+          <t>2026-torres</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>K-Means</t>
+          <t>Rolling Forward Validation</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -5625,14 +5845,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2026-gutierrez</t>
+          <t>2026-torres</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Partial Least Squares</t>
+          <t>Fourier Terms</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -5640,14 +5860,14 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2026-delrio</t>
+          <t>2026-gutierrez</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Principal Component Regression</t>
+          <t>Walk-Forward Validation</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -5655,14 +5875,14 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2026-delrio</t>
+          <t>2026-gutierrez</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Ecological Inference (RxC model)</t>
+          <t>ACF/PACF</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -5670,14 +5890,14 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2026-delrio</t>
+          <t>2026-gutierrez</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Expectation-Maximization</t>
+          <t>Ljung-Box Test</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -5685,14 +5905,14 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2026-delrio</t>
+          <t>2026-gutierrez</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LAD Regression with Cardinality Constraint (MILP)</t>
+          <t>K-Means</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -5700,14 +5920,14 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2026-delrio</t>
+          <t>2026-gutierrez</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Leave-One-Out Cross-Validation</t>
+          <t>Partial Least Squares</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -5722,7 +5942,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Web Scraping</t>
+          <t>Principal Component Regression</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -5730,14 +5950,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2026-hernandez</t>
+          <t>2026-delrio</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>API Harvesting</t>
+          <t>Ecological Inference (RxC model)</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -5745,14 +5965,14 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2026-hernandez</t>
+          <t>2026-delrio</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Raster Polygonization (GDAL)</t>
+          <t>Expectation-Maximization</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -5760,14 +5980,14 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2026-hernandez</t>
+          <t>2026-delrio</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Compactness Index (Isoperimetric Quotient)</t>
+          <t>LAD Regression with Cardinality Constraint (MILP)</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -5775,14 +5995,14 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2026-hernandez</t>
+          <t>2026-delrio</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Spatial Join (Point-in-Polygon)</t>
+          <t>Leave-One-Out Cross-Validation</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -5790,14 +6010,14 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2026-hernandez</t>
+          <t>2026-delrio</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Nearest-Polygon Matching</t>
+          <t>Web Scraping</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -5812,7 +6032,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Haversine Distance</t>
+          <t>API Harvesting</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -5827,7 +6047,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>BPR Traffic Model</t>
+          <t>Raster Polygonization (GDAL)</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -5842,7 +6062,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>CLIP ViT-B/32</t>
+          <t>Compactness Index (Isoperimetric Quotient)</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -5857,7 +6077,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Weighted Scoring Model</t>
+          <t>Spatial Join (Point-in-Polygon)</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -5872,7 +6092,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Nearest-Polygon Matching</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -5880,14 +6100,14 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2025-canete</t>
+          <t>2026-hernandez</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>T-Learner</t>
+          <t>Haversine Distance</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -5895,14 +6115,14 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>2025-canete</t>
+          <t>2026-hernandez</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Feature Importance</t>
+          <t>BPR Traffic Model</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -5910,14 +6130,14 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>2025-canete</t>
+          <t>2026-hernandez</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>CLIP ViT-B/32</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -5925,14 +6145,14 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>2025-araneda</t>
+          <t>2026-hernandez</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>BERTopic</t>
+          <t>Weighted Scoring Model</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -5940,14 +6160,14 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2025-araneda</t>
+          <t>2026-hernandez</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Sentence-BERT</t>
+          <t>T-Learner</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -5955,14 +6175,14 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>2025-araneda</t>
+          <t>2025-canete</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>BERTweet (PySentimiento)</t>
+          <t>Feature Importance</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -5970,14 +6190,14 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>2025-araneda</t>
+          <t>2025-canete</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>XLM-RoBERTa</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -5992,7 +6212,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>DEA</t>
+          <t>BERTopic</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -6000,14 +6220,14 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>2025-barros</t>
+          <t>2025-araneda</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Multilayer Perceptron (MLP)</t>
+          <t>Sentence-BERT</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -6015,14 +6235,14 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>2025-barros</t>
+          <t>2025-araneda</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Support Vector Regression (SVM)</t>
+          <t>BERTweet (PySentimiento)</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -6030,14 +6250,14 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>2025-barros</t>
+          <t>2025-araneda</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Grid Search</t>
+          <t>XLM-RoBERTa</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -6045,14 +6265,14 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2025-barros</t>
+          <t>2025-araneda</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Min-Max Scaling</t>
+          <t>DEA</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -6067,7 +6287,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>One-Hot Encoding</t>
+          <t>Multilayer Perceptron (MLP)</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -6082,7 +6302,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ANOVA / Kruskal-Wallis</t>
+          <t>Support Vector Regression (SVM)</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -6097,7 +6317,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Grid Search</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -6105,14 +6325,14 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>2025-sepulveda</t>
+          <t>2025-barros</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Min-Max Scaling</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -6120,14 +6340,14 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>2025-sepulveda</t>
+          <t>2025-barros</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Zero-shot LLM classification</t>
+          <t>One-Hot Encoding</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -6135,14 +6355,14 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>2025-sepulveda</t>
+          <t>2025-barros</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>LLM-based machine translation</t>
+          <t>ANOVA / Kruskal-Wallis</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -6150,14 +6370,14 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2025-sepulveda</t>
+          <t>2025-barros</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Cohen's Kappa</t>
+          <t>Gemini</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -6172,7 +6392,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Pearson correlation</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -6187,7 +6407,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>t-test</t>
+          <t>Zero-shot LLM classification</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -6202,7 +6422,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Cohen's d</t>
+          <t>LLM-based machine translation</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -6217,7 +6437,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Threshold optimization (binarization cutoffs)</t>
+          <t>Cohen's Kappa</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -6232,7 +6452,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ARIMA</t>
+          <t>Pearson correlation</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -6240,14 +6460,14 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>2025-gajardo</t>
+          <t>2025-sepulveda</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>t-test</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -6255,14 +6475,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>2025-gajardo</t>
+          <t>2025-sepulveda</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>ADF test</t>
+          <t>Cohen's d</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -6270,14 +6490,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>2025-gajardo</t>
+          <t>2025-sepulveda</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Seasonal decomposition</t>
+          <t>Threshold optimization (binarization cutoffs)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -6285,14 +6505,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>2025-gajardo</t>
+          <t>2025-sepulveda</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Extra Trees Regressor</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -6300,14 +6520,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>2025-ceroni</t>
+          <t>2025-gajardo</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PyCaret AutoML</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -6315,14 +6535,14 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>2025-ceroni</t>
+          <t>2025-gajardo</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Random Oversampling</t>
+          <t>ADF test</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -6330,14 +6550,14 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>2025-ceroni</t>
+          <t>2025-gajardo</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Support Vector Machine</t>
+          <t>Seasonal decomposition</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -6345,14 +6565,14 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>2025-ceroni</t>
+          <t>2025-gajardo</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>Extra Trees Regressor</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -6367,7 +6587,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Neural Network</t>
+          <t>PyCaret AutoML</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -6382,7 +6602,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Multilayer Perceptron</t>
+          <t>Random Oversampling</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -6390,20 +6610,65 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>2025-yanez</t>
+          <t>2025-ceroni</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>Support Vector Machine</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>2025-ceroni</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>2025-ceroni</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Neural Network</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>2025-ceroni</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>Mortality tables (A/E ratio)</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="B97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>2025-yanez</t>
         </is>

--- a/catalogo_tesis_MAN.xlsx
+++ b/catalogo_tesis_MAN.xlsx
@@ -4765,7 +4765,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/sebastian-maldonado</t>
+          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/sebastian-maldonado-3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Ingeniería Industrial (DII), Facultad de Ciencias Físicas y Matemáticas (FCFM), Universidad de Chile</t>
+          <t>Departamento de Administración, Facultad de Economía y Negocios (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Department of Industrial Engineering (DII), School of Physical and Mathematical Sciences (FCFM), Universidad de Chile</t>
+          <t>Department of Management, School of Economics and Business (FEN), Universidad de Chile</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.dii.uchile.cl/quien/marcelo-olivares/</t>
+          <t>https://fen.uchile.cl/es/academicos-investigacion/directorio-de-academicos/detalle/marcelo-olivares</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.researchgate.net/profile/Cinthya-Vergara-Silva</t>
+          <t>https://www.linkedin.com/in/cinthya-leonor-vergara-silva-6298b221/</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
